--- a/research/traditional_assets/database/data/ireland/ireland_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_construction_supplies.xlsx
@@ -650,10 +650,10 @@
         <v>0.1686479172707065</v>
       </c>
       <c r="X2">
-        <v>0.09042774033032944</v>
+        <v>0.09040689873561278</v>
       </c>
       <c r="Y2">
-        <v>0.07822017694037706</v>
+        <v>0.07824101853509371</v>
       </c>
       <c r="Z2">
         <v>1.22249528330497</v>
@@ -662,10 +662,10 @@
         <v>0.1253379895465686</v>
       </c>
       <c r="AB2">
-        <v>0.08334417630902112</v>
+        <v>0.08332744897299357</v>
       </c>
       <c r="AC2">
-        <v>0.04199381323754746</v>
+        <v>0.04201054057357501</v>
       </c>
       <c r="AD2">
         <v>14118</v>
@@ -787,10 +787,10 @@
         <v>0.1686479172707065</v>
       </c>
       <c r="X3">
-        <v>0.09042774033032944</v>
+        <v>0.09040689873561278</v>
       </c>
       <c r="Y3">
-        <v>0.07822017694037706</v>
+        <v>0.07824101853509371</v>
       </c>
       <c r="Z3">
         <v>1.22249528330497</v>
@@ -799,10 +799,10 @@
         <v>0.1253379895465686</v>
       </c>
       <c r="AB3">
-        <v>0.08334417630902112</v>
+        <v>0.08332744897299357</v>
       </c>
       <c r="AC3">
-        <v>0.04199381323754746</v>
+        <v>0.04201054057357501</v>
       </c>
       <c r="AD3">
         <v>14118</v>
@@ -1139,49 +1139,49 @@
         <v>9.222627737226279</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>8.845794923715751</v>
       </c>
       <c r="G2">
         <v>2.27276560849811</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1.49670893982956</v>
       </c>
       <c r="I2">
         <v>0.197406136385074</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="K2">
         <v>62723.7</v>
       </c>
       <c r="L2">
-        <v>79829.8084041109</v>
+        <v>69994.6869979981</v>
       </c>
       <c r="M2">
         <v>75173.2329504852</v>
       </c>
       <c r="N2">
-        <v>76851.8084041109</v>
+        <v>77176.3472815612</v>
       </c>
       <c r="O2">
         <v>15427.5329504852</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>10159.6602835631</v>
       </c>
       <c r="Q2">
-        <v>0.08334417630902111</v>
+        <v>0.0833274489729936</v>
       </c>
       <c r="R2">
-        <v>0.0825241470333594</v>
+        <v>0.0823534229469589</v>
       </c>
       <c r="S2">
         <v>0.0545445395797173</v>
       </c>
       <c r="T2">
-        <v>0.0504320395797173</v>
+        <v>0.0492070395797173</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0904277403303294</v>
+        <v>0.09040689873561281</v>
       </c>
       <c r="X2">
-        <v>0.0825241470333594</v>
+        <v>0.0873063308064318</v>
       </c>
       <c r="Y2">
         <v>0.869471483134048</v>
       </c>
       <c r="Z2">
-        <v>0.715487684377053</v>
+        <v>0.80903564311026</v>
       </c>
       <c r="AA2">
         <v>14118</v>
@@ -1236,7 +1236,7 @@
         <v>62723.7</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963756</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08252414703335936</v>
+        <v>0.08250699649463347</v>
       </c>
       <c r="C2">
-        <v>79829.80840411088</v>
+        <v>79831.45936970701</v>
       </c>
       <c r="D2">
-        <v>76851.80840411088</v>
+        <v>76853.45936970701</v>
       </c>
       <c r="E2">
         <v>-15427.53295048516</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08252414703335936</v>
+        <v>0.08250699649463347</v>
       </c>
       <c r="T2">
         <v>0.7154876843770529</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.125</v>
       </c>
       <c r="W2">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08252456224536484</v>
+        <v>0.08249518314481236</v>
       </c>
       <c r="C3">
-        <v>79047.42717947044</v>
+        <v>79074.68861995976</v>
       </c>
       <c r="D3">
-        <v>76850.93950897529</v>
+        <v>76878.20094946462</v>
       </c>
       <c r="E3">
         <v>-14646.02062098031</v>
@@ -1539,37 +1539,37 @@
         <v>5054</v>
       </c>
       <c r="M3">
-        <v>45.04372655271517</v>
+        <v>43.94960929140838</v>
       </c>
       <c r="N3">
-        <v>5008.956273447285</v>
+        <v>5010.050390708591</v>
       </c>
       <c r="O3">
-        <v>626.1195341809106</v>
+        <v>626.2562988385739</v>
       </c>
       <c r="P3">
-        <v>4382.836739266374</v>
+        <v>4383.794091870017</v>
       </c>
       <c r="Q3">
-        <v>6116.836739266374</v>
+        <v>6117.794091870017</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08284872914097743</v>
+        <v>0.08283142701920726</v>
       </c>
       <c r="T3">
         <v>0.7218114391632138</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.125</v>
       </c>
       <c r="W3">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>112.202084214441</v>
+        <v>114.9953340083047</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08252497745737031</v>
+        <v>0.08248336979499123</v>
       </c>
       <c r="C4">
-        <v>78265.04597447744</v>
+        <v>78317.93380554991</v>
       </c>
       <c r="D4">
-        <v>76850.07063348715</v>
+        <v>76902.95846455962</v>
       </c>
       <c r="E4">
         <v>-13864.50829147546</v>
@@ -1621,37 +1621,37 @@
         <v>5054</v>
       </c>
       <c r="M4">
-        <v>90.08745310543034</v>
+        <v>87.89921858281676</v>
       </c>
       <c r="N4">
-        <v>4963.912546894569</v>
+        <v>4966.100781417183</v>
       </c>
       <c r="O4">
-        <v>620.4890683618212</v>
+        <v>620.7625976771479</v>
       </c>
       <c r="P4">
-        <v>4343.423478532748</v>
+        <v>4345.338183740036</v>
       </c>
       <c r="Q4">
-        <v>6077.423478532748</v>
+        <v>6079.338183740036</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08317993537324077</v>
+        <v>0.08316247857489478</v>
       </c>
       <c r="T4">
         <v>0.7282642501695002</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.125</v>
       </c>
       <c r="W4">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>56.1010421072205</v>
+        <v>57.49766700415238</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08252539266937578</v>
+        <v>0.08247155644517012</v>
       </c>
       <c r="C5">
-        <v>77482.6647891312</v>
+        <v>77561.19494187758</v>
       </c>
       <c r="D5">
-        <v>76849.20177764575</v>
+        <v>76927.73193039212</v>
       </c>
       <c r="E5">
         <v>-13082.99596197061</v>
@@ -1703,37 +1703,37 @@
         <v>5054</v>
       </c>
       <c r="M5">
-        <v>135.1311796581455</v>
+        <v>131.8488278742252</v>
       </c>
       <c r="N5">
-        <v>4918.868820341854</v>
+        <v>4922.151172125775</v>
       </c>
       <c r="O5">
-        <v>614.8586025427318</v>
+        <v>615.2688965157218</v>
       </c>
       <c r="P5">
-        <v>4304.010217799122</v>
+        <v>4306.882275610053</v>
       </c>
       <c r="Q5">
-        <v>6038.010217799122</v>
+        <v>6040.882275610053</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08351797059998377</v>
+        <v>0.08350035593585423</v>
       </c>
       <c r="T5">
         <v>0.7348501088254009</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.125</v>
       </c>
       <c r="W5">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>37.400694738147</v>
+        <v>38.33177800276825</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08252580788138124</v>
+        <v>0.08245974309534899</v>
       </c>
       <c r="C6">
-        <v>76700.28362343107</v>
+        <v>76804.47204436292</v>
       </c>
       <c r="D6">
-        <v>76848.33294145047</v>
+        <v>76952.52136238232</v>
       </c>
       <c r="E6">
         <v>-12301.48363246576</v>
@@ -1785,37 +1785,37 @@
         <v>5054</v>
       </c>
       <c r="M6">
-        <v>180.1749062108607</v>
+        <v>175.7984371656335</v>
       </c>
       <c r="N6">
-        <v>4873.825093789139</v>
+        <v>4878.201562834366</v>
       </c>
       <c r="O6">
-        <v>609.2281367236424</v>
+        <v>609.7751953542958</v>
       </c>
       <c r="P6">
-        <v>4264.596957065496</v>
+        <v>4268.42636748007</v>
       </c>
       <c r="Q6">
-        <v>5998.596957065496</v>
+        <v>6002.42636748007</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08386304822728391</v>
+        <v>0.08384527240850032</v>
       </c>
       <c r="T6">
         <v>0.7415731728699663</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.125</v>
       </c>
       <c r="W6">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>28.05052105361025</v>
+        <v>28.74883350207618</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08252622309338672</v>
+        <v>0.08244792974552788</v>
       </c>
       <c r="C7">
-        <v>75917.90247737632</v>
+        <v>76047.76512844575</v>
       </c>
       <c r="D7">
-        <v>76847.46412490058</v>
+        <v>76977.32677597001</v>
       </c>
       <c r="E7">
         <v>-11519.9713029609</v>
@@ -1867,37 +1867,37 @@
         <v>5054</v>
       </c>
       <c r="M7">
-        <v>225.2186327635759</v>
+        <v>219.7480464570419</v>
       </c>
       <c r="N7">
-        <v>4828.781367236425</v>
+        <v>4834.251953542958</v>
       </c>
       <c r="O7">
-        <v>603.5976709045531</v>
+        <v>604.2814941928698</v>
       </c>
       <c r="P7">
-        <v>4225.183696331871</v>
+        <v>4229.970459350088</v>
       </c>
       <c r="Q7">
-        <v>5959.183696331871</v>
+        <v>5963.970459350088</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08421539064673775</v>
+        <v>0.08419745028057055</v>
       </c>
       <c r="T7">
         <v>0.7484377751049435</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.125</v>
       </c>
       <c r="W7">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.4404168428882</v>
+        <v>22.99906680166094</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.0825266383053922</v>
+        <v>0.08243611639570675</v>
       </c>
       <c r="C8">
-        <v>75135.52135096634</v>
+        <v>75291.07420958602</v>
       </c>
       <c r="D8">
-        <v>76846.59532799546</v>
+        <v>77002.14818661513</v>
       </c>
       <c r="E8">
         <v>-10738.45897345605</v>
@@ -1949,37 +1949,37 @@
         <v>5054</v>
       </c>
       <c r="M8">
-        <v>270.2623593162911</v>
+        <v>263.6976557484503</v>
       </c>
       <c r="N8">
-        <v>4783.737640683709</v>
+        <v>4790.30234425155</v>
       </c>
       <c r="O8">
-        <v>597.9672050854637</v>
+        <v>598.7877930314437</v>
       </c>
       <c r="P8">
-        <v>4185.770435598246</v>
+        <v>4191.514551220106</v>
       </c>
       <c r="Q8">
-        <v>5919.770435598246</v>
+        <v>5925.514551220106</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.084575229713414</v>
+        <v>0.08455712129885502</v>
       </c>
       <c r="T8">
         <v>0.7554484327066224</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.125</v>
       </c>
       <c r="W8">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.7003473690735</v>
+        <v>19.16588900138412</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08252705351739767</v>
+        <v>0.08242430304588565</v>
       </c>
       <c r="C9">
-        <v>74353.14024420048</v>
+        <v>74534.39930326339</v>
       </c>
       <c r="D9">
-        <v>76845.72655073444</v>
+        <v>77026.98560979735</v>
       </c>
       <c r="E9">
         <v>-9956.9466439512</v>
@@ -2031,37 +2031,37 @@
         <v>5054</v>
       </c>
       <c r="M9">
-        <v>315.3060858690062</v>
+        <v>307.6472650398587</v>
       </c>
       <c r="N9">
-        <v>4738.693914130994</v>
+        <v>4746.352734960141</v>
       </c>
       <c r="O9">
-        <v>592.3367392663743</v>
+        <v>593.2940918700176</v>
       </c>
       <c r="P9">
-        <v>4146.35717486462</v>
+        <v>4153.058643090123</v>
       </c>
       <c r="Q9">
-        <v>5880.35717486462</v>
+        <v>5887.058643090123</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08494280725464243</v>
+        <v>0.08492452717774777</v>
       </c>
       <c r="T9">
         <v>0.7626098571384449</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.125</v>
       </c>
       <c r="W9">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.02886917349157</v>
+        <v>16.42790485832925</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08252746872940316</v>
+        <v>0.08241248969606453</v>
       </c>
       <c r="C10">
-        <v>73570.75915707802</v>
+        <v>73777.74042497773</v>
       </c>
       <c r="D10">
-        <v>76844.85779311684</v>
+        <v>77051.83906101655</v>
       </c>
       <c r="E10">
         <v>-9175.434314446349</v>
@@ -2113,37 +2113,37 @@
         <v>5054</v>
       </c>
       <c r="M10">
-        <v>360.3498124217214</v>
+        <v>351.596874331267</v>
       </c>
       <c r="N10">
-        <v>4693.650187578279</v>
+        <v>4702.403125668733</v>
       </c>
       <c r="O10">
-        <v>586.7062734472848</v>
+        <v>587.8003907085916</v>
       </c>
       <c r="P10">
-        <v>4106.943914130994</v>
+        <v>4114.602734960142</v>
       </c>
       <c r="Q10">
-        <v>5840.943914130994</v>
+        <v>5848.602734960142</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08531837561198452</v>
+        <v>0.08529992014096428</v>
       </c>
       <c r="T10">
         <v>0.7699269647100896</v>
       </c>
       <c r="U10">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V10">
         <v>0.125</v>
       </c>
       <c r="W10">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.02526052680513</v>
+        <v>14.37441675103809</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08252788394140861</v>
+        <v>0.08240067634624339</v>
       </c>
       <c r="C11">
-        <v>72788.37808959839</v>
+        <v>73021.09759024887</v>
       </c>
       <c r="D11">
-        <v>76843.98905514205</v>
+        <v>77076.70855579253</v>
       </c>
       <c r="E11">
         <v>-8393.921984941497</v>
@@ -2195,37 +2195,37 @@
         <v>5054</v>
       </c>
       <c r="M11">
-        <v>405.3935389744365</v>
+        <v>395.5464836226754</v>
       </c>
       <c r="N11">
-        <v>4648.606461025563</v>
+        <v>4658.453516377324</v>
       </c>
       <c r="O11">
-        <v>581.0758076281954</v>
+        <v>582.3066895471655</v>
       </c>
       <c r="P11">
-        <v>4067.530653397368</v>
+        <v>4076.146826830159</v>
       </c>
       <c r="Q11">
-        <v>5801.530653397368</v>
+        <v>5810.146826830159</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08570219821893851</v>
+        <v>0.08568356349897674</v>
       </c>
       <c r="T11">
         <v>0.7774048878327593</v>
       </c>
       <c r="U11">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.466898246049</v>
+        <v>12.77725933425608</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.0825282991534141</v>
+        <v>0.08238886299642229</v>
       </c>
       <c r="C12">
-        <v>72005.9970417608</v>
+        <v>72264.47081461646</v>
       </c>
       <c r="D12">
-        <v>76843.12033680931</v>
+        <v>77101.59410966498</v>
       </c>
       <c r="E12">
         <v>-7612.409655436644</v>
@@ -2277,37 +2277,37 @@
         <v>5054</v>
       </c>
       <c r="M12">
-        <v>450.4372655271517</v>
+        <v>439.4960929140839</v>
       </c>
       <c r="N12">
-        <v>4603.562734472848</v>
+        <v>4614.503907085917</v>
       </c>
       <c r="O12">
-        <v>575.445341809106</v>
+        <v>576.8129883857396</v>
       </c>
       <c r="P12">
-        <v>4028.117392663742</v>
+        <v>4037.690918700177</v>
       </c>
       <c r="Q12">
-        <v>5762.117392663742</v>
+        <v>5771.690918700177</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08609455021715817</v>
+        <v>0.08607573226494505</v>
       </c>
       <c r="T12">
         <v>0.785048987024822</v>
       </c>
       <c r="U12">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V12">
         <v>0.125</v>
       </c>
       <c r="W12">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.2202084214441</v>
+        <v>11.49953340083047</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08252871436541957</v>
+        <v>0.08237704964660118</v>
       </c>
       <c r="C13">
-        <v>71223.61601356465</v>
+        <v>71507.86011364048</v>
       </c>
       <c r="D13">
-        <v>76842.25163811802</v>
+        <v>77126.49573819384</v>
       </c>
       <c r="E13">
         <v>-6830.897325931794</v>
@@ -2359,37 +2359,37 @@
         <v>5054</v>
       </c>
       <c r="M13">
-        <v>495.4809920798669</v>
+        <v>483.4457022054922</v>
       </c>
       <c r="N13">
-        <v>4558.519007920133</v>
+        <v>4570.554297794508</v>
       </c>
       <c r="O13">
-        <v>569.8148759900166</v>
+        <v>571.3192872243135</v>
       </c>
       <c r="P13">
-        <v>3988.704131930116</v>
+        <v>3999.235010570194</v>
       </c>
       <c r="Q13">
-        <v>5722.704131930116</v>
+        <v>5733.235010570194</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08649571911421423</v>
+        <v>0.08647671381217109</v>
       </c>
       <c r="T13">
         <v>0.7928648637268185</v>
       </c>
       <c r="U13">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.20018947404009</v>
+        <v>10.45412127348225</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08252912957742503</v>
+        <v>0.08236523629678005</v>
       </c>
       <c r="C14">
-        <v>70441.23500500931</v>
+        <v>70751.26550290102</v>
       </c>
       <c r="D14">
-        <v>76841.38295906753</v>
+        <v>77151.41345695924</v>
       </c>
       <c r="E14">
         <v>-6049.384996426941</v>
@@ -2441,37 +2441,37 @@
         <v>5054</v>
       </c>
       <c r="M14">
-        <v>540.5247186325821</v>
+        <v>527.3953114969006</v>
       </c>
       <c r="N14">
-        <v>4513.475281367418</v>
+        <v>4526.604688503099</v>
       </c>
       <c r="O14">
-        <v>564.1844101709272</v>
+        <v>565.8255860628874</v>
       </c>
       <c r="P14">
-        <v>3949.290871196491</v>
+        <v>3960.779102440212</v>
       </c>
       <c r="Q14">
-        <v>5683.29087119649</v>
+        <v>5694.779102440212</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08690600548620336</v>
+        <v>0.08688680857637951</v>
       </c>
       <c r="T14">
         <v>0.8008583739902241</v>
       </c>
       <c r="U14">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V14">
         <v>0.125</v>
       </c>
       <c r="W14">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.350173684536749</v>
+        <v>9.58294450069206</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08265466978943052</v>
+        <v>0.08235342294695892</v>
       </c>
       <c r="C15">
-        <v>69397.97338938704</v>
+        <v>69994.68699799814</v>
       </c>
       <c r="D15">
-        <v>76579.63367295012</v>
+        <v>77176.34728156122</v>
       </c>
       <c r="E15">
         <v>-5267.872666922091</v>
@@ -2523,45 +2523,45 @@
         <v>5054</v>
       </c>
       <c r="M15">
-        <v>596.7440714972165</v>
+        <v>571.344920788309</v>
       </c>
       <c r="N15">
-        <v>4457.255928502784</v>
+        <v>4482.655079211691</v>
       </c>
       <c r="O15">
-        <v>557.156991062848</v>
+        <v>560.3318849014614</v>
       </c>
       <c r="P15">
-        <v>3900.098937439936</v>
+        <v>3922.32319431023</v>
       </c>
       <c r="Q15">
-        <v>5634.098937439936</v>
+        <v>5656.32319431023</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08732572372881295</v>
+        <v>0.08730633080643181</v>
       </c>
       <c r="T15">
         <v>0.8090356431102596</v>
       </c>
       <c r="U15">
-        <v>0.0587366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V15">
         <v>0.125</v>
       </c>
       <c r="W15">
-        <v>0.05139453957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>8.469292350604565</v>
+        <v>8.845794923715749</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08266471000143599</v>
+        <v>0.08252535959713782</v>
       </c>
       <c r="C16">
-        <v>68595.60437180984</v>
+        <v>68851.85914237745</v>
       </c>
       <c r="D16">
-        <v>76558.77698487777</v>
+        <v>76815.03175544536</v>
       </c>
       <c r="E16">
         <v>-4486.360337417238</v>
@@ -2605,37 +2605,37 @@
         <v>5054</v>
       </c>
       <c r="M16">
-        <v>642.6474616123871</v>
+        <v>631.7062889993192</v>
       </c>
       <c r="N16">
-        <v>4411.352538387613</v>
+        <v>4422.293711000681</v>
       </c>
       <c r="O16">
-        <v>551.4190672984516</v>
+        <v>552.7867138750851</v>
       </c>
       <c r="P16">
-        <v>3859.933471089162</v>
+        <v>3869.506997125595</v>
       </c>
       <c r="Q16">
-        <v>5593.933471089162</v>
+        <v>5603.506997125595</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08775520286078554</v>
+        <v>0.08773560936741556</v>
       </c>
       <c r="T16">
         <v>0.8174030812795983</v>
       </c>
       <c r="U16">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.864342896989953</v>
+        <v>8.000553561063956</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08267475021344146</v>
+        <v>0.08252667124731669</v>
       </c>
       <c r="C17">
-        <v>67793.24671189982</v>
+        <v>68067.60345370825</v>
       </c>
       <c r="D17">
-        <v>76537.93165447259</v>
+        <v>76812.28839628102</v>
       </c>
       <c r="E17">
         <v>-3704.848007912387</v>
@@ -2687,37 +2687,37 @@
         <v>5054</v>
       </c>
       <c r="M17">
-        <v>688.5508517275575</v>
+        <v>676.8281667849848</v>
       </c>
       <c r="N17">
-        <v>4365.449148272442</v>
+        <v>4377.171833215015</v>
       </c>
       <c r="O17">
-        <v>545.6811435340553</v>
+        <v>547.1464791518769</v>
       </c>
       <c r="P17">
-        <v>3819.768004738387</v>
+        <v>3830.025354063138</v>
       </c>
       <c r="Q17">
-        <v>5553.768004738387</v>
+        <v>5564.025354063138</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08819478738409867</v>
+        <v>0.08817498860042246</v>
       </c>
       <c r="T17">
         <v>0.825967400347039</v>
       </c>
       <c r="U17">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V17">
         <v>0.125</v>
       </c>
       <c r="W17">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.340053370523957</v>
+        <v>7.467183323659693</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08268479042544695</v>
+        <v>0.08252798289749558</v>
       </c>
       <c r="C18">
-        <v>66990.90040038207</v>
+        <v>67283.34796098375</v>
       </c>
       <c r="D18">
-        <v>76517.0976724597</v>
+        <v>76809.54523306138</v>
       </c>
       <c r="E18">
         <v>-2923.335678407535</v>
@@ -2769,37 +2769,37 @@
         <v>5054</v>
       </c>
       <c r="M18">
-        <v>734.4542418427282</v>
+        <v>721.9500445706504</v>
       </c>
       <c r="N18">
-        <v>4319.545758157272</v>
+        <v>4332.049955429349</v>
       </c>
       <c r="O18">
-        <v>539.943219769659</v>
+        <v>541.5062444286687</v>
       </c>
       <c r="P18">
-        <v>3779.602538387613</v>
+        <v>3790.543711000681</v>
       </c>
       <c r="Q18">
-        <v>5513.602538387613</v>
+        <v>5524.543711000681</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08864483820558591</v>
+        <v>0.08862482924373905</v>
       </c>
       <c r="T18">
         <v>0.8347356317732284</v>
       </c>
       <c r="U18">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.881300034866208</v>
+        <v>7.000484365930962</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08302208063745242</v>
+        <v>0.08278216954767446</v>
       </c>
       <c r="C19">
-        <v>65516.02360403389</v>
+        <v>65973.90659855974</v>
       </c>
       <c r="D19">
-        <v>75823.73320561637</v>
+        <v>76281.61620014222</v>
       </c>
       <c r="E19">
         <v>-2141.823348902682</v>
@@ -2851,37 +2851,37 @@
         <v>5054</v>
       </c>
       <c r="M19">
-        <v>809.5861930813801</v>
+        <v>789.6576286790064</v>
       </c>
       <c r="N19">
-        <v>4244.41380691862</v>
+        <v>4264.342371320994</v>
       </c>
       <c r="O19">
-        <v>530.5517258648275</v>
+        <v>533.0427964151243</v>
       </c>
       <c r="P19">
-        <v>3713.862081053793</v>
+        <v>3731.29957490587</v>
       </c>
       <c r="Q19">
-        <v>5447.862081053792</v>
+        <v>5465.29957490587</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08910573362518129</v>
+        <v>0.08908550942062954</v>
       </c>
       <c r="T19">
         <v>0.8437151458843862</v>
       </c>
       <c r="U19">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V19">
         <v>0.125</v>
       </c>
       <c r="W19">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.242695395735299</v>
+        <v>6.400242100433677</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08305137084945789</v>
+        <v>0.08279835619785335</v>
       </c>
       <c r="C20">
-        <v>64674.89217407729</v>
+        <v>65159.0213313517</v>
       </c>
       <c r="D20">
-        <v>75764.11410516463</v>
+        <v>76248.24326243903</v>
       </c>
       <c r="E20">
         <v>-1360.311019397832</v>
@@ -2933,37 +2933,37 @@
         <v>5054</v>
       </c>
       <c r="M20">
-        <v>857.2089103214612</v>
+        <v>836.1080774248302</v>
       </c>
       <c r="N20">
-        <v>4196.791089678539</v>
+        <v>4217.89192257517</v>
       </c>
       <c r="O20">
-        <v>524.5988862098174</v>
+        <v>527.2364903218962</v>
       </c>
       <c r="P20">
-        <v>3672.192203468721</v>
+        <v>3690.655432253273</v>
       </c>
       <c r="Q20">
-        <v>5406.192203468721</v>
+        <v>5424.655432253274</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08957787039647411</v>
+        <v>0.08955742569939538</v>
       </c>
       <c r="T20">
         <v>0.8529136725348405</v>
       </c>
       <c r="U20">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V20">
         <v>0.125</v>
       </c>
       <c r="W20">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.895878984861116</v>
+        <v>6.044673094854028</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08333003606146337</v>
+        <v>0.08281454284803222</v>
       </c>
       <c r="C21">
-        <v>63330.82182078195</v>
+        <v>64344.16525245869</v>
       </c>
       <c r="D21">
-        <v>75201.55608137413</v>
+        <v>76214.89951305087</v>
       </c>
       <c r="E21">
         <v>-578.7986898929794</v>
@@ -3015,45 +3015,45 @@
         <v>5054</v>
       </c>
       <c r="M21">
-        <v>927.1047289524307</v>
+        <v>882.5585261706542</v>
       </c>
       <c r="N21">
-        <v>4126.89527104757</v>
+        <v>4171.441473829345</v>
       </c>
       <c r="O21">
-        <v>515.8619088809462</v>
+        <v>521.4301842286682</v>
       </c>
       <c r="P21">
-        <v>3611.033362166623</v>
+        <v>3650.011289600677</v>
       </c>
       <c r="Q21">
-        <v>5345.033362166623</v>
+        <v>5384.011289600678</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09006166486582354</v>
+        <v>0.09004099423195792</v>
       </c>
       <c r="T21">
         <v>0.8623393233001208</v>
       </c>
       <c r="U21">
-        <v>0.0624366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V21">
         <v>0.125</v>
       </c>
       <c r="W21">
-        <v>0.05463203957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>5.451379808741455</v>
+        <v>5.726532405651183</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08337245127346884</v>
+        <v>0.08297072949821109</v>
       </c>
       <c r="C22">
-        <v>62464.41511158605</v>
+        <v>63242.40766521049</v>
       </c>
       <c r="D22">
-        <v>75116.66170168309</v>
+        <v>75894.65425530753</v>
       </c>
       <c r="E22">
         <v>202.7136396118731</v>
@@ -3097,37 +3097,37 @@
         <v>5054</v>
       </c>
       <c r="M22">
-        <v>975.8997146867692</v>
+        <v>941.5131721885558</v>
       </c>
       <c r="N22">
-        <v>4078.100285313231</v>
+        <v>4112.486827811445</v>
       </c>
       <c r="O22">
-        <v>509.7625356641539</v>
+        <v>514.0608534764306</v>
       </c>
       <c r="P22">
-        <v>3568.337749649077</v>
+        <v>3598.425974335014</v>
       </c>
       <c r="Q22">
-        <v>5302.337749649078</v>
+        <v>5332.425974335014</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09055755419690671</v>
+        <v>0.09053665197783453</v>
       </c>
       <c r="T22">
         <v>0.8720006153345332</v>
       </c>
       <c r="U22">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.178810818304382</v>
+        <v>5.367954638650389</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.0834148664854743</v>
+        <v>0.08299391614838998</v>
       </c>
       <c r="C23">
-        <v>61598.19985930332</v>
+        <v>62413.58268404388</v>
       </c>
       <c r="D23">
-        <v>75031.9587789052</v>
+        <v>75847.34160364576</v>
       </c>
       <c r="E23">
         <v>984.2259691167237</v>
@@ -3179,37 +3179,37 @@
         <v>5054</v>
       </c>
       <c r="M23">
-        <v>1024.694700421108</v>
+        <v>988.5888307979835</v>
       </c>
       <c r="N23">
-        <v>4029.305299578892</v>
+        <v>4065.411169202016</v>
       </c>
       <c r="O23">
-        <v>503.6631624473615</v>
+        <v>508.1763961502521</v>
       </c>
       <c r="P23">
-        <v>3525.64213713153</v>
+        <v>3557.234773051764</v>
       </c>
       <c r="Q23">
-        <v>5259.64213713153</v>
+        <v>5291.234773051765</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09106599768827046</v>
+        <v>0.09104485802107512</v>
       </c>
       <c r="T23">
         <v>0.8819064970407028</v>
       </c>
       <c r="U23">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.932200779337506</v>
+        <v>5.112337751095608</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08345728169747979</v>
+        <v>0.08301710279856887</v>
       </c>
       <c r="C24">
-        <v>60732.17541699222</v>
+        <v>61584.81665544587</v>
       </c>
       <c r="D24">
-        <v>74947.44666609896</v>
+        <v>75800.08790455261</v>
       </c>
       <c r="E24">
         <v>1765.738298621574</v>
@@ -3261,37 +3261,37 @@
         <v>5054</v>
       </c>
       <c r="M24">
-        <v>1073.489686155446</v>
+        <v>1035.664489407411</v>
       </c>
       <c r="N24">
-        <v>3980.510313844554</v>
+        <v>4018.335510592588</v>
       </c>
       <c r="O24">
-        <v>497.5637892305692</v>
+        <v>502.2919388240736</v>
       </c>
       <c r="P24">
-        <v>3482.946524613984</v>
+        <v>3516.043571768515</v>
       </c>
       <c r="Q24">
-        <v>5216.946524613984</v>
+        <v>5250.043571768515</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.0915874781922333</v>
+        <v>0.09156609498850135</v>
       </c>
       <c r="T24">
         <v>0.8920663757136974</v>
       </c>
       <c r="U24">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V24">
         <v>0.125</v>
       </c>
       <c r="W24">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.708009834822166</v>
+        <v>4.879958762409444</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08349969690948525</v>
+        <v>0.08304028944874775</v>
       </c>
       <c r="C25">
-        <v>59866.34114062284</v>
+        <v>60756.10946930086</v>
       </c>
       <c r="D25">
-        <v>74863.12471923443</v>
+        <v>75752.89304791245</v>
       </c>
       <c r="E25">
         <v>2547.250628126429</v>
@@ -3343,37 +3343,37 @@
         <v>5054</v>
       </c>
       <c r="M25">
-        <v>1122.284671889785</v>
+        <v>1082.740148016839</v>
       </c>
       <c r="N25">
-        <v>3931.715328110216</v>
+        <v>3971.259851983161</v>
       </c>
       <c r="O25">
-        <v>491.4644160137769</v>
+        <v>496.4074814978951</v>
       </c>
       <c r="P25">
-        <v>3440.250912096439</v>
+        <v>3474.852370485266</v>
       </c>
       <c r="Q25">
-        <v>5174.250912096439</v>
+        <v>5208.852370485266</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.092122503644351</v>
+        <v>0.09210087057845812</v>
       </c>
       <c r="T25">
         <v>0.902490147339237</v>
       </c>
       <c r="U25">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V25">
         <v>0.125</v>
       </c>
       <c r="W25">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.503313755047288</v>
+        <v>4.667786642304685</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08354211212149074</v>
+        <v>0.08306347609892661</v>
       </c>
       <c r="C26">
-        <v>59000.69638906015</v>
+        <v>59927.46101576735</v>
       </c>
       <c r="D26">
-        <v>74778.99229717659</v>
+        <v>75705.75692388379</v>
       </c>
       <c r="E26">
         <v>3328.762957631279</v>
@@ -3425,37 +3425,37 @@
         <v>5054</v>
       </c>
       <c r="M26">
-        <v>1171.079657624123</v>
+        <v>1129.815806626267</v>
       </c>
       <c r="N26">
-        <v>3882.920342375877</v>
+        <v>3924.184193373733</v>
       </c>
       <c r="O26">
-        <v>485.3650427969847</v>
+        <v>490.5230241717167</v>
       </c>
       <c r="P26">
-        <v>3397.555299578893</v>
+        <v>3433.661169202016</v>
       </c>
       <c r="Q26">
-        <v>5131.555299578893</v>
+        <v>5167.661169202016</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.0926716087136297</v>
+        <v>0.09264971921025586</v>
       </c>
       <c r="T26">
         <v>0.9131882287443963</v>
       </c>
       <c r="U26">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V26">
         <v>0.125</v>
       </c>
       <c r="W26">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.315675681920318</v>
+        <v>4.473295532208658</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.0838907773334962</v>
+        <v>0.08308666274910551</v>
       </c>
       <c r="C27">
-        <v>57534.69203739007</v>
+        <v>59098.87118527684</v>
       </c>
       <c r="D27">
-        <v>74094.50027501136</v>
+        <v>75658.67942289813</v>
       </c>
       <c r="E27">
         <v>4110.27528713613</v>
@@ -3507,45 +3507,45 @@
         <v>5054</v>
       </c>
       <c r="M27">
-        <v>1247.227574891131</v>
+        <v>1176.891465235695</v>
       </c>
       <c r="N27">
-        <v>3806.772425108868</v>
+        <v>3877.108534764306</v>
       </c>
       <c r="O27">
-        <v>475.8465531386086</v>
+        <v>484.6385668455382</v>
       </c>
       <c r="P27">
-        <v>3330.92587197026</v>
+        <v>3392.469967918767</v>
       </c>
       <c r="Q27">
-        <v>5064.925871970259</v>
+        <v>5126.469967918767</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09323535658475583</v>
+        <v>0.09321320380556823</v>
       </c>
       <c r="T27">
         <v>0.9241715923203599</v>
       </c>
       <c r="U27">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.05585703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.052187509116896</v>
+        <v>4.294363710920312</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08394544254550168</v>
+        <v>0.08333734939928439</v>
       </c>
       <c r="C28">
-        <v>56646.996864125</v>
+        <v>57812.08554252506</v>
       </c>
       <c r="D28">
-        <v>73988.31743125114</v>
+        <v>75153.4061096512</v>
       </c>
       <c r="E28">
         <v>4891.787616640981</v>
@@ -3589,37 +3589,37 @@
         <v>5054</v>
       </c>
       <c r="M28">
-        <v>1297.116677886776</v>
+        <v>1244.286444412249</v>
       </c>
       <c r="N28">
-        <v>3756.883322113224</v>
+        <v>3809.713555587751</v>
       </c>
       <c r="O28">
-        <v>469.6104152641529</v>
+        <v>476.2141944484689</v>
       </c>
       <c r="P28">
-        <v>3287.272906849071</v>
+        <v>3333.499361139282</v>
       </c>
       <c r="Q28">
-        <v>5021.272906849071</v>
+        <v>5067.499361139282</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09381434088483132</v>
+        <v>0.09379191771426741</v>
       </c>
       <c r="T28">
         <v>0.9354518035605388</v>
       </c>
       <c r="U28">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.896334143381631</v>
+        <v>4.061765699285833</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08400010775750716</v>
+        <v>0.08336928604946327</v>
       </c>
       <c r="C29">
-        <v>55759.60559092756</v>
+        <v>56966.68730266474</v>
       </c>
       <c r="D29">
-        <v>73882.43848755855</v>
+        <v>75089.52019929573</v>
       </c>
       <c r="E29">
         <v>5673.299946145835</v>
@@ -3671,37 +3671,37 @@
         <v>5054</v>
       </c>
       <c r="M29">
-        <v>1347.005780882422</v>
+        <v>1292.143615351181</v>
       </c>
       <c r="N29">
-        <v>3706.994219117578</v>
+        <v>3761.856384648819</v>
       </c>
       <c r="O29">
-        <v>463.3742773896972</v>
+        <v>470.2320480811023</v>
       </c>
       <c r="P29">
-        <v>3243.61994172788</v>
+        <v>3291.624336567716</v>
       </c>
       <c r="Q29">
-        <v>4977.61994172788</v>
+        <v>5025.624336567716</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09440918776847051</v>
+        <v>0.09438648679854739</v>
       </c>
       <c r="T29">
         <v>0.9470410616840101</v>
       </c>
       <c r="U29">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V29">
         <v>0.125</v>
       </c>
       <c r="W29">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.752025471404532</v>
+        <v>3.911329932645617</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08405477296951264</v>
+        <v>0.08340122269964215</v>
       </c>
       <c r="C30">
-        <v>54872.51691499862</v>
+        <v>56121.39758597594</v>
       </c>
       <c r="D30">
-        <v>73776.86214113446</v>
+        <v>75025.74281211178</v>
       </c>
       <c r="E30">
         <v>6454.812275650685</v>
@@ -3753,37 +3753,37 @@
         <v>5054</v>
       </c>
       <c r="M30">
-        <v>1396.894883878067</v>
+        <v>1340.000786290114</v>
       </c>
       <c r="N30">
-        <v>3657.105116121933</v>
+        <v>3713.999213709886</v>
       </c>
       <c r="O30">
-        <v>457.1381395152416</v>
+        <v>464.2499017137358</v>
       </c>
       <c r="P30">
-        <v>3199.966976606691</v>
+        <v>3249.74931199615</v>
       </c>
       <c r="Q30">
-        <v>4933.966976606691</v>
+        <v>4983.749311996151</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09502055817665525</v>
+        <v>0.09499757169072404</v>
       </c>
       <c r="T30">
         <v>0.9589522436442446</v>
       </c>
       <c r="U30">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V30">
         <v>0.125</v>
       </c>
       <c r="W30">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.618024561711514</v>
+        <v>3.771639577908274</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.0841094381815181</v>
+        <v>0.08343315934982103</v>
       </c>
       <c r="C31">
-        <v>53985.72954097514</v>
+        <v>55276.21611617041</v>
       </c>
       <c r="D31">
-        <v>73671.58709661584</v>
+        <v>74962.07367181111</v>
       </c>
       <c r="E31">
         <v>7236.324605155536</v>
@@ -3835,37 +3835,37 @@
         <v>5054</v>
       </c>
       <c r="M31">
-        <v>1446.783986873712</v>
+        <v>1387.857957229046</v>
       </c>
       <c r="N31">
-        <v>3607.216013126288</v>
+        <v>3666.142042770954</v>
       </c>
       <c r="O31">
-        <v>450.902001640786</v>
+        <v>458.2677553463692</v>
       </c>
       <c r="P31">
-        <v>3156.314011485502</v>
+        <v>3207.874287424585</v>
       </c>
       <c r="Q31">
-        <v>4890.314011485502</v>
+        <v>4941.874287424585</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09564915028647898</v>
+        <v>0.09562587024183522</v>
       </c>
       <c r="T31">
         <v>0.9711989518568799</v>
       </c>
       <c r="U31">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V31">
         <v>0.125</v>
       </c>
       <c r="W31">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.49326509406629</v>
+        <v>3.641583040739023</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08416410339352356</v>
+        <v>0.08346509599999991</v>
       </c>
       <c r="C32">
-        <v>53099.2421808771</v>
+        <v>54431.14261789701</v>
       </c>
       <c r="D32">
-        <v>73566.61206602264</v>
+        <v>74898.51250304256</v>
       </c>
       <c r="E32">
         <v>8017.836934660387</v>
@@ -3917,37 +3917,37 @@
         <v>5054</v>
       </c>
       <c r="M32">
-        <v>1496.673089869357</v>
+        <v>1435.715128167979</v>
       </c>
       <c r="N32">
-        <v>3557.326910130642</v>
+        <v>3618.284871832021</v>
       </c>
       <c r="O32">
-        <v>444.6658637663303</v>
+        <v>452.2856089790026</v>
       </c>
       <c r="P32">
-        <v>3112.661046364312</v>
+        <v>3165.999262853019</v>
       </c>
       <c r="Q32">
-        <v>4846.661046364312</v>
+        <v>4899.999262853018</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09629570217086911</v>
+        <v>0.09627212018012102</v>
       </c>
       <c r="T32">
         <v>0.9837955660184478</v>
       </c>
       <c r="U32">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V32">
         <v>0.125</v>
       </c>
       <c r="W32">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.37682292426408</v>
+        <v>3.520196939381056</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08421876860552906</v>
+        <v>0.0834970326501788</v>
       </c>
       <c r="C33">
-        <v>52213.053554055</v>
+        <v>53586.17681673759</v>
       </c>
       <c r="D33">
-        <v>73461.9357687054</v>
+        <v>74835.05903138799</v>
       </c>
       <c r="E33">
         <v>8799.349264165241</v>
@@ -3999,37 +3999,37 @@
         <v>5054</v>
       </c>
       <c r="M33">
-        <v>1546.562192865003</v>
+        <v>1483.572299106912</v>
       </c>
       <c r="N33">
-        <v>3507.437807134997</v>
+        <v>3570.427700893089</v>
       </c>
       <c r="O33">
-        <v>438.4297258918747</v>
+        <v>446.3034626116361</v>
       </c>
       <c r="P33">
-        <v>3069.008081243123</v>
+        <v>3124.124238281453</v>
       </c>
       <c r="Q33">
-        <v>4803.008081243122</v>
+        <v>4858.124238281453</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09696099468958939</v>
+        <v>0.09693710200067598</v>
       </c>
       <c r="T33">
         <v>0.9967572994310756</v>
       </c>
       <c r="U33">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V33">
         <v>0.125</v>
       </c>
       <c r="W33">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.267893152513626</v>
+        <v>3.406642199401022</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08427343381753451</v>
+        <v>0.08352896930035769</v>
       </c>
       <c r="C34">
-        <v>51327.16238713801</v>
+        <v>52741.3184392033</v>
       </c>
       <c r="D34">
-        <v>73357.55693129326</v>
+        <v>74771.71298335855</v>
       </c>
       <c r="E34">
         <v>9580.861593670092</v>
@@ -4081,37 +4081,37 @@
         <v>5054</v>
       </c>
       <c r="M34">
-        <v>1596.451295860648</v>
+        <v>1531.429470045844</v>
       </c>
       <c r="N34">
-        <v>3457.548704139352</v>
+        <v>3522.570529954156</v>
       </c>
       <c r="O34">
-        <v>432.193588017419</v>
+        <v>440.3213162442694</v>
       </c>
       <c r="P34">
-        <v>3025.355116121933</v>
+        <v>3082.249213709886</v>
       </c>
       <c r="Q34">
-        <v>4759.355116121933</v>
+        <v>4816.249213709886</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09764585463533085</v>
+        <v>0.09762164211007079</v>
       </c>
       <c r="T34">
         <v>1.010100260297016</v>
       </c>
       <c r="U34">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V34">
         <v>0.125</v>
       </c>
       <c r="W34">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.165771491497575</v>
+        <v>3.300184630669739</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08432809902954</v>
+        <v>0.08356090595053654</v>
       </c>
       <c r="C35">
-        <v>50441.56741398184</v>
+        <v>51896.56721273047</v>
       </c>
       <c r="D35">
-        <v>73253.47428764195</v>
+        <v>74708.47408639058</v>
       </c>
       <c r="E35">
         <v>10362.37392317495</v>
@@ -4163,37 +4163,37 @@
         <v>5054</v>
       </c>
       <c r="M35">
-        <v>1646.340398856293</v>
+        <v>1579.286640984777</v>
       </c>
       <c r="N35">
-        <v>3407.659601143707</v>
+        <v>3474.713359015223</v>
       </c>
       <c r="O35">
-        <v>425.9574501429634</v>
+        <v>434.3391698769028</v>
       </c>
       <c r="P35">
-        <v>2981.702151000743</v>
+        <v>3040.37418913832</v>
       </c>
       <c r="Q35">
-        <v>4715.702151000743</v>
+        <v>4774.37418913832</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09835115816154222</v>
+        <v>0.09832661625258185</v>
       </c>
       <c r="T35">
         <v>1.023841518502238</v>
       </c>
       <c r="U35">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V35">
         <v>0.125</v>
       </c>
       <c r="W35">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.069839022058254</v>
+        <v>3.200179035800959</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08515626424154546</v>
+        <v>0.08359284260071544</v>
       </c>
       <c r="C36">
-        <v>48118.5983371793</v>
+        <v>51051.92286567659</v>
       </c>
       <c r="D36">
-        <v>71712.01754034426</v>
+        <v>74645.34206884155</v>
       </c>
       <c r="E36">
         <v>11143.8862526798</v>
@@ -4245,45 +4245,45 @@
         <v>5054</v>
       </c>
       <c r="M36">
-        <v>1765.315191780167</v>
+        <v>1627.14381192371</v>
       </c>
       <c r="N36">
-        <v>3288.684808219833</v>
+        <v>3426.85618807629</v>
       </c>
       <c r="O36">
-        <v>411.0856010274791</v>
+        <v>428.3570235095362</v>
       </c>
       <c r="P36">
-        <v>2877.599207192354</v>
+        <v>2998.499164566754</v>
       </c>
       <c r="Q36">
-        <v>4611.599207192354</v>
+        <v>4732.499164566754</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09907783452188118</v>
+        <v>0.09905295324789629</v>
       </c>
       <c r="T36">
         <v>1.037999178471255</v>
       </c>
       <c r="U36">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V36">
         <v>0.125</v>
       </c>
       <c r="W36">
-        <v>0.05813203957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.862944829078075</v>
+        <v>3.106056122983284</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08523367945355095</v>
+        <v>0.08362477925089432</v>
       </c>
       <c r="C37">
-        <v>47196.3027706507</v>
+        <v>50207.38512731681</v>
       </c>
       <c r="D37">
-        <v>71571.23430332051</v>
+        <v>74582.31665998662</v>
       </c>
       <c r="E37">
         <v>11925.39858218465</v>
@@ -4327,45 +4327,45 @@
         <v>5054</v>
       </c>
       <c r="M37">
-        <v>1817.236226832525</v>
+        <v>1675.000982862643</v>
       </c>
       <c r="N37">
-        <v>3236.763773167475</v>
+        <v>3378.999017137357</v>
       </c>
       <c r="O37">
-        <v>404.5954716459344</v>
+        <v>422.3748771421697</v>
       </c>
       <c r="P37">
-        <v>2832.16830152154</v>
+        <v>2956.624139995188</v>
       </c>
       <c r="Q37">
-        <v>4566.16830152154</v>
+        <v>4690.624139995188</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09982687015484598</v>
+        <v>0.09980163907383578</v>
       </c>
       <c r="T37">
         <v>1.052592458747011</v>
       </c>
       <c r="U37">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.05813203957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.78114640539013</v>
+        <v>3.017311662326619</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08531109466555642</v>
+        <v>0.08444421590107321</v>
       </c>
       <c r="C38">
-        <v>46274.5588853263</v>
+        <v>47844.38169231527</v>
       </c>
       <c r="D38">
-        <v>71431.00274750096</v>
+        <v>73000.82555448993</v>
       </c>
       <c r="E38">
         <v>12706.9109116895</v>
@@ -4409,37 +4409,37 @@
         <v>5054</v>
       </c>
       <c r="M38">
-        <v>1869.157261884883</v>
+        <v>1793.194263457011</v>
       </c>
       <c r="N38">
-        <v>3184.842738115117</v>
+        <v>3260.805736542989</v>
       </c>
       <c r="O38">
-        <v>398.1053422643896</v>
+        <v>407.6007170678736</v>
       </c>
       <c r="P38">
-        <v>2786.737395850727</v>
+        <v>2853.205019475115</v>
       </c>
       <c r="Q38">
-        <v>4520.737395850727</v>
+        <v>4587.205019475115</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1005993131513409</v>
+        <v>0.1005737213318359</v>
       </c>
       <c r="T38">
         <v>1.067641779031384</v>
       </c>
       <c r="U38">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V38">
         <v>0.125</v>
       </c>
       <c r="W38">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.703892338573738</v>
+        <v>2.818434178044179</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08538850987756189</v>
+        <v>0.08449802755125208</v>
       </c>
       <c r="C39">
-        <v>45353.36344477323</v>
+        <v>46961.35786116337</v>
       </c>
       <c r="D39">
-        <v>71291.31963645274</v>
+        <v>72899.31405284288</v>
       </c>
       <c r="E39">
         <v>13488.42324119435</v>
@@ -4491,37 +4491,37 @@
         <v>5054</v>
       </c>
       <c r="M39">
-        <v>1921.078296937241</v>
+        <v>1843.005215219706</v>
       </c>
       <c r="N39">
-        <v>3132.92170306276</v>
+        <v>3210.994784780294</v>
       </c>
       <c r="O39">
-        <v>391.615212882845</v>
+        <v>401.3743480975368</v>
       </c>
       <c r="P39">
-        <v>2741.306490179915</v>
+        <v>2809.620436682757</v>
       </c>
       <c r="Q39">
-        <v>4475.306490179915</v>
+        <v>4543.620436682757</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1013962781477246</v>
+        <v>0.101370314137709</v>
       </c>
       <c r="T39">
         <v>1.083168855515261</v>
       </c>
       <c r="U39">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V39">
         <v>0.125</v>
       </c>
       <c r="W39">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.630814167260934</v>
+        <v>2.742260281340283</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08546592508956738</v>
+        <v>0.08455183920143096</v>
       </c>
       <c r="C40">
-        <v>44432.71323782457</v>
+        <v>46078.61595218742</v>
       </c>
       <c r="D40">
-        <v>71152.18175900893</v>
+        <v>72798.08447337178</v>
       </c>
       <c r="E40">
         <v>14269.9355706992</v>
@@ -4573,37 +4573,37 @@
         <v>5054</v>
       </c>
       <c r="M40">
-        <v>1972.999331989599</v>
+        <v>1892.816166982401</v>
       </c>
       <c r="N40">
-        <v>3081.000668010402</v>
+        <v>3161.183833017599</v>
       </c>
       <c r="O40">
-        <v>385.1250835013002</v>
+        <v>395.1479791271998</v>
       </c>
       <c r="P40">
-        <v>2695.875584509101</v>
+        <v>2766.035853890399</v>
       </c>
       <c r="Q40">
-        <v>4429.875584509102</v>
+        <v>4500.035853890398</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1022189516923787</v>
+        <v>0.1021926034857071</v>
       </c>
       <c r="T40">
         <v>1.099196805434101</v>
       </c>
       <c r="U40">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V40">
         <v>0.125</v>
       </c>
       <c r="W40">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.561582215490909</v>
+        <v>2.670095537094486</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08646471530157283</v>
+        <v>0.08460565085160984</v>
       </c>
       <c r="C41">
-        <v>41903.58993461194</v>
+        <v>45196.1547925662</v>
       </c>
       <c r="D41">
-        <v>69404.57078530116</v>
+        <v>72697.13564325542</v>
       </c>
       <c r="E41">
         <v>15051.44790020405</v>
@@ -4655,45 +4655,45 @@
         <v>5054</v>
       </c>
       <c r="M41">
-        <v>2107.213615338817</v>
+        <v>1942.627118745096</v>
       </c>
       <c r="N41">
-        <v>2946.786384661183</v>
+        <v>3111.372881254904</v>
       </c>
       <c r="O41">
-        <v>368.3482980826478</v>
+        <v>388.921610156863</v>
       </c>
       <c r="P41">
-        <v>2578.438086578535</v>
+        <v>2722.451271098041</v>
       </c>
       <c r="Q41">
-        <v>4312.438086578535</v>
+        <v>4456.451271098042</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1030685981401362</v>
+        <v>0.1030418531401969</v>
       </c>
       <c r="T41">
         <v>1.115750261907658</v>
       </c>
       <c r="U41">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V41">
         <v>0.125</v>
       </c>
       <c r="W41">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.39842793498056</v>
+        <v>2.601631548963858</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08656575551357831</v>
+        <v>0.08465946250178873</v>
       </c>
       <c r="C42">
-        <v>40950.05448280876</v>
+        <v>44313.97321597484</v>
       </c>
       <c r="D42">
-        <v>69232.54766300283</v>
+        <v>72596.46639616891</v>
       </c>
       <c r="E42">
         <v>15832.96022970891</v>
@@ -4737,45 +4737,45 @@
         <v>5054</v>
       </c>
       <c r="M42">
-        <v>2161.244733680839</v>
+        <v>1992.438070507791</v>
       </c>
       <c r="N42">
-        <v>2892.755266319161</v>
+        <v>3061.561929492209</v>
       </c>
       <c r="O42">
-        <v>361.5944082898952</v>
+        <v>382.6952411865262</v>
       </c>
       <c r="P42">
-        <v>2531.160858029266</v>
+        <v>2678.866688305683</v>
       </c>
       <c r="Q42">
-        <v>4265.160858029267</v>
+        <v>4412.866688305683</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1039465661361523</v>
+        <v>0.103919411116503</v>
       </c>
       <c r="T42">
         <v>1.132855500263667</v>
       </c>
       <c r="U42">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V42">
         <v>0.125</v>
       </c>
       <c r="W42">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.338467236606045</v>
+        <v>2.536590760239761</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08666679572558379</v>
+        <v>0.08596889915196762</v>
       </c>
       <c r="C43">
-        <v>39997.36966059072</v>
+        <v>41165.94161958668</v>
       </c>
       <c r="D43">
-        <v>69061.37517028964</v>
+        <v>70229.9471292856</v>
       </c>
       <c r="E43">
         <v>16614.47255921376</v>
@@ -4819,37 +4819,37 @@
         <v>5054</v>
       </c>
       <c r="M43">
-        <v>2215.275852022859</v>
+        <v>2154.396041554432</v>
       </c>
       <c r="N43">
-        <v>2838.724147977141</v>
+        <v>2899.603958445568</v>
       </c>
       <c r="O43">
-        <v>354.8405184971426</v>
+        <v>362.4504948056961</v>
       </c>
       <c r="P43">
-        <v>2483.883629479998</v>
+        <v>2537.153463639872</v>
       </c>
       <c r="Q43">
-        <v>4217.883629479998</v>
+        <v>4271.153463639872</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.104854295759152</v>
+        <v>0.1048267168208195</v>
       </c>
       <c r="T43">
         <v>1.150540577208015</v>
       </c>
       <c r="U43">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V43">
         <v>0.125</v>
       </c>
       <c r="W43">
-        <v>0.06049453957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.281431450347362</v>
+        <v>2.345901079707451</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08849508593758927</v>
+        <v>0.0860533358021465</v>
       </c>
       <c r="C44">
-        <v>36258.509114571</v>
+        <v>40237.11276687531</v>
       </c>
       <c r="D44">
-        <v>66104.02695377477</v>
+        <v>70082.63060607908</v>
       </c>
       <c r="E44">
         <v>17395.98488871861</v>
@@ -4901,45 +4901,45 @@
         <v>5054</v>
       </c>
       <c r="M44">
-        <v>2423.577504209139</v>
+        <v>2206.942286470393</v>
       </c>
       <c r="N44">
-        <v>2630.422495790861</v>
+        <v>2847.057713529607</v>
       </c>
       <c r="O44">
-        <v>328.8028119738577</v>
+        <v>355.8822141912008</v>
       </c>
       <c r="P44">
-        <v>2301.619683817004</v>
+        <v>2491.175499338406</v>
       </c>
       <c r="Q44">
-        <v>4035.619683817004</v>
+        <v>4225.175499338406</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1057933264036345</v>
+        <v>0.1057653089287331</v>
       </c>
       <c r="T44">
         <v>1.168835484391823</v>
       </c>
       <c r="U44">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V44">
         <v>0.125</v>
       </c>
       <c r="W44">
-        <v>0.06460703957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.085346967952329</v>
+        <v>2.290046292095369</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08863725114959475</v>
+        <v>0.08719127245232539</v>
       </c>
       <c r="C45">
-        <v>35257.61545797114</v>
+        <v>37528.87557044443</v>
       </c>
       <c r="D45">
-        <v>65884.64562667976</v>
+        <v>68155.90573915305</v>
       </c>
       <c r="E45">
         <v>18177.49721822346</v>
@@ -4983,37 +4983,37 @@
         <v>5054</v>
       </c>
       <c r="M45">
-        <v>2481.281730499832</v>
+        <v>2353.582615858739</v>
       </c>
       <c r="N45">
-        <v>2572.718269500168</v>
+        <v>2700.417384141261</v>
       </c>
       <c r="O45">
-        <v>321.589783687521</v>
+        <v>337.5521730176577</v>
       </c>
       <c r="P45">
-        <v>2251.128485812647</v>
+        <v>2362.865211123603</v>
       </c>
       <c r="Q45">
-        <v>3985.128485812647</v>
+        <v>4096.865211123603</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.106765305491783</v>
+        <v>0.1067368340930648</v>
       </c>
       <c r="T45">
         <v>1.187772318143485</v>
       </c>
       <c r="U45">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V45">
         <v>0.125</v>
       </c>
       <c r="W45">
-        <v>0.06460703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.036850526837159</v>
+        <v>2.147364603199185</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.09235991636160021</v>
+        <v>0.08730020910250426</v>
       </c>
       <c r="C46">
-        <v>29208.34284352668</v>
+        <v>36568.45628548806</v>
       </c>
       <c r="D46">
-        <v>60616.88534174015</v>
+        <v>67976.99878370154</v>
       </c>
       <c r="E46">
         <v>18959.00954772831</v>
@@ -5065,45 +5065,45 @@
         <v>5054</v>
       </c>
       <c r="M46">
-        <v>2858.780802023911</v>
+        <v>2408.317095297314</v>
       </c>
       <c r="N46">
-        <v>2195.219197976089</v>
+        <v>2645.682904702686</v>
       </c>
       <c r="O46">
-        <v>274.4023997470111</v>
+        <v>330.7103630878357</v>
       </c>
       <c r="P46">
-        <v>1920.816798229078</v>
+        <v>2314.97254161485</v>
       </c>
       <c r="Q46">
-        <v>3654.816798229078</v>
+        <v>4048.97254161485</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1077719981187939</v>
+        <v>0.107743056584694</v>
       </c>
       <c r="T46">
         <v>1.207385467386277</v>
       </c>
       <c r="U46">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V46">
         <v>0.125</v>
       </c>
       <c r="W46">
-        <v>0.07274453957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.767886504772229</v>
+        <v>2.098560862217385</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.09443408157360569</v>
+        <v>0.08740914575268313</v>
       </c>
       <c r="C47">
-        <v>25841.61802993952</v>
+        <v>35608.97379094484</v>
       </c>
       <c r="D47">
-        <v>58031.67285765785</v>
+        <v>67799.02861866317</v>
       </c>
       <c r="E47">
         <v>19740.52187723316</v>
@@ -5147,45 +5147,45 @@
         <v>5054</v>
       </c>
       <c r="M47">
-        <v>3089.042950669276</v>
+        <v>2463.05157473589</v>
       </c>
       <c r="N47">
-        <v>1964.957049330724</v>
+        <v>2590.94842526411</v>
       </c>
       <c r="O47">
-        <v>245.6196311663405</v>
+        <v>323.8685531580138</v>
       </c>
       <c r="P47">
-        <v>1719.337418164384</v>
+        <v>2267.079872106096</v>
       </c>
       <c r="Q47">
-        <v>3453.337418164384</v>
+        <v>4001.079872106096</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1088152977504234</v>
+        <v>0.1087858689851097</v>
       </c>
       <c r="T47">
         <v>1.227711822056079</v>
       </c>
       <c r="U47">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V47">
         <v>0.125</v>
       </c>
       <c r="W47">
-        <v>0.07685703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.636105447774688</v>
+        <v>2.051926176390332</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09469874678561116</v>
+        <v>0.08751808240286202</v>
       </c>
       <c r="C48">
-        <v>24746.00838691367</v>
+        <v>34650.42074821219</v>
       </c>
       <c r="D48">
-        <v>57717.57554413685</v>
+        <v>67621.98790543537</v>
       </c>
       <c r="E48">
         <v>20522.03420673802</v>
@@ -5229,45 +5229,45 @@
         <v>5054</v>
       </c>
       <c r="M48">
-        <v>3157.688349573038</v>
+        <v>2517.786054174465</v>
       </c>
       <c r="N48">
-        <v>1896.311650426962</v>
+        <v>2536.213945825535</v>
       </c>
       <c r="O48">
-        <v>237.0389563033702</v>
+        <v>317.0267432281918</v>
       </c>
       <c r="P48">
-        <v>1659.272694123592</v>
+        <v>2219.187202597343</v>
       </c>
       <c r="Q48">
-        <v>3393.272694123591</v>
+        <v>3953.187202597343</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1098972381091503</v>
+        <v>0.1098673040670223</v>
       </c>
       <c r="T48">
         <v>1.248791004676615</v>
       </c>
       <c r="U48">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V48">
         <v>0.125</v>
       </c>
       <c r="W48">
-        <v>0.07685703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.600537938040456</v>
+        <v>2.007319085599238</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.09496341199761663</v>
+        <v>0.09083476905304091</v>
       </c>
       <c r="C49">
-        <v>23653.78055278577</v>
+        <v>28888.73533776264</v>
       </c>
       <c r="D49">
-        <v>57406.8600395138</v>
+        <v>62641.81482449066</v>
       </c>
       <c r="E49">
         <v>21303.54653624287</v>
@@ -5311,45 +5311,45 @@
         <v>5054</v>
       </c>
       <c r="M49">
-        <v>3226.333748476799</v>
+        <v>2859.022953609519</v>
       </c>
       <c r="N49">
-        <v>1827.666251523201</v>
+        <v>2194.977046390481</v>
       </c>
       <c r="O49">
-        <v>228.4582814404001</v>
+        <v>274.3721307988101</v>
       </c>
       <c r="P49">
-        <v>1599.207970082801</v>
+        <v>1920.604915591671</v>
       </c>
       <c r="Q49">
-        <v>3333.207970082801</v>
+        <v>3654.604915591671</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1110200064059424</v>
+        <v>0.1109895480199505</v>
       </c>
       <c r="T49">
         <v>1.270665628150757</v>
       </c>
       <c r="U49">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V49">
         <v>0.125</v>
       </c>
       <c r="W49">
-        <v>0.07685703957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.566483939358744</v>
+        <v>1.767736769520972</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09522807720962211</v>
+        <v>0.09264995570321977</v>
       </c>
       <c r="C50">
-        <v>22564.88020334052</v>
+        <v>25680.18579326684</v>
       </c>
       <c r="D50">
-        <v>57099.4720195734</v>
+        <v>60214.77760949972</v>
       </c>
       <c r="E50">
         <v>22085.05886574772</v>
@@ -5393,37 +5393,37 @@
         <v>5054</v>
       </c>
       <c r="M50">
-        <v>3294.979147380561</v>
+        <v>3066.152337301541</v>
       </c>
       <c r="N50">
-        <v>1759.020852619439</v>
+        <v>1987.847662698459</v>
       </c>
       <c r="O50">
-        <v>219.8776065774298</v>
+        <v>248.4809578373074</v>
       </c>
       <c r="P50">
-        <v>1539.143246042009</v>
+        <v>1739.366704861152</v>
       </c>
       <c r="Q50">
-        <v>3273.143246042009</v>
+        <v>3473.366704861152</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.112185958098765</v>
+        <v>0.1121549552018374</v>
       </c>
       <c r="T50">
         <v>1.29338158329698</v>
       </c>
       <c r="U50">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V50">
         <v>0.125</v>
       </c>
       <c r="W50">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.53384885728877</v>
+        <v>1.648319928046342</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09549274242162759</v>
+        <v>0.09286126735339867</v>
       </c>
       <c r="C51">
-        <v>21479.25417169304</v>
+        <v>24628.30071909555</v>
       </c>
       <c r="D51">
-        <v>56795.35831743077</v>
+        <v>59944.40486483328</v>
       </c>
       <c r="E51">
         <v>22866.57119525257</v>
@@ -5475,37 +5475,37 @@
         <v>5054</v>
       </c>
       <c r="M51">
-        <v>3363.624546284322</v>
+        <v>3130.030510995322</v>
       </c>
       <c r="N51">
-        <v>1690.375453715678</v>
+        <v>1923.969489004678</v>
       </c>
       <c r="O51">
-        <v>211.2969317144597</v>
+        <v>240.4961861255847</v>
       </c>
       <c r="P51">
-        <v>1479.078522001218</v>
+        <v>1683.473302879093</v>
       </c>
       <c r="Q51">
-        <v>3213.078522001218</v>
+        <v>3417.473302879093</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1133976333873845</v>
+        <v>0.1133660646261513</v>
       </c>
       <c r="T51">
         <v>1.316988360213644</v>
       </c>
       <c r="U51">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V51">
         <v>0.125</v>
       </c>
       <c r="W51">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.502545819384918</v>
+        <v>1.614680745841315</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1177892739547476</v>
+        <v>0.09307257900357754</v>
       </c>
       <c r="C52">
-        <v>3107.07273146115</v>
+        <v>23578.83281411809</v>
       </c>
       <c r="D52">
-        <v>39204.68920670373</v>
+        <v>59676.44928936067</v>
       </c>
       <c r="E52">
         <v>23648.08352475742</v>
@@ -5557,45 +5557,45 @@
         <v>5054</v>
       </c>
       <c r="M52">
-        <v>5346.975152474972</v>
+        <v>3193.908684689105</v>
       </c>
       <c r="N52">
-        <v>-292.9751524749718</v>
+        <v>1860.091315310895</v>
       </c>
       <c r="O52">
-        <v>-36.62189405937147</v>
+        <v>232.5114144138619</v>
       </c>
       <c r="P52">
-        <v>-256.3532584156003</v>
+        <v>1627.579900897033</v>
       </c>
       <c r="Q52">
-        <v>1477.6467415844</v>
+        <v>3361.579900897033</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1149093025384738</v>
+        <v>0.1146256184274378</v>
       </c>
       <c r="T52">
-        <v>1.346439845076578</v>
+        <v>1.341539408206974</v>
       </c>
       <c r="U52">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V52">
-        <v>0.118150913738131</v>
+        <v>0.125</v>
       </c>
       <c r="W52">
-        <v>0.1206692453710213</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.9452073099050476</v>
+        <v>1.582387130924489</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1186996401213729</v>
+        <v>0.09328389065375643</v>
       </c>
       <c r="C53">
-        <v>1835.974684284396</v>
+        <v>22531.74980785248</v>
       </c>
       <c r="D53">
-        <v>38715.10348903183</v>
+        <v>59410.87861259992</v>
       </c>
       <c r="E53">
         <v>24429.59585426228</v>
@@ -5639,45 +5639,45 @@
         <v>5054</v>
       </c>
       <c r="M53">
-        <v>5453.914655524472</v>
+        <v>3257.786858382887</v>
       </c>
       <c r="N53">
-        <v>-399.9146555244715</v>
+        <v>1796.213141617113</v>
       </c>
       <c r="O53">
-        <v>-49.98933194055894</v>
+        <v>224.5266427021391</v>
       </c>
       <c r="P53">
-        <v>-349.9253235839126</v>
+        <v>1571.686498914974</v>
       </c>
       <c r="Q53">
-        <v>1384.074676416087</v>
+        <v>3305.686498914974</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1163196964678304</v>
+        <v>0.1159365825879604</v>
       </c>
       <c r="T53">
-        <v>1.373918209261814</v>
+        <v>1.367092539791869</v>
       </c>
       <c r="U53">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V53">
-        <v>0.1158342291550303</v>
+        <v>0.125</v>
       </c>
       <c r="W53">
-        <v>0.1209862526512471</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.9266738332402428</v>
+        <v>1.55135993227891</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1196100062879983</v>
+        <v>0.09349520230393532</v>
       </c>
       <c r="C54">
-        <v>576.9536520124457</v>
+        <v>21487.0200017091</v>
       </c>
       <c r="D54">
-        <v>38237.59478626473</v>
+        <v>59147.66113596139</v>
       </c>
       <c r="E54">
         <v>25211.10818376712</v>
@@ -5721,45 +5721,45 @@
         <v>5054</v>
       </c>
       <c r="M54">
-        <v>5560.85415857397</v>
+        <v>3321.665032076669</v>
       </c>
       <c r="N54">
-        <v>-506.8541585739704</v>
+        <v>1732.334967923331</v>
       </c>
       <c r="O54">
-        <v>-63.3567698217463</v>
+        <v>216.5418709904164</v>
       </c>
       <c r="P54">
-        <v>-443.4973887522241</v>
+        <v>1515.793096932915</v>
       </c>
       <c r="Q54">
-        <v>1290.502611247776</v>
+        <v>3249.793096932915</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1177888568109103</v>
+        <v>0.1173021702551715</v>
       </c>
       <c r="T54">
-        <v>1.402541505288102</v>
+        <v>1.393710385192801</v>
       </c>
       <c r="U54">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V54">
-        <v>0.1136066478251259</v>
+        <v>0.125</v>
       </c>
       <c r="W54">
-        <v>0.1212910673437718</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.9088531826010073</v>
+        <v>1.521526087427393</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1205203724546236</v>
+        <v>0.1002917639541142</v>
       </c>
       <c r="C55">
-        <v>-670.4317913835766</v>
+        <v>13328.23271900282</v>
       </c>
       <c r="D55">
-        <v>37771.72167237356</v>
+        <v>51770.38618275996</v>
       </c>
       <c r="E55">
         <v>25992.62051327198</v>
@@ -5803,45 +5803,45 @@
         <v>5054</v>
       </c>
       <c r="M55">
-        <v>5667.79366162347</v>
+        <v>3973.709384955803</v>
       </c>
       <c r="N55">
-        <v>-613.7936616234701</v>
+        <v>1080.290615044197</v>
       </c>
       <c r="O55">
-        <v>-76.72420770293377</v>
+        <v>135.0363268805247</v>
       </c>
       <c r="P55">
-        <v>-537.0694539205364</v>
+        <v>945.2542881636725</v>
       </c>
       <c r="Q55">
-        <v>1196.930546079464</v>
+        <v>2679.254288163673</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1193205346153977</v>
+        <v>0.1187258680358809</v>
       </c>
       <c r="T55">
-        <v>1.432382813911253</v>
+        <v>1.421460904866113</v>
       </c>
       <c r="U55">
-        <v>0.1368366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V55">
-        <v>0.1114631261680481</v>
+        <v>0.125</v>
       </c>
       <c r="W55">
-        <v>0.1215843795950692</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.8917050093443846</v>
+        <v>1.271859492074107</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.121430738621249</v>
+        <v>0.114558428619496</v>
       </c>
       <c r="C56">
-        <v>-1906.601818176307</v>
+        <v>1804.899290675923</v>
       </c>
       <c r="D56">
-        <v>37317.06397508569</v>
+        <v>41028.56508393792</v>
       </c>
       <c r="E56">
         <v>26774.13284277683</v>
@@ -5885,37 +5885,37 @@
         <v>5054</v>
       </c>
       <c r="M56">
-        <v>5774.73316467297</v>
+        <v>5255.652675415847</v>
       </c>
       <c r="N56">
-        <v>-720.7331646729699</v>
+        <v>-201.6526754158467</v>
       </c>
       <c r="O56">
-        <v>-90.09164558412124</v>
+        <v>-25.20658442698084</v>
       </c>
       <c r="P56">
-        <v>-630.6415190888487</v>
+        <v>-176.4460909888659</v>
       </c>
       <c r="Q56">
-        <v>1103.358480911151</v>
+        <v>1557.553909011134</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1209188071070368</v>
+        <v>0.1204181331901826</v>
       </c>
       <c r="T56">
-        <v>1.463521570735411</v>
+        <v>1.454446302534929</v>
       </c>
       <c r="U56">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V56">
-        <v>0.1093989942019731</v>
+        <v>0.1202039097741583</v>
       </c>
       <c r="W56">
-        <v>0.1218668284296519</v>
+        <v>0.1095668284296519</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8751919536157848</v>
+        <v>0.9616312781932662</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1223411047878743</v>
+        <v>0.1153457947861214</v>
       </c>
       <c r="C57">
-        <v>-3131.956610823843</v>
+        <v>558.8800256816176</v>
       </c>
       <c r="D57">
-        <v>36873.221511943</v>
+        <v>40564.05814844846</v>
       </c>
       <c r="E57">
         <v>27555.64517228169</v>
@@ -5967,37 +5967,37 @@
         <v>5054</v>
       </c>
       <c r="M57">
-        <v>5881.67266772247</v>
+        <v>5352.979576812437</v>
       </c>
       <c r="N57">
-        <v>-827.6726677224697</v>
+        <v>-298.9795768124368</v>
       </c>
       <c r="O57">
-        <v>-103.4590834653087</v>
+        <v>-37.3724471015546</v>
       </c>
       <c r="P57">
-        <v>-724.213584257161</v>
+        <v>-261.6071297108822</v>
       </c>
       <c r="Q57">
-        <v>1009.786415742839</v>
+        <v>1472.392870289118</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1225881139316376</v>
+        <v>0.1220763139277422</v>
       </c>
       <c r="T57">
-        <v>1.496044272307308</v>
+        <v>1.48676733148015</v>
       </c>
       <c r="U57">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V57">
-        <v>0.107409921580119</v>
+        <v>0.1180183841419008</v>
       </c>
       <c r="W57">
-        <v>0.1221390063975225</v>
+        <v>0.1098390063975225</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8592793726409523</v>
+        <v>0.9441470731352067</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1232514709544996</v>
+        <v>0.1161331609527467</v>
       </c>
       <c r="C58">
-        <v>-4346.877536773209</v>
+        <v>-676.7391082731192</v>
       </c>
       <c r="D58">
-        <v>36439.81291549849</v>
+        <v>40109.95134399857</v>
       </c>
       <c r="E58">
         <v>28337.15750178653</v>
@@ -6049,37 +6049,37 @@
         <v>5054</v>
       </c>
       <c r="M58">
-        <v>5988.612170771969</v>
+        <v>5450.306478209026</v>
       </c>
       <c r="N58">
-        <v>-934.6121707719685</v>
+        <v>-396.306478209026</v>
       </c>
       <c r="O58">
-        <v>-116.8265213464961</v>
+        <v>-49.53830977612824</v>
       </c>
       <c r="P58">
-        <v>-817.7856494254725</v>
+        <v>-346.7681684328977</v>
       </c>
       <c r="Q58">
-        <v>916.2143505745275</v>
+        <v>1387.231831567102</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1243332983391748</v>
+        <v>0.1238098665170091</v>
       </c>
       <c r="T58">
-        <v>1.530045278496111</v>
+        <v>1.520557498104699</v>
       </c>
       <c r="U58">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V58">
-        <v>0.1054918872661884</v>
+        <v>0.1159109129965098</v>
       </c>
       <c r="W58">
-        <v>0.1224014637236834</v>
+        <v>0.1101014637236834</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8439350981295068</v>
+        <v>0.9272873039720781</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.124161837121125</v>
+        <v>0.116920527119372</v>
       </c>
       <c r="C59">
-        <v>-5551.728241374483</v>
+        <v>-1902.303526709278</v>
       </c>
       <c r="D59">
-        <v>36016.47454040207</v>
+        <v>39665.89925506727</v>
       </c>
       <c r="E59">
         <v>29118.66983129139</v>
@@ -6131,37 +6131,37 @@
         <v>5054</v>
       </c>
       <c r="M59">
-        <v>6095.551673821468</v>
+        <v>5547.633379605616</v>
       </c>
       <c r="N59">
-        <v>-1041.551673821468</v>
+        <v>-493.633379605616</v>
       </c>
       <c r="O59">
-        <v>-130.1939592276835</v>
+        <v>-61.704172450702</v>
       </c>
       <c r="P59">
-        <v>-911.3577145937847</v>
+        <v>-431.929207154914</v>
       </c>
       <c r="Q59">
-        <v>822.6422854062153</v>
+        <v>1302.070792845086</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1261596541145045</v>
+        <v>0.1256240494592651</v>
       </c>
       <c r="T59">
-        <v>1.56562772683323</v>
+        <v>1.555919300386203</v>
       </c>
       <c r="U59">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V59">
-        <v>0.1036411524018692</v>
+        <v>0.1138773882070973</v>
       </c>
       <c r="W59">
-        <v>0.1226547120208562</v>
+        <v>0.1103547120208562</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.829129219214954</v>
+        <v>0.9110191056567785</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1250722032877503</v>
+        <v>0.1177078932859974</v>
       </c>
       <c r="C60">
-        <v>-6746.855665488059</v>
+        <v>-3118.143516433462</v>
       </c>
       <c r="D60">
-        <v>35602.85944579334</v>
+        <v>39231.57159484793</v>
       </c>
       <c r="E60">
         <v>29900.18216079623</v>
@@ -6213,37 +6213,37 @@
         <v>5054</v>
       </c>
       <c r="M60">
-        <v>6202.491176870967</v>
+        <v>5644.960281002205</v>
       </c>
       <c r="N60">
-        <v>-1148.491176870967</v>
+        <v>-590.9602810022052</v>
       </c>
       <c r="O60">
-        <v>-143.5613971088709</v>
+        <v>-73.87003512527565</v>
       </c>
       <c r="P60">
-        <v>-1004.929779762096</v>
+        <v>-517.0902458769295</v>
       </c>
       <c r="Q60">
-        <v>729.0702202379038</v>
+        <v>1216.90975412307</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1280729792124688</v>
+        <v>0.127524622065438</v>
       </c>
       <c r="T60">
-        <v>1.602904577472116</v>
+        <v>1.592964998014446</v>
       </c>
       <c r="U60">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V60">
-        <v>0.1018542359811474</v>
+        <v>0.1119139849621474</v>
       </c>
       <c r="W60">
-        <v>0.1228992276181265</v>
+        <v>0.1105992276181266</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.814833887849179</v>
+        <v>0.895311879697179</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1259825694543757</v>
+        <v>0.1184952594526227</v>
       </c>
       <c r="C61">
-        <v>-7932.590993770842</v>
+        <v>-4324.575054837405</v>
       </c>
       <c r="D61">
-        <v>35198.6364470154</v>
+        <v>38806.65238594884</v>
       </c>
       <c r="E61">
         <v>30681.69449030108</v>
@@ -6295,37 +6295,37 @@
         <v>5054</v>
       </c>
       <c r="M61">
-        <v>6309.430679920465</v>
+        <v>5742.287182398794</v>
       </c>
       <c r="N61">
-        <v>-1255.430679920465</v>
+        <v>-688.2871823987944</v>
       </c>
       <c r="O61">
-        <v>-156.9288349900581</v>
+        <v>-86.03589779984929</v>
       </c>
       <c r="P61">
-        <v>-1098.501844930407</v>
+        <v>-602.2512845989451</v>
       </c>
       <c r="Q61">
-        <v>635.4981550695929</v>
+        <v>1131.748715401055</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1300796372420412</v>
+        <v>0.1295179055304487</v>
       </c>
       <c r="T61">
-        <v>1.641999811068997</v>
+        <v>1.631817802844066</v>
       </c>
       <c r="U61">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V61">
-        <v>0.1001278929984161</v>
+        <v>0.1100171377593991</v>
       </c>
       <c r="W61">
-        <v>0.1231354545510826</v>
+        <v>0.1108354545510826</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8010231439873288</v>
+        <v>0.880137102075193</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1786636066808662</v>
+        <v>0.119282625619248</v>
       </c>
       <c r="C62">
-        <v>-22670.52617909122</v>
+        <v>-5521.900576524698</v>
       </c>
       <c r="D62">
-        <v>21242.21359119987</v>
+        <v>38390.8391937664</v>
       </c>
       <c r="E62">
         <v>31463.20681980594</v>
@@ -6377,45 +6377,45 @@
         <v>5054</v>
       </c>
       <c r="M62">
-        <v>10397.39398946768</v>
+        <v>5839.614083795384</v>
       </c>
       <c r="N62">
-        <v>-5343.393989467679</v>
+        <v>-785.6140837953844</v>
       </c>
       <c r="O62">
-        <v>-667.9242486834598</v>
+        <v>-98.20176047442305</v>
       </c>
       <c r="P62">
-        <v>-4675.469740784219</v>
+        <v>-687.4123233209614</v>
       </c>
       <c r="Q62">
-        <v>-2941.469740784219</v>
+        <v>1046.587676679039</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1342633058227553</v>
+        <v>0.1316108531687099</v>
       </c>
       <c r="T62">
-        <v>1.723509215284622</v>
+        <v>1.672613247915168</v>
       </c>
       <c r="U62">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V62">
-        <v>0.06076041752769475</v>
+        <v>0.1081835187967425</v>
       </c>
       <c r="W62">
-        <v>0.2082638072529401</v>
+        <v>0.1110638072529401</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.486083340221558</v>
+        <v>0.8654681503739398</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1804229728474916</v>
+        <v>0.1200699917858734</v>
       </c>
       <c r="C63">
-        <v>-23729.64961096658</v>
+        <v>-6710.409691173612</v>
       </c>
       <c r="D63">
-        <v>20964.60248882937</v>
+        <v>37983.84240862234</v>
       </c>
       <c r="E63">
         <v>32244.71914931079</v>
@@ -6459,45 +6459,45 @@
         <v>5054</v>
       </c>
       <c r="M63">
-        <v>10570.68388929214</v>
+        <v>5936.940985191975</v>
       </c>
       <c r="N63">
-        <v>-5516.683889292142</v>
+        <v>-882.9409851919745</v>
       </c>
       <c r="O63">
-        <v>-689.5854861615178</v>
+        <v>-110.3676231489968</v>
       </c>
       <c r="P63">
-        <v>-4827.098403130624</v>
+        <v>-772.5733620429777</v>
       </c>
       <c r="Q63">
-        <v>-3093.098403130624</v>
+        <v>961.4266379570223</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1365315957156465</v>
+        <v>0.1338111314550871</v>
       </c>
       <c r="T63">
-        <v>1.767701759266279</v>
+        <v>1.71550076709248</v>
       </c>
       <c r="U63">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V63">
-        <v>0.05976434510920794</v>
+        <v>0.1064100184885991</v>
       </c>
       <c r="W63">
-        <v>0.2084846729809663</v>
+        <v>0.1112846729809663</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.4781147608736636</v>
+        <v>0.8512801479087931</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1821823390141169</v>
+        <v>0.1208573579524987</v>
       </c>
       <c r="C64">
-        <v>-24781.61053801145</v>
+        <v>-7890.379856216794</v>
       </c>
       <c r="D64">
-        <v>20694.15389128935</v>
+        <v>37585.38457308401</v>
       </c>
       <c r="E64">
         <v>33026.23147881564</v>
@@ -6541,45 +6541,45 @@
         <v>5054</v>
       </c>
       <c r="M64">
-        <v>10743.9737891166</v>
+        <v>6034.267886588565</v>
       </c>
       <c r="N64">
-        <v>-5689.973789116604</v>
+        <v>-980.2678865885646</v>
       </c>
       <c r="O64">
-        <v>-711.2467236395755</v>
+        <v>-122.5334858235706</v>
       </c>
       <c r="P64">
-        <v>-4978.727065477029</v>
+        <v>-857.734400764994</v>
       </c>
       <c r="Q64">
-        <v>-3244.727065477029</v>
+        <v>876.265599235006</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1389192692871109</v>
+        <v>0.1361272138618</v>
       </c>
       <c r="T64">
-        <v>1.814220226615392</v>
+        <v>1.76064552412123</v>
       </c>
       <c r="U64">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V64">
-        <v>0.05880040405905942</v>
+        <v>0.1046937278678153</v>
       </c>
       <c r="W64">
-        <v>0.2086984140080883</v>
+        <v>0.1114984140080883</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.4704032324724754</v>
+        <v>0.8375498229425222</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1839417051807423</v>
+        <v>0.1216447241191241</v>
       </c>
       <c r="C65">
-        <v>-25826.68262418527</v>
+        <v>-9062.077007621287</v>
       </c>
       <c r="D65">
-        <v>20430.59413462038</v>
+        <v>37195.19975118437</v>
       </c>
       <c r="E65">
         <v>33807.74380832049</v>
@@ -6623,45 +6623,45 @@
         <v>5054</v>
       </c>
       <c r="M65">
-        <v>10917.26368894106</v>
+        <v>6131.594787985154</v>
       </c>
       <c r="N65">
-        <v>-5863.263688941064</v>
+        <v>-1077.594787985154</v>
       </c>
       <c r="O65">
-        <v>-732.907961117633</v>
+        <v>-134.6993484981442</v>
       </c>
       <c r="P65">
-        <v>-5130.355727823431</v>
+        <v>-942.8954394870095</v>
       </c>
       <c r="Q65">
-        <v>-3396.355727823431</v>
+        <v>791.1045605129905</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1414360062948706</v>
+        <v>0.1385684899121189</v>
       </c>
       <c r="T65">
-        <v>1.863253205713105</v>
+        <v>1.808230538286668</v>
       </c>
       <c r="U65">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V65">
-        <v>0.05786706431209023</v>
+        <v>0.1030319226635643</v>
       </c>
       <c r="W65">
-        <v>0.208905369605778</v>
+        <v>0.1117053696057779</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.4629365144967218</v>
+        <v>0.8242553813085141</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1857010713473676</v>
+        <v>0.1224320902857494</v>
       </c>
       <c r="C66">
-        <v>-26865.12576728809</v>
+        <v>-10225.75615178237</v>
       </c>
       <c r="D66">
-        <v>20173.66332102242</v>
+        <v>36813.03293652814</v>
       </c>
       <c r="E66">
         <v>34589.25613782534</v>
@@ -6705,45 +6705,45 @@
         <v>5054</v>
       </c>
       <c r="M66">
-        <v>11090.55358876553</v>
+        <v>6228.921689381744</v>
       </c>
       <c r="N66">
-        <v>-6036.553588765526</v>
+        <v>-1174.921689381744</v>
       </c>
       <c r="O66">
-        <v>-754.5691985956908</v>
+        <v>-146.865211172718</v>
       </c>
       <c r="P66">
-        <v>-5281.984390169835</v>
+        <v>-1028.056478209026</v>
       </c>
       <c r="Q66">
-        <v>-3547.984390169835</v>
+        <v>705.943521790974</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1440925620252837</v>
+        <v>0.1411453924096777</v>
       </c>
       <c r="T66">
-        <v>1.915010239205136</v>
+        <v>1.858459164350187</v>
       </c>
       <c r="U66">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V66">
-        <v>0.05696289143221382</v>
+        <v>0.1014220488719461</v>
       </c>
       <c r="W66">
-        <v>0.2091058578410398</v>
+        <v>0.1119058578410397</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.4557031314577106</v>
+        <v>0.8113763909755685</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1874604375139929</v>
+        <v>0.1419893698069705</v>
       </c>
       <c r="C67">
-        <v>-27897.18695381162</v>
+        <v>-18492.11609603295</v>
       </c>
       <c r="D67">
-        <v>19923.11446400374</v>
+        <v>29328.18532178241</v>
       </c>
       <c r="E67">
         <v>35370.7684673302</v>
@@ -6787,45 +6787,45 @@
         <v>5054</v>
       </c>
       <c r="M67">
-        <v>11263.84348858999</v>
+        <v>7758.760690760728</v>
       </c>
       <c r="N67">
-        <v>-6209.843488589988</v>
+        <v>-2704.760690760728</v>
       </c>
       <c r="O67">
-        <v>-776.2304360737485</v>
+        <v>-338.095086345091</v>
       </c>
       <c r="P67">
-        <v>-5433.613052516239</v>
+        <v>-2366.665604415637</v>
       </c>
       <c r="Q67">
-        <v>-3699.613052516239</v>
+        <v>-632.6656044156371</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1469009209402918</v>
+        <v>0.1451264417773706</v>
       </c>
       <c r="T67">
-        <v>1.96972481746814</v>
+        <v>1.936057226449812</v>
       </c>
       <c r="U67">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V67">
-        <v>0.0560865392563336</v>
+        <v>0.0814240862915516</v>
       </c>
       <c r="W67">
-        <v>0.2093001772075243</v>
+        <v>0.1403001772075243</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.4486923140506688</v>
+        <v>0.6513926903324128</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1892198036806182</v>
+        <v>0.179206183869433</v>
       </c>
       <c r="C68">
-        <v>-28923.10105087034</v>
+        <v>-27455.42021547831</v>
       </c>
       <c r="D68">
-        <v>19678.71269644987</v>
+        <v>21146.39353184191</v>
       </c>
       <c r="E68">
         <v>36152.28079683505</v>
@@ -6869,37 +6869,37 @@
         <v>5054</v>
       </c>
       <c r="M68">
-        <v>11437.13338841445</v>
+        <v>10663.43618220464</v>
       </c>
       <c r="N68">
-        <v>-6383.13338841445</v>
+        <v>-5609.436182204645</v>
       </c>
       <c r="O68">
-        <v>-797.8916735518062</v>
+        <v>-701.1795227755806</v>
       </c>
       <c r="P68">
-        <v>-5585.241714862644</v>
+        <v>-4908.256659429064</v>
       </c>
       <c r="Q68">
-        <v>-3851.241714862644</v>
+        <v>-3174.256659429064</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1498744774385357</v>
+        <v>0.149540301523285</v>
       </c>
       <c r="T68">
-        <v>2.02765790033485</v>
+        <v>2.022091568410509</v>
       </c>
       <c r="U68">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.05523674320699521</v>
+        <v>0.05924450516750661</v>
       </c>
       <c r="W68">
-        <v>0.2094886081083578</v>
+        <v>0.1944886081083578</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4418939456559617</v>
+        <v>0.4739560413400529</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1909791698472436</v>
+        <v>0.1808155500360584</v>
       </c>
       <c r="C69">
-        <v>-29943.09154054998</v>
+        <v>-28488.99455033885</v>
       </c>
       <c r="D69">
-        <v>19440.23453627508</v>
+        <v>20894.33152648621</v>
       </c>
       <c r="E69">
         <v>36933.7931263399</v>
@@ -6951,37 +6951,37 @@
         <v>5054</v>
       </c>
       <c r="M69">
-        <v>11610.42328823891</v>
+        <v>10825.00339708653</v>
       </c>
       <c r="N69">
-        <v>-6556.42328823891</v>
+        <v>-5771.003397086533</v>
       </c>
       <c r="O69">
-        <v>-819.5529110298637</v>
+        <v>-721.3754246358167</v>
       </c>
       <c r="P69">
-        <v>-5736.870377209046</v>
+        <v>-5049.627972450717</v>
       </c>
       <c r="Q69">
-        <v>-4002.870377209046</v>
+        <v>-3315.627972450717</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1530282494821277</v>
+        <v>0.1526839470239906</v>
       </c>
       <c r="T69">
-        <v>2.089102079132876</v>
+        <v>2.083367070483555</v>
       </c>
       <c r="U69">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.05441231420390574</v>
+        <v>0.05836025882172292</v>
       </c>
       <c r="W69">
-        <v>0.2096714142061813</v>
+        <v>0.1946714142061813</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4352985136312459</v>
+        <v>0.4668820705737834</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1927385360138689</v>
+        <v>0.1824249162026837</v>
       </c>
       <c r="C70">
-        <v>-30957.37120149984</v>
+        <v>-29516.63058236876</v>
       </c>
       <c r="D70">
-        <v>19207.46720483008</v>
+        <v>20648.20782396115</v>
       </c>
       <c r="E70">
         <v>37715.30545584475</v>
@@ -7033,37 +7033,37 @@
         <v>5054</v>
       </c>
       <c r="M70">
-        <v>11783.71318806337</v>
+        <v>10986.57061196842</v>
       </c>
       <c r="N70">
-        <v>-6729.713188063371</v>
+        <v>-5932.570611968422</v>
       </c>
       <c r="O70">
-        <v>-841.2141485079214</v>
+        <v>-741.5713264960527</v>
       </c>
       <c r="P70">
-        <v>-5888.499039555451</v>
+        <v>-5190.99928547237</v>
       </c>
       <c r="Q70">
-        <v>-4154.499039555451</v>
+        <v>-3456.99928547237</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1563791322784442</v>
+        <v>0.1560240703684903</v>
       </c>
       <c r="T70">
-        <v>2.154386519105778</v>
+        <v>2.148472291436166</v>
       </c>
       <c r="U70">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.05361213311267183</v>
+        <v>0.05750201972140347</v>
       </c>
       <c r="W70">
-        <v>0.2098488436540688</v>
+        <v>0.1948488436540688</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4288970649013746</v>
+        <v>0.4600161577712277</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1944979021804943</v>
+        <v>0.1840342823693091</v>
       </c>
       <c r="C71">
-        <v>-31966.14274213819</v>
+        <v>-30538.53571822937</v>
       </c>
       <c r="D71">
-        <v>18980.20799369658</v>
+        <v>20407.8150176054</v>
       </c>
       <c r="E71">
         <v>38496.81778534961</v>
@@ -7115,37 +7115,37 @@
         <v>5054</v>
       </c>
       <c r="M71">
-        <v>11957.00308788783</v>
+        <v>11148.13782685031</v>
       </c>
       <c r="N71">
-        <v>-6903.003087887833</v>
+        <v>-6094.137826850312</v>
       </c>
       <c r="O71">
-        <v>-862.8753859859792</v>
+        <v>-761.767228356289</v>
       </c>
       <c r="P71">
-        <v>-6040.127701901854</v>
+        <v>-5332.370598494023</v>
       </c>
       <c r="Q71">
-        <v>-4306.127701901854</v>
+        <v>-3598.370598494023</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1599462010616198</v>
+        <v>0.1595796855416674</v>
       </c>
       <c r="T71">
-        <v>2.223882858431772</v>
+        <v>2.217777849224429</v>
       </c>
       <c r="U71">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.05283514567625629</v>
+        <v>0.05666865711674544</v>
       </c>
       <c r="W71">
-        <v>0.2100211302194089</v>
+        <v>0.1950211302194089</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4226811654100503</v>
+        <v>0.4533492569339636</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1962572683471197</v>
+        <v>0.1856436485359344</v>
       </c>
       <c r="C72">
-        <v>-32969.59938943153</v>
+        <v>-31554.90781696889</v>
       </c>
       <c r="D72">
-        <v>18758.26367590809</v>
+        <v>20172.95524837074</v>
       </c>
       <c r="E72">
         <v>39278.33011485446</v>
@@ -7197,37 +7197,37 @@
         <v>5054</v>
       </c>
       <c r="M72">
-        <v>12130.2929877123</v>
+        <v>11309.7050417322</v>
       </c>
       <c r="N72">
-        <v>-7076.292987712295</v>
+        <v>-6255.705041732201</v>
       </c>
       <c r="O72">
-        <v>-884.5366234640369</v>
+        <v>-781.9631302165251</v>
       </c>
       <c r="P72">
-        <v>-6191.756364248258</v>
+        <v>-5473.741911515675</v>
       </c>
       <c r="Q72">
-        <v>-4457.756364248258</v>
+        <v>-3739.741911515675</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1637510744303405</v>
+        <v>0.1633723417263897</v>
       </c>
       <c r="T72">
-        <v>2.298012287046164</v>
+        <v>2.29170377753191</v>
       </c>
       <c r="U72">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.0520803578808812</v>
+        <v>0.0558591048722205</v>
       </c>
       <c r="W72">
-        <v>0.2101884943114536</v>
+        <v>0.1951884943114536</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4166428630470496</v>
+        <v>0.4468728389777641</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.198016634513745</v>
+        <v>0.1872530147025597</v>
       </c>
       <c r="C73">
-        <v>-33967.92543684215</v>
+        <v>-32565.93573315699</v>
       </c>
       <c r="D73">
-        <v>18541.44995800232</v>
+        <v>19943.43966168747</v>
       </c>
       <c r="E73">
         <v>40059.8424443593</v>
@@ -7279,37 +7279,37 @@
         <v>5054</v>
       </c>
       <c r="M73">
-        <v>12303.58288753675</v>
+        <v>11471.27225661409</v>
       </c>
       <c r="N73">
-        <v>-7249.582887536753</v>
+        <v>-6417.272256614087</v>
       </c>
       <c r="O73">
-        <v>-906.1978609420942</v>
+        <v>-802.1590320767609</v>
       </c>
       <c r="P73">
-        <v>-6343.385026594659</v>
+        <v>-5615.113224537326</v>
       </c>
       <c r="Q73">
-        <v>-4609.385026594659</v>
+        <v>-3881.113224537326</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1678183528589729</v>
+        <v>0.16742656040661</v>
       </c>
       <c r="T73">
-        <v>2.377254090047755</v>
+        <v>2.370728045722665</v>
       </c>
       <c r="U73">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.05134683171354486</v>
+        <v>0.05507235691627375</v>
       </c>
       <c r="W73">
-        <v>0.2103511439220322</v>
+        <v>0.1953511439220321</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4107746537083589</v>
+        <v>0.44057885533019</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1997760006803703</v>
+        <v>0.1888623808691851</v>
       </c>
       <c r="C74">
-        <v>-34961.29675470976</v>
+        <v>-33571.79982335988</v>
       </c>
       <c r="D74">
-        <v>18329.59096963956</v>
+        <v>19719.08790098945</v>
       </c>
       <c r="E74">
         <v>40841.35477386416</v>
@@ -7361,37 +7361,37 @@
         <v>5054</v>
       </c>
       <c r="M74">
-        <v>12476.87278736122</v>
+        <v>11632.83947149598</v>
       </c>
       <c r="N74">
-        <v>-7422.872787361217</v>
+        <v>-6578.839471495976</v>
       </c>
       <c r="O74">
-        <v>-927.8590984201521</v>
+        <v>-822.354933936997</v>
       </c>
       <c r="P74">
-        <v>-6495.013688941065</v>
+        <v>-5756.484537558979</v>
       </c>
       <c r="Q74">
-        <v>-4761.013688941065</v>
+        <v>-4022.484537558979</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1721761511753648</v>
+        <v>0.1717703661354175</v>
       </c>
       <c r="T74">
-        <v>2.462156021835174</v>
+        <v>2.455396904498475</v>
       </c>
       <c r="U74">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.05063368127307895</v>
+        <v>0.05430746307021439</v>
       </c>
       <c r="W74">
-        <v>0.2105092754878725</v>
+        <v>0.1955092754878724</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4050694501846316</v>
+        <v>0.4344597045617151</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2015353668469956</v>
+        <v>0.1904717470358104</v>
       </c>
       <c r="C75">
-        <v>-35949.88126603795</v>
+        <v>-34572.67241881015</v>
       </c>
       <c r="D75">
-        <v>18122.51878781623</v>
+        <v>19499.72763504403</v>
       </c>
       <c r="E75">
         <v>41622.86710336901</v>
@@ -7443,37 +7443,37 @@
         <v>5054</v>
       </c>
       <c r="M75">
-        <v>12650.16268718568</v>
+        <v>11794.40668637786</v>
       </c>
       <c r="N75">
-        <v>-7596.162687185679</v>
+        <v>-6740.406686377864</v>
       </c>
       <c r="O75">
-        <v>-949.5203358982099</v>
+        <v>-842.550835797233</v>
       </c>
       <c r="P75">
-        <v>-6646.642351287469</v>
+        <v>-5897.855850580631</v>
       </c>
       <c r="Q75">
-        <v>-4912.642351287469</v>
+        <v>-4163.855850580631</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1768567493670449</v>
+        <v>0.1764359352515441</v>
       </c>
       <c r="T75">
-        <v>2.553346985606848</v>
+        <v>2.546337530591011</v>
       </c>
       <c r="U75">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.04994006920084499</v>
+        <v>0.05356352521993748</v>
       </c>
       <c r="W75">
-        <v>0.2106630746820459</v>
+        <v>0.1956630746820459</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3995205536067599</v>
+        <v>0.4285082017594999</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.203294733013621</v>
+        <v>0.1920811132024357</v>
       </c>
       <c r="C76">
-        <v>-36933.8393903908</v>
+        <v>-35568.71826687538</v>
       </c>
       <c r="D76">
-        <v>17920.07299296822</v>
+        <v>19285.19411648364</v>
       </c>
       <c r="E76">
         <v>42404.37943287386</v>
@@ -7525,37 +7525,37 @@
         <v>5054</v>
       </c>
       <c r="M76">
-        <v>12823.45258701014</v>
+        <v>11955.97390125975</v>
       </c>
       <c r="N76">
-        <v>-7769.452587010139</v>
+        <v>-6901.973901259753</v>
       </c>
       <c r="O76">
-        <v>-971.1815733762674</v>
+        <v>-862.7467376574691</v>
       </c>
       <c r="P76">
-        <v>-6798.271013633872</v>
+        <v>-6039.227163602283</v>
       </c>
       <c r="Q76">
-        <v>-5064.271013633872</v>
+        <v>-4305.227163602283</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1818973935734697</v>
+        <v>0.1814603942996804</v>
       </c>
       <c r="T76">
-        <v>2.651552638899419</v>
+        <v>2.644273589459896</v>
       </c>
       <c r="U76">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.04926520340083358</v>
+        <v>0.05283969379804643</v>
       </c>
       <c r="W76">
-        <v>0.2108127171412417</v>
+        <v>0.1958127171412417</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3941216272066687</v>
+        <v>0.4227175503843715</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2050540991802464</v>
+        <v>0.1936904793690611</v>
       </c>
       <c r="C77">
-        <v>-37913.32445836565</v>
+        <v>-36560.09494370187</v>
       </c>
       <c r="D77">
-        <v>17722.10025449823</v>
+        <v>19075.32976916201</v>
       </c>
       <c r="E77">
         <v>43185.89176237871</v>
@@ -7607,37 +7607,37 @@
         <v>5054</v>
       </c>
       <c r="M77">
-        <v>12996.7424868346</v>
+        <v>12117.54111614164</v>
       </c>
       <c r="N77">
-        <v>-7942.742486834601</v>
+        <v>-7063.541116141641</v>
       </c>
       <c r="O77">
-        <v>-992.8428108543251</v>
+        <v>-882.9426395177052</v>
       </c>
       <c r="P77">
-        <v>-6949.899675980276</v>
+        <v>-6180.598476623936</v>
       </c>
       <c r="Q77">
-        <v>-5215.899675980276</v>
+        <v>-4446.598476623936</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1873412893164085</v>
+        <v>0.1868868100716676</v>
       </c>
       <c r="T77">
-        <v>2.757614744455396</v>
+        <v>2.750044533038291</v>
       </c>
       <c r="U77">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.04860833402215579</v>
+        <v>0.05213516454740581</v>
       </c>
       <c r="W77">
-        <v>0.2109583691348589</v>
+        <v>0.1959583691348589</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3888666721772464</v>
+        <v>0.4170813163792465</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2068134653468717</v>
+        <v>0.1952998455356864</v>
       </c>
       <c r="C78">
-        <v>-38888.48309889259</v>
+        <v>-37546.95324020562</v>
       </c>
       <c r="D78">
-        <v>17528.45394347614</v>
+        <v>18869.98380216311</v>
       </c>
       <c r="E78">
         <v>43967.40409188357</v>
@@ -7689,37 +7689,37 @@
         <v>5054</v>
       </c>
       <c r="M78">
-        <v>13170.03238665906</v>
+        <v>12279.10833102353</v>
       </c>
       <c r="N78">
-        <v>-8116.032386659062</v>
+        <v>-7225.10833102353</v>
       </c>
       <c r="O78">
-        <v>-1014.504048332383</v>
+        <v>-903.1385413779412</v>
       </c>
       <c r="P78">
-        <v>-7101.52833832668</v>
+        <v>-6321.969789645589</v>
       </c>
       <c r="Q78">
-        <v>-5367.52833832668</v>
+        <v>-4587.969789645589</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1932388430379256</v>
+        <v>0.1927654271579871</v>
       </c>
       <c r="T78">
-        <v>2.872515358807704</v>
+        <v>2.864629721914887</v>
       </c>
       <c r="U78">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.047968750679759</v>
+        <v>0.05144917554020311</v>
       </c>
       <c r="W78">
-        <v>0.2111001881812757</v>
+        <v>0.1961001881812757</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.383750005438072</v>
+        <v>0.4115934043216248</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.208572831513497</v>
+        <v>0.1969092117023118</v>
       </c>
       <c r="C79">
-        <v>-39859.45560141683</v>
+        <v>-38529.43752339782</v>
       </c>
       <c r="D79">
-        <v>17338.99377045675</v>
+        <v>18669.01184847576</v>
       </c>
       <c r="E79">
         <v>44748.91642138841</v>
@@ -7771,37 +7771,37 @@
         <v>5054</v>
       </c>
       <c r="M79">
-        <v>13343.32228648352</v>
+        <v>12440.67554590542</v>
       </c>
       <c r="N79">
-        <v>-8289.322286483522</v>
+        <v>-7386.675545905418</v>
       </c>
       <c r="O79">
-        <v>-1036.16528581044</v>
+        <v>-923.3344432381773</v>
       </c>
       <c r="P79">
-        <v>-7253.157000673082</v>
+        <v>-6463.341102667241</v>
       </c>
       <c r="Q79">
-        <v>-5519.157000673082</v>
+        <v>-4729.341102667241</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1996492275178354</v>
+        <v>0.1991552283387691</v>
       </c>
       <c r="T79">
-        <v>2.997407330929778</v>
+        <v>2.989178840259013</v>
       </c>
       <c r="U79">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.04734577989171019</v>
+        <v>0.05078100442929138</v>
       </c>
       <c r="W79">
-        <v>0.2112383236160973</v>
+        <v>0.1962383236160972</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3787662391336816</v>
+        <v>0.4062480354343311</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2103321976801224</v>
+        <v>0.1985185778689371</v>
       </c>
       <c r="C80">
-        <v>-40826.37625484365</v>
+        <v>-39507.68607486415</v>
       </c>
       <c r="D80">
-        <v>17153.58544653478</v>
+        <v>18472.27562651428</v>
       </c>
       <c r="E80">
         <v>45530.42875089327</v>
@@ -7853,37 +7853,37 @@
         <v>5054</v>
       </c>
       <c r="M80">
-        <v>13516.61218630798</v>
+        <v>12602.24276078731</v>
       </c>
       <c r="N80">
-        <v>-8462.612186307984</v>
+        <v>-7548.242760787307</v>
       </c>
       <c r="O80">
-        <v>-1057.826523288498</v>
+        <v>-943.5303450984134</v>
       </c>
       <c r="P80">
-        <v>-7404.785663019486</v>
+        <v>-6604.712415688893</v>
       </c>
       <c r="Q80">
-        <v>-5670.785663019486</v>
+        <v>-4870.712415688893</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2066423742231916</v>
+        <v>0.2061259205359859</v>
       </c>
       <c r="T80">
-        <v>3.133653118699314</v>
+        <v>3.125050605725332</v>
       </c>
       <c r="U80">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.04673878271361134</v>
+        <v>0.05012996591096713</v>
       </c>
       <c r="W80">
-        <v>0.2113729171166926</v>
+        <v>0.1963729171166926</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3739102617088907</v>
+        <v>0.4010397272877371</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2120915638467477</v>
+        <v>0.2001279440355625</v>
       </c>
       <c r="C81">
-        <v>-41789.37366496728</v>
+        <v>-40481.8314080656</v>
       </c>
       <c r="D81">
-        <v>16972.10036591601</v>
+        <v>18279.64262281769</v>
       </c>
       <c r="E81">
         <v>46311.94108039812</v>
@@ -7935,37 +7935,37 @@
         <v>5054</v>
       </c>
       <c r="M81">
-        <v>13689.90208613245</v>
+        <v>12763.8099756692</v>
       </c>
       <c r="N81">
-        <v>-8635.902086132446</v>
+        <v>-7709.809975669195</v>
       </c>
       <c r="O81">
-        <v>-1079.487760766556</v>
+        <v>-963.7262469586494</v>
       </c>
       <c r="P81">
-        <v>-7556.41432536589</v>
+        <v>-6746.083728710546</v>
       </c>
       <c r="Q81">
-        <v>-5822.41432536589</v>
+        <v>-5012.083728710546</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2143015349004864</v>
+        <v>0.2137604881805567</v>
       </c>
       <c r="T81">
-        <v>3.282874695780233</v>
+        <v>3.2738625393313</v>
       </c>
       <c r="U81">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.04614715255267955</v>
+        <v>0.04949540938044856</v>
       </c>
       <c r="W81">
-        <v>0.2115041031868931</v>
+        <v>0.1965041031868931</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3691772204214364</v>
+        <v>0.3959632750435885</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.213850930013373</v>
+        <v>0.2017373102021878</v>
       </c>
       <c r="C82">
-        <v>-42748.57105196029</v>
+        <v>-41452.00056599093</v>
       </c>
       <c r="D82">
-        <v>16794.41530842785</v>
+        <v>18090.98579439721</v>
       </c>
       <c r="E82">
         <v>47093.45340990298</v>
@@ -8017,37 +8017,37 @@
         <v>5054</v>
       </c>
       <c r="M82">
-        <v>13863.19198595691</v>
+        <v>12925.37719055109</v>
       </c>
       <c r="N82">
-        <v>-8809.191985956908</v>
+        <v>-7871.377190551086</v>
       </c>
       <c r="O82">
-        <v>-1101.148998244613</v>
+        <v>-983.9221488188857</v>
       </c>
       <c r="P82">
-        <v>-7708.042987712294</v>
+        <v>-6887.4550417322</v>
       </c>
       <c r="Q82">
-        <v>-5974.042987712294</v>
+        <v>-5153.4550417322</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2227266116455107</v>
+        <v>0.2221585125895845</v>
       </c>
       <c r="T82">
-        <v>3.447018430569246</v>
+        <v>3.437555666297865</v>
       </c>
       <c r="U82">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.04557031314577106</v>
+        <v>0.04887671676319295</v>
       </c>
       <c r="W82">
-        <v>0.2116320096053386</v>
+        <v>0.1966320096053386</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3645625051661684</v>
+        <v>0.3910137341055435</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2156102961799984</v>
+        <v>0.2033466763688132</v>
       </c>
       <c r="C83">
-        <v>-43704.08652936955</v>
+        <v>-42418.31540056573</v>
       </c>
       <c r="D83">
-        <v>16620.41216052344</v>
+        <v>17906.18328932725</v>
       </c>
       <c r="E83">
         <v>47874.96573940782</v>
@@ -8099,37 +8099,37 @@
         <v>5054</v>
       </c>
       <c r="M83">
-        <v>14036.48188578137</v>
+        <v>13086.94440543297</v>
       </c>
       <c r="N83">
-        <v>-8982.481885781368</v>
+        <v>-8032.944405432972</v>
       </c>
       <c r="O83">
-        <v>-1122.810235722671</v>
+        <v>-1004.118050679122</v>
       </c>
       <c r="P83">
-        <v>-7859.671650058697</v>
+        <v>-7028.826354753851</v>
       </c>
       <c r="Q83">
-        <v>-6125.671650058697</v>
+        <v>-5294.826354753851</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2320385385742218</v>
+        <v>0.2314405395679837</v>
       </c>
       <c r="T83">
-        <v>3.628440453230785</v>
+        <v>3.618479648734595</v>
       </c>
       <c r="U83">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.04500771668718129</v>
+        <v>0.04827330050685723</v>
       </c>
       <c r="W83">
-        <v>0.2117567578406127</v>
+        <v>0.1967567578406126</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3600617334974503</v>
+        <v>0.3861864040548579</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2173696623466237</v>
+        <v>0.2049560425354385</v>
       </c>
       <c r="C84">
-        <v>-44656.03336594663</v>
+        <v>-43380.89283510936</v>
       </c>
       <c r="D84">
-        <v>16449.97765345121</v>
+        <v>17725.11818428847</v>
       </c>
       <c r="E84">
         <v>48656.47806891268</v>
@@ -8181,37 +8181,37 @@
         <v>5054</v>
       </c>
       <c r="M84">
-        <v>14209.77178560583</v>
+        <v>13248.51162031486</v>
       </c>
       <c r="N84">
-        <v>-9155.77178560583</v>
+        <v>-8194.511620314863</v>
       </c>
       <c r="O84">
-        <v>-1144.471473200729</v>
+        <v>-1024.313952539358</v>
       </c>
       <c r="P84">
-        <v>-8011.300312405101</v>
+        <v>-7170.197667775505</v>
       </c>
       <c r="Q84">
-        <v>-6277.300312405101</v>
+        <v>-5436.197667775505</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2423851240505674</v>
+        <v>0.2417539028773161</v>
       </c>
       <c r="T84">
-        <v>3.830020478410273</v>
+        <v>3.819506295886517</v>
       </c>
       <c r="U84">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.04445884209343517</v>
+        <v>0.04768460172018824</v>
       </c>
       <c r="W84">
-        <v>0.2118784634360019</v>
+        <v>0.1968784634360019</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3556707367474814</v>
+        <v>0.3814768137615059</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2191290285132491</v>
+        <v>0.2065654087020638</v>
       </c>
       <c r="C85">
-        <v>-45604.52023153163</v>
+        <v>-44339.84511102767</v>
       </c>
       <c r="D85">
-        <v>16283.00311737106</v>
+        <v>17547.67823787503</v>
       </c>
       <c r="E85">
         <v>49437.99039841753</v>
@@ -8263,37 +8263,37 @@
         <v>5054</v>
       </c>
       <c r="M85">
-        <v>14383.06168543029</v>
+        <v>13410.07883519675</v>
       </c>
       <c r="N85">
-        <v>-9329.061685430292</v>
+        <v>-8356.078835196751</v>
       </c>
       <c r="O85">
-        <v>-1166.132710678786</v>
+        <v>-1044.509854399594</v>
       </c>
       <c r="P85">
-        <v>-8162.928974751505</v>
+        <v>-7311.568980797158</v>
       </c>
       <c r="Q85">
-        <v>-6428.928974751505</v>
+        <v>-5577.568980797158</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2539489548770714</v>
+        <v>0.25328060304657</v>
       </c>
       <c r="T85">
-        <v>4.055315800669701</v>
+        <v>4.044183136821018</v>
       </c>
       <c r="U85">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.04392319339351427</v>
+        <v>0.04711008844645103</v>
       </c>
       <c r="W85">
-        <v>0.2119972363664421</v>
+        <v>0.1969972363664421</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3513855471481142</v>
+        <v>0.3768807075716083</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2208883946798744</v>
+        <v>0.2081747748686892</v>
       </c>
       <c r="C86">
-        <v>-46549.65142811296</v>
+        <v>-45295.28001983525</v>
       </c>
       <c r="D86">
-        <v>16119.38425029458</v>
+        <v>17373.75565857229</v>
       </c>
       <c r="E86">
         <v>50219.50272792238</v>
@@ -8345,37 +8345,37 @@
         <v>5054</v>
       </c>
       <c r="M86">
-        <v>14556.35158525475</v>
+        <v>13571.64605007864</v>
       </c>
       <c r="N86">
-        <v>-9502.351585254753</v>
+        <v>-8517.646050078638</v>
       </c>
       <c r="O86">
-        <v>-1187.793948156844</v>
+        <v>-1064.70575625983</v>
       </c>
       <c r="P86">
-        <v>-8314.557637097909</v>
+        <v>-7452.940293818809</v>
       </c>
       <c r="Q86">
-        <v>-6580.557637097909</v>
+        <v>-5718.940293818809</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2669582645568883</v>
+        <v>0.2662481407369806</v>
       </c>
       <c r="T86">
-        <v>4.308773038211555</v>
+        <v>4.29694458287233</v>
       </c>
       <c r="U86">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.04340029823406767</v>
+        <v>0.04654925406018377</v>
       </c>
       <c r="W86">
-        <v>0.212113181369967</v>
+        <v>0.197113181369967</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3472023858725414</v>
+        <v>0.3723940324814701</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2226477608464997</v>
+        <v>0.2097841410353145</v>
       </c>
       <c r="C87">
-        <v>-47491.52710709452</v>
+        <v>-46247.30112151521</v>
       </c>
       <c r="D87">
-        <v>15959.02090081788</v>
+        <v>17203.24688639718</v>
       </c>
       <c r="E87">
         <v>51001.01505742723</v>
@@ -8427,37 +8427,37 @@
         <v>5054</v>
       </c>
       <c r="M87">
-        <v>14729.64148507922</v>
+        <v>13733.21326496053</v>
       </c>
       <c r="N87">
-        <v>-9675.641485079215</v>
+        <v>-8679.213264960528</v>
       </c>
       <c r="O87">
-        <v>-1209.455185634902</v>
+        <v>-1084.901658120066</v>
       </c>
       <c r="P87">
-        <v>-8466.186299444313</v>
+        <v>-7594.311606840462</v>
       </c>
       <c r="Q87">
-        <v>-6732.186299444313</v>
+        <v>-5860.311606840462</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2817021488606808</v>
+        <v>0.2809446834527792</v>
       </c>
       <c r="T87">
-        <v>4.596024574092326</v>
+        <v>4.583407555063818</v>
       </c>
       <c r="U87">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.04288970649013746</v>
+        <v>0.04600161577712277</v>
       </c>
       <c r="W87">
-        <v>0.2122263982557619</v>
+        <v>0.1972263982557619</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3431176519210997</v>
+        <v>0.3680129262169822</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2244071270131251</v>
+        <v>0.2113935072019398</v>
       </c>
       <c r="C88">
-        <v>-48430.24347372215</v>
+        <v>-47196.00795014559</v>
       </c>
       <c r="D88">
-        <v>15801.81686369509</v>
+        <v>17036.05238727164</v>
       </c>
       <c r="E88">
         <v>51782.52738693207</v>
@@ -8509,37 +8509,37 @@
         <v>5054</v>
       </c>
       <c r="M88">
-        <v>14902.93138490367</v>
+        <v>13894.78047984241</v>
       </c>
       <c r="N88">
-        <v>-9848.931384903673</v>
+        <v>-8840.780479842413</v>
       </c>
       <c r="O88">
-        <v>-1231.116423112959</v>
+        <v>-1105.097559980302</v>
       </c>
       <c r="P88">
-        <v>-8617.814961790715</v>
+        <v>-7735.682919862112</v>
       </c>
       <c r="Q88">
-        <v>-6883.814961790715</v>
+        <v>-6001.682919862112</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2985523023507295</v>
+        <v>0.297740732270835</v>
       </c>
       <c r="T88">
-        <v>4.92431204367035</v>
+        <v>4.910793808996949</v>
       </c>
       <c r="U88">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.04239098897281029</v>
+        <v>0.04546671326808648</v>
       </c>
       <c r="W88">
-        <v>0.2123369821907244</v>
+        <v>0.1973369821907243</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3391279117824824</v>
+        <v>0.3637337061446918</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2261664931797504</v>
+        <v>0.2130028733685652</v>
       </c>
       <c r="C89">
-        <v>-49365.89297954548</v>
+        <v>-48141.49620765078</v>
       </c>
       <c r="D89">
-        <v>15647.67968737661</v>
+        <v>16872.07645927131</v>
       </c>
       <c r="E89">
         <v>52564.03971643693</v>
@@ -8591,37 +8591,37 @@
         <v>5054</v>
       </c>
       <c r="M89">
-        <v>15076.22128472814</v>
+        <v>14056.3476947243</v>
       </c>
       <c r="N89">
-        <v>-10022.22128472814</v>
+        <v>-9002.347694724303</v>
       </c>
       <c r="O89">
-        <v>-1252.777660591017</v>
+        <v>-1125.293461840538</v>
       </c>
       <c r="P89">
-        <v>-8769.443624137119</v>
+        <v>-7877.054232883766</v>
       </c>
       <c r="Q89">
-        <v>-7035.443624137119</v>
+        <v>-6143.054232883766</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3179947871469395</v>
+        <v>0.3171207885993607</v>
       </c>
       <c r="T89">
-        <v>5.303105277798838</v>
+        <v>5.288547178919791</v>
       </c>
       <c r="U89">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.04190373622599638</v>
+        <v>0.04494410736845329</v>
       </c>
       <c r="W89">
-        <v>0.2124450239662624</v>
+        <v>0.1974450239662624</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.335229889807971</v>
+        <v>0.3595528589476263</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2279258593463758</v>
+        <v>0.2146122395351905</v>
       </c>
       <c r="C90">
-        <v>-50298.56450372463</v>
+        <v>-49083.85794646997</v>
       </c>
       <c r="D90">
-        <v>15496.52049270232</v>
+        <v>16711.22704995697</v>
       </c>
       <c r="E90">
         <v>53345.55204594178</v>
@@ -8673,37 +8673,37 @@
         <v>5054</v>
       </c>
       <c r="M90">
-        <v>15249.5111845526</v>
+        <v>14217.91490960619</v>
       </c>
       <c r="N90">
-        <v>-10195.5111845526</v>
+        <v>-9163.914909606192</v>
       </c>
       <c r="O90">
-        <v>-1274.438898069075</v>
+        <v>-1145.489363700774</v>
       </c>
       <c r="P90">
-        <v>-8921.072286483522</v>
+        <v>-8018.425545905418</v>
       </c>
       <c r="Q90">
-        <v>-7187.072286483522</v>
+        <v>-6284.425545905418</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3406776860758511</v>
+        <v>0.3397308543159742</v>
       </c>
       <c r="T90">
-        <v>5.745030717615409</v>
+        <v>5.729259443829775</v>
       </c>
       <c r="U90">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.04142755740524642</v>
+        <v>0.04443337887562996</v>
       </c>
       <c r="W90">
-        <v>0.2125506102469019</v>
+        <v>0.1975506102469018</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3314204592419714</v>
+        <v>0.3554670310050396</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2296852255130011</v>
+        <v>0.2162216057018159</v>
       </c>
       <c r="C91">
-        <v>-51228.34352392862</v>
+        <v>-50023.18174187577</v>
       </c>
       <c r="D91">
-        <v>15348.25380200318</v>
+        <v>16553.41558405603</v>
       </c>
       <c r="E91">
         <v>54127.06437544664</v>
@@ -8755,37 +8755,37 @@
         <v>5054</v>
       </c>
       <c r="M91">
-        <v>15422.80108437706</v>
+        <v>14379.48212448808</v>
       </c>
       <c r="N91">
-        <v>-10368.80108437706</v>
+        <v>-9325.48212448808</v>
       </c>
       <c r="O91">
-        <v>-1296.100135547132</v>
+        <v>-1165.68526556101</v>
       </c>
       <c r="P91">
-        <v>-9072.700948829926</v>
+        <v>-8159.79685892707</v>
       </c>
       <c r="Q91">
-        <v>-7338.700948829926</v>
+        <v>-6425.79685892707</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3674847484463831</v>
+        <v>0.3664518410719718</v>
       </c>
       <c r="T91">
-        <v>6.267306237398628</v>
+        <v>6.250101211450663</v>
       </c>
       <c r="U91">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.04096207923215376</v>
+        <v>0.04393412742758918</v>
       </c>
       <c r="W91">
-        <v>0.2126538238021337</v>
+        <v>0.1976538238021337</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.32769663385723</v>
+        <v>0.3514730194207134</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2314445916796264</v>
+        <v>0.2178309718684412</v>
       </c>
       <c r="C92">
-        <v>-52155.31227751623</v>
+        <v>-50959.5528546202</v>
       </c>
       <c r="D92">
-        <v>15202.79737792042</v>
+        <v>16398.55680081645</v>
       </c>
       <c r="E92">
         <v>54908.57670495149</v>
@@ -8837,37 +8837,37 @@
         <v>5054</v>
       </c>
       <c r="M92">
-        <v>15596.09098420152</v>
+        <v>14541.04933936997</v>
       </c>
       <c r="N92">
-        <v>-10542.09098420152</v>
+        <v>-9487.049339369971</v>
       </c>
       <c r="O92">
-        <v>-1317.76137302519</v>
+        <v>-1185.881167421246</v>
       </c>
       <c r="P92">
-        <v>-9224.32961117633</v>
+        <v>-8301.168171948724</v>
       </c>
       <c r="Q92">
-        <v>-7490.32961117633</v>
+        <v>-6567.168171948724</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3996532232910214</v>
+        <v>0.398517025179169</v>
       </c>
       <c r="T92">
-        <v>6.89403686113849</v>
+        <v>6.87511133259573</v>
       </c>
       <c r="U92">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.04050694501846316</v>
+        <v>0.04344597045617151</v>
       </c>
       <c r="W92">
-        <v>0.2127547437228048</v>
+        <v>0.1977547437228048</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3240555601477053</v>
+        <v>0.347567763649372</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2332039578462518</v>
+        <v>0.2194403380350665</v>
       </c>
       <c r="C93">
-        <v>-53079.54991363772</v>
+        <v>-51893.05338453611</v>
       </c>
       <c r="D93">
-        <v>15060.07207130379</v>
+        <v>16246.5686004054</v>
       </c>
       <c r="E93">
         <v>55690.08903445634</v>
@@ -8919,37 +8919,37 @@
         <v>5054</v>
       </c>
       <c r="M93">
-        <v>15769.38088402598</v>
+        <v>14702.61655425186</v>
       </c>
       <c r="N93">
-        <v>-10715.38088402598</v>
+        <v>-9648.616554251859</v>
       </c>
       <c r="O93">
-        <v>-1339.422610503248</v>
+        <v>-1206.077069281482</v>
       </c>
       <c r="P93">
-        <v>-9375.958273522734</v>
+        <v>-8442.539484970377</v>
       </c>
       <c r="Q93">
-        <v>-7641.958273522734</v>
+        <v>-6708.539484970377</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4389702481011349</v>
+        <v>0.4377078057546323</v>
       </c>
       <c r="T93">
-        <v>7.660040956820546</v>
+        <v>7.639012591773033</v>
       </c>
       <c r="U93">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.040061813754524</v>
+        <v>0.04296854220940039</v>
       </c>
       <c r="W93">
-        <v>0.2128534456232414</v>
+        <v>0.1978534456232414</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.320494510036192</v>
+        <v>0.3437483376752032</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2349633240128771</v>
+        <v>0.2210497042016919</v>
       </c>
       <c r="C94">
-        <v>-54001.13263684842</v>
+        <v>-52823.7624156751</v>
       </c>
       <c r="D94">
-        <v>14920.00167759795</v>
+        <v>16097.37189877126</v>
       </c>
       <c r="E94">
         <v>56471.6013639612</v>
@@ -9001,37 +9001,37 @@
         <v>5054</v>
       </c>
       <c r="M94">
-        <v>15942.67078385044</v>
+        <v>14864.18376913375</v>
       </c>
       <c r="N94">
-        <v>-10888.67078385044</v>
+        <v>-9810.183769133748</v>
       </c>
       <c r="O94">
-        <v>-1361.083847981306</v>
+        <v>-1226.272971141718</v>
       </c>
       <c r="P94">
-        <v>-9527.586935869138</v>
+        <v>-8583.91079799203</v>
       </c>
       <c r="Q94">
-        <v>-7793.586935869138</v>
+        <v>-6849.91079799203</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4881165291137768</v>
+        <v>0.4866962814739614</v>
       </c>
       <c r="T94">
-        <v>8.617546076423116</v>
+        <v>8.593889165744665</v>
       </c>
       <c r="U94">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.03962635925719222</v>
+        <v>0.04250149283755909</v>
       </c>
       <c r="W94">
-        <v>0.2129500018301902</v>
+        <v>0.1979500018301902</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3170108740575378</v>
+        <v>0.3400119427004726</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2367226901795025</v>
+        <v>0.2226590703683172</v>
       </c>
       <c r="C95">
-        <v>-54920.13384278215</v>
+        <v>-53751.75615352116</v>
       </c>
       <c r="D95">
-        <v>14782.51280116907</v>
+        <v>15950.89049043005</v>
       </c>
       <c r="E95">
         <v>57253.11369346605</v>
@@ -9083,37 +9083,37 @@
         <v>5054</v>
       </c>
       <c r="M95">
-        <v>16115.96068367491</v>
+        <v>15025.75098401564</v>
       </c>
       <c r="N95">
-        <v>-11061.96068367491</v>
+        <v>-9971.750984015638</v>
       </c>
       <c r="O95">
-        <v>-1382.745085459363</v>
+        <v>-1246.468873001955</v>
       </c>
       <c r="P95">
-        <v>-9679.215598215544</v>
+        <v>-8725.282111013683</v>
       </c>
       <c r="Q95">
-        <v>-7945.215598215544</v>
+        <v>-6991.282111013683</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5513046047014594</v>
+        <v>0.5496814645416702</v>
       </c>
       <c r="T95">
-        <v>9.848624087340706</v>
+        <v>9.821587617993904</v>
       </c>
       <c r="U95">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.03920026937270628</v>
+        <v>0.04204448753823049</v>
       </c>
       <c r="W95">
-        <v>0.2130444815595703</v>
+        <v>0.1980444815595702</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3136021549816502</v>
+        <v>0.3363559003058439</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2384820563461278</v>
+        <v>0.2242684365349426</v>
       </c>
       <c r="C96">
-        <v>-55836.62424639142</v>
+        <v>-54677.10805478029</v>
       </c>
       <c r="D96">
-        <v>14647.53472706463</v>
+        <v>15807.05091867576</v>
       </c>
       <c r="E96">
         <v>58034.62602297089</v>
@@ -9165,37 +9165,37 @@
         <v>5054</v>
       </c>
       <c r="M96">
-        <v>16289.25058349937</v>
+        <v>15187.31819889752</v>
       </c>
       <c r="N96">
-        <v>-11235.25058349937</v>
+        <v>-10133.31819889752</v>
       </c>
       <c r="O96">
-        <v>-1404.406322937421</v>
+        <v>-1266.66477486219</v>
       </c>
       <c r="P96">
-        <v>-9830.844260561946</v>
+        <v>-8866.653424035332</v>
       </c>
       <c r="Q96">
-        <v>-8096.844260561946</v>
+        <v>-7132.653424035332</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6355553721517028</v>
+        <v>0.6336617086319487</v>
       </c>
       <c r="T96">
-        <v>11.49006143523083</v>
+        <v>11.45851888765956</v>
       </c>
       <c r="U96">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.03878324523044345</v>
+        <v>0.0415972057559089</v>
       </c>
       <c r="W96">
-        <v>0.2131369510819422</v>
+        <v>0.1981369510819422</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3102659618435476</v>
+        <v>0.3327776460472712</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2402414225127532</v>
+        <v>0.2258778027015679</v>
       </c>
       <c r="C97">
-        <v>-56750.6720032257</v>
+        <v>-55599.88895021052</v>
       </c>
       <c r="D97">
-        <v>14514.99929973521</v>
+        <v>15665.7823527504</v>
       </c>
       <c r="E97">
         <v>58816.13835247575</v>
@@ -9247,37 +9247,37 @@
         <v>5054</v>
       </c>
       <c r="M97">
-        <v>16462.54048332383</v>
+        <v>15348.88541377941</v>
       </c>
       <c r="N97">
-        <v>-11408.54048332383</v>
+        <v>-10294.88541377941</v>
       </c>
       <c r="O97">
-        <v>-1426.067560415479</v>
+        <v>-1286.860676722427</v>
       </c>
       <c r="P97">
-        <v>-9982.47292290835</v>
+        <v>-9008.024737056987</v>
       </c>
       <c r="Q97">
-        <v>-8248.47292290835</v>
+        <v>-7274.024737056987</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7535064465820438</v>
+        <v>0.7512340503583388</v>
       </c>
       <c r="T97">
-        <v>13.788073722277</v>
+        <v>13.75022266519148</v>
       </c>
       <c r="U97">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.0383750005438072</v>
+        <v>0.04115934043216248</v>
       </c>
       <c r="W97">
-        <v>0.2132274738775274</v>
+        <v>0.1982274738775274</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3070000043504576</v>
+        <v>0.3292747234572999</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2420007886793785</v>
+        <v>0.2274871688681932</v>
       </c>
       <c r="C98">
-        <v>-57662.34282418431</v>
+        <v>-56520.16716092364</v>
       </c>
       <c r="D98">
-        <v>14384.84080828145</v>
+        <v>15527.01647154212</v>
       </c>
       <c r="E98">
         <v>59597.6506819806</v>
@@ -9329,37 +9329,37 @@
         <v>5054</v>
       </c>
       <c r="M98">
-        <v>16635.83038314829</v>
+        <v>15510.4526286613</v>
       </c>
       <c r="N98">
-        <v>-11581.83038314829</v>
+        <v>-10456.4526286613</v>
       </c>
       <c r="O98">
-        <v>-1447.728797893536</v>
+        <v>-1307.056578582663</v>
       </c>
       <c r="P98">
-        <v>-10134.10158525475</v>
+        <v>-9149.39605007864</v>
       </c>
       <c r="Q98">
-        <v>-8400.101585254752</v>
+        <v>-7415.39605007864</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.9304330582275525</v>
+        <v>0.9275925629479217</v>
       </c>
       <c r="T98">
-        <v>17.23509215284621</v>
+        <v>17.18777833148931</v>
       </c>
       <c r="U98">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.03797526095480921</v>
+        <v>0.04073059730266079</v>
       </c>
       <c r="W98">
-        <v>0.2133161107815379</v>
+        <v>0.1983161107815379</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3038020876384737</v>
+        <v>0.3258447784212863</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2437601548460038</v>
+        <v>0.2290965350348186</v>
       </c>
       <c r="C99">
-        <v>-58571.70008415037</v>
+        <v>-57438.00860856041</v>
       </c>
       <c r="D99">
-        <v>14256.99587782023</v>
+        <v>15390.68735341019</v>
       </c>
       <c r="E99">
         <v>60379.16301148544</v>
@@ -9411,37 +9411,37 @@
         <v>5054</v>
       </c>
       <c r="M99">
-        <v>16809.12028297275</v>
+        <v>15672.01984354319</v>
       </c>
       <c r="N99">
-        <v>-11755.12028297275</v>
+        <v>-10618.01984354319</v>
       </c>
       <c r="O99">
-        <v>-1469.390035371594</v>
+        <v>-1327.252480442899</v>
       </c>
       <c r="P99">
-        <v>-10285.73024760115</v>
+        <v>-9290.767363100291</v>
       </c>
       <c r="Q99">
-        <v>-8551.730247601154</v>
+        <v>-7556.767363100291</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.225310744303403</v>
+        <v>1.221523417263896</v>
       </c>
       <c r="T99">
-        <v>22.98012287046161</v>
+        <v>22.91703777531908</v>
       </c>
       <c r="U99">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.03758376341919262</v>
+        <v>0.04031069423768491</v>
       </c>
       <c r="W99">
-        <v>0.2134029201205172</v>
+        <v>0.1984029201205172</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.300670107353541</v>
+        <v>0.3224855539014793</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2455195210126292</v>
+        <v>0.230705901201444</v>
       </c>
       <c r="C100">
-        <v>-59478.80492488286</v>
+        <v>-58353.47691971186</v>
       </c>
       <c r="D100">
-        <v>14131.4033665926</v>
+        <v>15256.7313717636</v>
       </c>
       <c r="E100">
         <v>61160.6753409903</v>
@@ -9493,37 +9493,37 @@
         <v>5054</v>
       </c>
       <c r="M100">
-        <v>16982.41018279721</v>
+        <v>15833.58705842508</v>
       </c>
       <c r="N100">
-        <v>-11928.41018279721</v>
+        <v>-10779.58705842508</v>
       </c>
       <c r="O100">
-        <v>-1491.051272849651</v>
+        <v>-1347.448382303135</v>
       </c>
       <c r="P100">
-        <v>-10437.35890994756</v>
+        <v>-9432.138676121942</v>
       </c>
       <c r="Q100">
-        <v>-8703.358909947558</v>
+        <v>-7698.138676121942</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.815066116455105</v>
+        <v>1.809385125895844</v>
       </c>
       <c r="T100">
-        <v>34.47018430569242</v>
+        <v>34.37555666297862</v>
       </c>
       <c r="U100">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.03720025562920087</v>
+        <v>0.03989936062301466</v>
       </c>
       <c r="W100">
-        <v>0.2134879578403337</v>
+        <v>0.1984879578403337</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.297602045033607</v>
+        <v>0.3191948849841173</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2472788871792545</v>
+        <v>0.2323152673680693</v>
       </c>
       <c r="C101">
-        <v>-60383.71635251751</v>
+        <v>-59266.63352493465</v>
       </c>
       <c r="D101">
-        <v>14008.0042684628</v>
+        <v>15125.08709604566</v>
       </c>
       <c r="E101">
         <v>61942.18767049515</v>
@@ -9575,37 +9575,37 @@
         <v>5054</v>
       </c>
       <c r="M101">
-        <v>17155.70008262167</v>
+        <v>15995.15427330697</v>
       </c>
       <c r="N101">
-        <v>-12101.70008262167</v>
+        <v>-10941.15427330697</v>
       </c>
       <c r="O101">
-        <v>-1512.712510327709</v>
+        <v>-1367.644284163371</v>
       </c>
       <c r="P101">
-        <v>-10588.98757229396</v>
+        <v>-9573.509989143595</v>
       </c>
       <c r="Q101">
-        <v>-8854.987572293963</v>
+        <v>-7839.509989143595</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.58433223291021</v>
+        <v>3.572970251791687</v>
       </c>
       <c r="T101">
-        <v>68.94036861138484</v>
+        <v>68.75111332595723</v>
       </c>
       <c r="U101">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V101">
-        <v>0.03682449547133015</v>
+        <v>0.03949633677833774</v>
       </c>
       <c r="W101">
-        <v>0.2135712776264166</v>
+        <v>0.1985712776264165</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2945959637706412</v>
+        <v>0.315970694226702</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/ireland/ireland_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_construction_supplies.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08250699649463347</v>
+        <v>0.08249518314481236</v>
       </c>
       <c r="C2">
-        <v>79831.45936970701</v>
+        <v>79074.68861995976</v>
       </c>
       <c r="D2">
-        <v>76853.45936970701</v>
+        <v>76878.20094946462</v>
       </c>
       <c r="E2">
-        <v>-15427.53295048516</v>
+        <v>-14646.02062098031</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>781.5123295048517</v>
       </c>
       <c r="G2">
         <v>2978</v>
@@ -1457,28 +1457,28 @@
         <v>5054</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>43.94960929140838</v>
       </c>
       <c r="N2">
-        <v>5054</v>
+        <v>5010.050390708591</v>
       </c>
       <c r="O2">
-        <v>631.75</v>
+        <v>626.2562988385739</v>
       </c>
       <c r="P2">
-        <v>4422.25</v>
+        <v>4383.794091870017</v>
       </c>
       <c r="Q2">
-        <v>6156.25</v>
+        <v>6117.794091870017</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08250699649463347</v>
+        <v>0.08283142701920726</v>
       </c>
       <c r="T2">
-        <v>0.7154876843770529</v>
+        <v>0.7218114391632138</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>114.9953340083047</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08249518314481236</v>
+        <v>0.08248336979499123</v>
       </c>
       <c r="C3">
-        <v>79074.68861995976</v>
+        <v>78317.93380554991</v>
       </c>
       <c r="D3">
-        <v>76878.20094946462</v>
+        <v>76902.95846455962</v>
       </c>
       <c r="E3">
-        <v>-14646.02062098031</v>
+        <v>-13864.50829147546</v>
       </c>
       <c r="F3">
-        <v>781.5123295048517</v>
+        <v>1563.024659009703</v>
       </c>
       <c r="G3">
         <v>2978</v>
@@ -1539,28 +1539,28 @@
         <v>5054</v>
       </c>
       <c r="M3">
-        <v>43.94960929140838</v>
+        <v>87.89921858281676</v>
       </c>
       <c r="N3">
-        <v>5010.050390708591</v>
+        <v>4966.100781417183</v>
       </c>
       <c r="O3">
-        <v>626.2562988385739</v>
+        <v>620.7625976771479</v>
       </c>
       <c r="P3">
-        <v>4383.794091870017</v>
+        <v>4345.338183740036</v>
       </c>
       <c r="Q3">
-        <v>6117.794091870017</v>
+        <v>6079.338183740036</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08283142701920726</v>
+        <v>0.08316247857489478</v>
       </c>
       <c r="T3">
-        <v>0.7218114391632138</v>
+        <v>0.7282642501695002</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>114.9953340083047</v>
+        <v>57.49766700415238</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08248336979499123</v>
+        <v>0.08247155644517012</v>
       </c>
       <c r="C4">
-        <v>78317.93380554991</v>
+        <v>77561.19494187758</v>
       </c>
       <c r="D4">
-        <v>76902.95846455962</v>
+        <v>76927.73193039212</v>
       </c>
       <c r="E4">
-        <v>-13864.50829147546</v>
+        <v>-13082.99596197061</v>
       </c>
       <c r="F4">
-        <v>1563.024659009703</v>
+        <v>2344.536988514555</v>
       </c>
       <c r="G4">
         <v>2978</v>
@@ -1621,28 +1621,28 @@
         <v>5054</v>
       </c>
       <c r="M4">
-        <v>87.89921858281676</v>
+        <v>131.8488278742252</v>
       </c>
       <c r="N4">
-        <v>4966.100781417183</v>
+        <v>4922.151172125775</v>
       </c>
       <c r="O4">
-        <v>620.7625976771479</v>
+        <v>615.2688965157218</v>
       </c>
       <c r="P4">
-        <v>4345.338183740036</v>
+        <v>4306.882275610053</v>
       </c>
       <c r="Q4">
-        <v>6079.338183740036</v>
+        <v>6040.882275610053</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08316247857489478</v>
+        <v>0.08350035593585423</v>
       </c>
       <c r="T4">
-        <v>0.7282642501695002</v>
+        <v>0.7348501088254009</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>57.49766700415238</v>
+        <v>38.33177800276825</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08247155644517012</v>
+        <v>0.08245974309534899</v>
       </c>
       <c r="C5">
-        <v>77561.19494187758</v>
+        <v>76804.47204436292</v>
       </c>
       <c r="D5">
-        <v>76927.73193039212</v>
+        <v>76952.52136238232</v>
       </c>
       <c r="E5">
-        <v>-13082.99596197061</v>
+        <v>-12301.48363246576</v>
       </c>
       <c r="F5">
-        <v>2344.536988514555</v>
+        <v>3126.049318019407</v>
       </c>
       <c r="G5">
         <v>2978</v>
@@ -1703,28 +1703,28 @@
         <v>5054</v>
       </c>
       <c r="M5">
-        <v>131.8488278742252</v>
+        <v>175.7984371656335</v>
       </c>
       <c r="N5">
-        <v>4922.151172125775</v>
+        <v>4878.201562834366</v>
       </c>
       <c r="O5">
-        <v>615.2688965157218</v>
+        <v>609.7751953542958</v>
       </c>
       <c r="P5">
-        <v>4306.882275610053</v>
+        <v>4268.42636748007</v>
       </c>
       <c r="Q5">
-        <v>6040.882275610053</v>
+        <v>6002.42636748007</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08350035593585423</v>
+        <v>0.08384527240850032</v>
       </c>
       <c r="T5">
-        <v>0.7348501088254009</v>
+        <v>0.7415731728699663</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>38.33177800276825</v>
+        <v>28.74883350207618</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08245974309534899</v>
+        <v>0.08244792974552788</v>
       </c>
       <c r="C6">
-        <v>76804.47204436292</v>
+        <v>76047.76512844575</v>
       </c>
       <c r="D6">
-        <v>76952.52136238232</v>
+        <v>76977.32677597001</v>
       </c>
       <c r="E6">
-        <v>-12301.48363246576</v>
+        <v>-11519.9713029609</v>
       </c>
       <c r="F6">
-        <v>3126.049318019407</v>
+        <v>3907.561647524259</v>
       </c>
       <c r="G6">
         <v>2978</v>
@@ -1785,28 +1785,28 @@
         <v>5054</v>
       </c>
       <c r="M6">
-        <v>175.7984371656335</v>
+        <v>219.7480464570419</v>
       </c>
       <c r="N6">
-        <v>4878.201562834366</v>
+        <v>4834.251953542958</v>
       </c>
       <c r="O6">
-        <v>609.7751953542958</v>
+        <v>604.2814941928698</v>
       </c>
       <c r="P6">
-        <v>4268.42636748007</v>
+        <v>4229.970459350088</v>
       </c>
       <c r="Q6">
-        <v>6002.42636748007</v>
+        <v>5963.970459350088</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08384527240850032</v>
+        <v>0.08419745028057055</v>
       </c>
       <c r="T6">
-        <v>0.7415731728699663</v>
+        <v>0.7484377751049435</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>28.74883350207618</v>
+        <v>22.99906680166094</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08244792974552788</v>
+        <v>0.08243611639570675</v>
       </c>
       <c r="C7">
-        <v>76047.76512844575</v>
+        <v>75291.07420958602</v>
       </c>
       <c r="D7">
-        <v>76977.32677597001</v>
+        <v>77002.14818661513</v>
       </c>
       <c r="E7">
-        <v>-11519.9713029609</v>
+        <v>-10738.45897345605</v>
       </c>
       <c r="F7">
-        <v>3907.561647524259</v>
+        <v>4689.07397702911</v>
       </c>
       <c r="G7">
         <v>2978</v>
@@ -1867,28 +1867,28 @@
         <v>5054</v>
       </c>
       <c r="M7">
-        <v>219.7480464570419</v>
+        <v>263.6976557484503</v>
       </c>
       <c r="N7">
-        <v>4834.251953542958</v>
+        <v>4790.30234425155</v>
       </c>
       <c r="O7">
-        <v>604.2814941928698</v>
+        <v>598.7877930314437</v>
       </c>
       <c r="P7">
-        <v>4229.970459350088</v>
+        <v>4191.514551220106</v>
       </c>
       <c r="Q7">
-        <v>5963.970459350088</v>
+        <v>5925.514551220106</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08419745028057055</v>
+        <v>0.08455712129885502</v>
       </c>
       <c r="T7">
-        <v>0.7484377751049435</v>
+        <v>0.7554484327066224</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.99906680166094</v>
+        <v>19.16588900138412</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08243611639570675</v>
+        <v>0.08242430304588565</v>
       </c>
       <c r="C8">
-        <v>75291.07420958602</v>
+        <v>74534.39930326339</v>
       </c>
       <c r="D8">
-        <v>77002.14818661513</v>
+        <v>77026.98560979735</v>
       </c>
       <c r="E8">
-        <v>-10738.45897345605</v>
+        <v>-9956.9466439512</v>
       </c>
       <c r="F8">
-        <v>4689.07397702911</v>
+        <v>5470.586306533961</v>
       </c>
       <c r="G8">
         <v>2978</v>
@@ -1949,28 +1949,28 @@
         <v>5054</v>
       </c>
       <c r="M8">
-        <v>263.6976557484503</v>
+        <v>307.6472650398586</v>
       </c>
       <c r="N8">
-        <v>4790.30234425155</v>
+        <v>4746.352734960142</v>
       </c>
       <c r="O8">
-        <v>598.7877930314437</v>
+        <v>593.2940918700177</v>
       </c>
       <c r="P8">
-        <v>4191.514551220106</v>
+        <v>4153.058643090124</v>
       </c>
       <c r="Q8">
-        <v>5925.514551220106</v>
+        <v>5887.058643090124</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08455712129885502</v>
+        <v>0.08492452717774777</v>
       </c>
       <c r="T8">
-        <v>0.7554484327066224</v>
+        <v>0.7626098571384449</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.16588900138412</v>
+        <v>16.42790485832925</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08242430304588565</v>
+        <v>0.08241248969606453</v>
       </c>
       <c r="C9">
-        <v>74534.39930326339</v>
+        <v>73777.74042497773</v>
       </c>
       <c r="D9">
-        <v>77026.98560979735</v>
+        <v>77051.83906101655</v>
       </c>
       <c r="E9">
-        <v>-9956.9466439512</v>
+        <v>-9175.434314446349</v>
       </c>
       <c r="F9">
-        <v>5470.586306533962</v>
+        <v>6252.098636038813</v>
       </c>
       <c r="G9">
         <v>2978</v>
@@ -2031,28 +2031,28 @@
         <v>5054</v>
       </c>
       <c r="M9">
-        <v>307.6472650398587</v>
+        <v>351.596874331267</v>
       </c>
       <c r="N9">
-        <v>4746.352734960141</v>
+        <v>4702.403125668733</v>
       </c>
       <c r="O9">
-        <v>593.2940918700176</v>
+        <v>587.8003907085916</v>
       </c>
       <c r="P9">
-        <v>4153.058643090123</v>
+        <v>4114.602734960142</v>
       </c>
       <c r="Q9">
-        <v>5887.058643090123</v>
+        <v>5848.602734960142</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08492452717774777</v>
+        <v>0.08529992014096428</v>
       </c>
       <c r="T9">
-        <v>0.7626098571384449</v>
+        <v>0.7699269647100896</v>
       </c>
       <c r="U9">
         <v>0.0562366166625341</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.42790485832925</v>
+        <v>14.37441675103809</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08241248969606453</v>
+        <v>0.08240067634624339</v>
       </c>
       <c r="C10">
-        <v>73777.74042497773</v>
+        <v>73021.09759024887</v>
       </c>
       <c r="D10">
-        <v>77051.83906101655</v>
+        <v>77076.70855579253</v>
       </c>
       <c r="E10">
-        <v>-9175.434314446349</v>
+        <v>-8393.921984941497</v>
       </c>
       <c r="F10">
-        <v>6252.098636038813</v>
+        <v>7033.610965543665</v>
       </c>
       <c r="G10">
         <v>2978</v>
@@ -2113,28 +2113,28 @@
         <v>5054</v>
       </c>
       <c r="M10">
-        <v>351.596874331267</v>
+        <v>395.5464836226754</v>
       </c>
       <c r="N10">
-        <v>4702.403125668733</v>
+        <v>4658.453516377324</v>
       </c>
       <c r="O10">
-        <v>587.8003907085916</v>
+        <v>582.3066895471655</v>
       </c>
       <c r="P10">
-        <v>4114.602734960142</v>
+        <v>4076.146826830159</v>
       </c>
       <c r="Q10">
-        <v>5848.602734960142</v>
+        <v>5810.146826830159</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08529992014096428</v>
+        <v>0.08568356349897674</v>
       </c>
       <c r="T10">
-        <v>0.7699269647100896</v>
+        <v>0.7774048878327593</v>
       </c>
       <c r="U10">
         <v>0.0562366166625341</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.37441675103809</v>
+        <v>12.77725933425608</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08240067634624339</v>
+        <v>0.08238886299642229</v>
       </c>
       <c r="C11">
-        <v>73021.09759024887</v>
+        <v>72264.47081461646</v>
       </c>
       <c r="D11">
-        <v>77076.70855579253</v>
+        <v>77101.59410966498</v>
       </c>
       <c r="E11">
-        <v>-8393.921984941497</v>
+        <v>-7612.409655436646</v>
       </c>
       <c r="F11">
-        <v>7033.610965543665</v>
+        <v>7815.123295048516</v>
       </c>
       <c r="G11">
         <v>2978</v>
@@ -2195,28 +2195,28 @@
         <v>5054</v>
       </c>
       <c r="M11">
-        <v>395.5464836226754</v>
+        <v>439.4960929140838</v>
       </c>
       <c r="N11">
-        <v>4658.453516377324</v>
+        <v>4614.503907085917</v>
       </c>
       <c r="O11">
-        <v>582.3066895471655</v>
+        <v>576.8129883857396</v>
       </c>
       <c r="P11">
-        <v>4076.146826830159</v>
+        <v>4037.690918700177</v>
       </c>
       <c r="Q11">
-        <v>5810.146826830159</v>
+        <v>5771.690918700177</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08568356349897674</v>
+        <v>0.08607573226494505</v>
       </c>
       <c r="T11">
-        <v>0.7774048878327593</v>
+        <v>0.785048987024822</v>
       </c>
       <c r="U11">
         <v>0.0562366166625341</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.77725933425608</v>
+        <v>11.49953340083048</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08238886299642229</v>
+        <v>0.08237704964660118</v>
       </c>
       <c r="C12">
-        <v>72264.47081461646</v>
+        <v>71507.86011364048</v>
       </c>
       <c r="D12">
-        <v>77101.59410966498</v>
+        <v>77126.49573819384</v>
       </c>
       <c r="E12">
-        <v>-7612.409655436644</v>
+        <v>-6830.897325931794</v>
       </c>
       <c r="F12">
-        <v>7815.123295048517</v>
+        <v>8596.635624553368</v>
       </c>
       <c r="G12">
         <v>2978</v>
@@ -2277,28 +2277,28 @@
         <v>5054</v>
       </c>
       <c r="M12">
-        <v>439.4960929140839</v>
+        <v>483.4457022054922</v>
       </c>
       <c r="N12">
-        <v>4614.503907085917</v>
+        <v>4570.554297794508</v>
       </c>
       <c r="O12">
-        <v>576.8129883857396</v>
+        <v>571.3192872243135</v>
       </c>
       <c r="P12">
-        <v>4037.690918700177</v>
+        <v>3999.235010570194</v>
       </c>
       <c r="Q12">
-        <v>5771.690918700177</v>
+        <v>5733.235010570194</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08607573226494505</v>
+        <v>0.08647671381217109</v>
       </c>
       <c r="T12">
-        <v>0.785048987024822</v>
+        <v>0.7928648637268185</v>
       </c>
       <c r="U12">
         <v>0.0562366166625341</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.49953340083047</v>
+        <v>10.45412127348225</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08237704964660118</v>
+        <v>0.08236523629678005</v>
       </c>
       <c r="C13">
-        <v>71507.86011364048</v>
+        <v>70751.26550290102</v>
       </c>
       <c r="D13">
-        <v>77126.49573819384</v>
+        <v>77151.41345695924</v>
       </c>
       <c r="E13">
-        <v>-6830.897325931794</v>
+        <v>-6049.384996426941</v>
       </c>
       <c r="F13">
-        <v>8596.635624553368</v>
+        <v>9378.14795405822</v>
       </c>
       <c r="G13">
         <v>2978</v>
@@ -2359,28 +2359,28 @@
         <v>5054</v>
       </c>
       <c r="M13">
-        <v>483.4457022054922</v>
+        <v>527.3953114969006</v>
       </c>
       <c r="N13">
-        <v>4570.554297794508</v>
+        <v>4526.604688503099</v>
       </c>
       <c r="O13">
-        <v>571.3192872243135</v>
+        <v>565.8255860628874</v>
       </c>
       <c r="P13">
-        <v>3999.235010570194</v>
+        <v>3960.779102440212</v>
       </c>
       <c r="Q13">
-        <v>5733.235010570194</v>
+        <v>5694.779102440212</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08647671381217109</v>
+        <v>0.08688680857637951</v>
       </c>
       <c r="T13">
-        <v>0.7928648637268185</v>
+        <v>0.8008583739902241</v>
       </c>
       <c r="U13">
         <v>0.0562366166625341</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.45412127348225</v>
+        <v>9.58294450069206</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08236523629678005</v>
+        <v>0.08235342294695892</v>
       </c>
       <c r="C14">
-        <v>70751.26550290102</v>
+        <v>69994.68699799814</v>
       </c>
       <c r="D14">
-        <v>77151.41345695924</v>
+        <v>77176.34728156122</v>
       </c>
       <c r="E14">
-        <v>-6049.384996426941</v>
+        <v>-5267.872666922091</v>
       </c>
       <c r="F14">
-        <v>9378.14795405822</v>
+        <v>10159.66028356307</v>
       </c>
       <c r="G14">
         <v>2978</v>
@@ -2441,28 +2441,28 @@
         <v>5054</v>
       </c>
       <c r="M14">
-        <v>527.3953114969006</v>
+        <v>571.344920788309</v>
       </c>
       <c r="N14">
-        <v>4526.604688503099</v>
+        <v>4482.655079211691</v>
       </c>
       <c r="O14">
-        <v>565.8255860628874</v>
+        <v>560.3318849014614</v>
       </c>
       <c r="P14">
-        <v>3960.779102440212</v>
+        <v>3922.32319431023</v>
       </c>
       <c r="Q14">
-        <v>5694.779102440212</v>
+        <v>5656.32319431023</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08688680857637951</v>
+        <v>0.08730633080643181</v>
       </c>
       <c r="T14">
-        <v>0.8008583739902241</v>
+        <v>0.8090356431102596</v>
       </c>
       <c r="U14">
         <v>0.0562366166625341</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.58294450069206</v>
+        <v>8.845794923715749</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08235342294695892</v>
+        <v>0.08252535959713782</v>
       </c>
       <c r="C15">
-        <v>69994.68699799814</v>
+        <v>68851.85914237745</v>
       </c>
       <c r="D15">
-        <v>77176.34728156122</v>
+        <v>76815.03175544536</v>
       </c>
       <c r="E15">
-        <v>-5267.872666922091</v>
+        <v>-4486.360337417238</v>
       </c>
       <c r="F15">
-        <v>10159.66028356307</v>
+        <v>10941.17261306792</v>
       </c>
       <c r="G15">
         <v>2978</v>
@@ -2523,45 +2523,45 @@
         <v>5054</v>
       </c>
       <c r="M15">
-        <v>571.344920788309</v>
+        <v>631.7062889993192</v>
       </c>
       <c r="N15">
-        <v>4482.655079211691</v>
+        <v>4422.293711000681</v>
       </c>
       <c r="O15">
-        <v>560.3318849014614</v>
+        <v>552.7867138750851</v>
       </c>
       <c r="P15">
-        <v>3922.32319431023</v>
+        <v>3869.506997125595</v>
       </c>
       <c r="Q15">
-        <v>5656.32319431023</v>
+        <v>5603.506997125595</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08730633080643181</v>
+        <v>0.08773560936741556</v>
       </c>
       <c r="T15">
-        <v>0.8090356431102596</v>
+        <v>0.8174030812795983</v>
       </c>
       <c r="U15">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V15">
         <v>0.125</v>
       </c>
       <c r="W15">
-        <v>0.04920703957971734</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>8.845794923715749</v>
+        <v>8.000553561063956</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08252535959713782</v>
+        <v>0.0825266712473167</v>
       </c>
       <c r="C16">
-        <v>68851.85914237745</v>
+        <v>68067.60345370822</v>
       </c>
       <c r="D16">
-        <v>76815.03175544536</v>
+        <v>76812.28839628099</v>
       </c>
       <c r="E16">
-        <v>-4486.360337417238</v>
+        <v>-3704.848007912386</v>
       </c>
       <c r="F16">
-        <v>10941.17261306792</v>
+        <v>11722.68494257278</v>
       </c>
       <c r="G16">
         <v>2978</v>
@@ -2605,28 +2605,28 @@
         <v>5054</v>
       </c>
       <c r="M16">
-        <v>631.7062889993192</v>
+        <v>676.8281667849849</v>
       </c>
       <c r="N16">
-        <v>4422.293711000681</v>
+        <v>4377.171833215015</v>
       </c>
       <c r="O16">
-        <v>552.7867138750851</v>
+        <v>547.1464791518769</v>
       </c>
       <c r="P16">
-        <v>3869.506997125595</v>
+        <v>3830.025354063138</v>
       </c>
       <c r="Q16">
-        <v>5603.506997125595</v>
+        <v>5564.025354063138</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08773560936741556</v>
+        <v>0.08817498860042247</v>
       </c>
       <c r="T16">
-        <v>0.8174030812795983</v>
+        <v>0.8259674003470391</v>
       </c>
       <c r="U16">
         <v>0.05773661666253409</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.000553561063956</v>
+        <v>7.467183323659692</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08252667124731669</v>
+        <v>0.08252798289749558</v>
       </c>
       <c r="C17">
-        <v>68067.60345370825</v>
+        <v>67283.34796098375</v>
       </c>
       <c r="D17">
-        <v>76812.28839628102</v>
+        <v>76809.54523306138</v>
       </c>
       <c r="E17">
-        <v>-3704.848007912387</v>
+        <v>-2923.335678407535</v>
       </c>
       <c r="F17">
-        <v>11722.68494257277</v>
+        <v>12504.19727207763</v>
       </c>
       <c r="G17">
         <v>2978</v>
@@ -2687,28 +2687,28 @@
         <v>5054</v>
       </c>
       <c r="M17">
-        <v>676.8281667849848</v>
+        <v>721.9500445706504</v>
       </c>
       <c r="N17">
-        <v>4377.171833215015</v>
+        <v>4332.049955429349</v>
       </c>
       <c r="O17">
-        <v>547.1464791518769</v>
+        <v>541.5062444286687</v>
       </c>
       <c r="P17">
-        <v>3830.025354063138</v>
+        <v>3790.543711000681</v>
       </c>
       <c r="Q17">
-        <v>5564.025354063138</v>
+        <v>5524.543711000681</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08817498860042246</v>
+        <v>0.08862482924373905</v>
       </c>
       <c r="T17">
-        <v>0.825967400347039</v>
+        <v>0.8347356317732284</v>
       </c>
       <c r="U17">
         <v>0.05773661666253409</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.467183323659693</v>
+        <v>7.000484365930962</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08252798289749558</v>
+        <v>0.08278216954767446</v>
       </c>
       <c r="C18">
-        <v>67283.34796098375</v>
+        <v>65973.90659855974</v>
       </c>
       <c r="D18">
-        <v>76809.54523306138</v>
+        <v>76281.61620014222</v>
       </c>
       <c r="E18">
-        <v>-2923.335678407535</v>
+        <v>-2141.823348902682</v>
       </c>
       <c r="F18">
-        <v>12504.19727207763</v>
+        <v>13285.70960158248</v>
       </c>
       <c r="G18">
         <v>2978</v>
@@ -2769,45 +2769,45 @@
         <v>5054</v>
       </c>
       <c r="M18">
-        <v>721.9500445706504</v>
+        <v>789.6576286790064</v>
       </c>
       <c r="N18">
-        <v>4332.049955429349</v>
+        <v>4264.342371320994</v>
       </c>
       <c r="O18">
-        <v>541.5062444286687</v>
+        <v>533.0427964151243</v>
       </c>
       <c r="P18">
-        <v>3790.543711000681</v>
+        <v>3731.29957490587</v>
       </c>
       <c r="Q18">
-        <v>5524.543711000681</v>
+        <v>5465.29957490587</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08862482924373905</v>
+        <v>0.08908550942062954</v>
       </c>
       <c r="T18">
-        <v>0.8347356317732284</v>
+        <v>0.8437151458843862</v>
       </c>
       <c r="U18">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.05051953957971733</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.000484365930962</v>
+        <v>6.400242100433677</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08278216954767446</v>
+        <v>0.08279835619785333</v>
       </c>
       <c r="C19">
-        <v>65973.90659855974</v>
+        <v>65159.02133135173</v>
       </c>
       <c r="D19">
-        <v>76281.61620014222</v>
+        <v>76248.24326243906</v>
       </c>
       <c r="E19">
-        <v>-2141.823348902682</v>
+        <v>-1360.31101939783</v>
       </c>
       <c r="F19">
-        <v>13285.70960158248</v>
+        <v>14067.22193108733</v>
       </c>
       <c r="G19">
         <v>2978</v>
@@ -2851,28 +2851,28 @@
         <v>5054</v>
       </c>
       <c r="M19">
-        <v>789.6576286790064</v>
+        <v>836.1080774248303</v>
       </c>
       <c r="N19">
-        <v>4264.342371320994</v>
+        <v>4217.89192257517</v>
       </c>
       <c r="O19">
-        <v>533.0427964151243</v>
+        <v>527.2364903218962</v>
       </c>
       <c r="P19">
-        <v>3731.29957490587</v>
+        <v>3690.655432253273</v>
       </c>
       <c r="Q19">
-        <v>5465.29957490587</v>
+        <v>5424.655432253274</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08908550942062954</v>
+        <v>0.08955742569939538</v>
       </c>
       <c r="T19">
-        <v>0.8437151458843862</v>
+        <v>0.8529136725348405</v>
       </c>
       <c r="U19">
         <v>0.05943661666253409</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.400242100433677</v>
+        <v>6.044673094854028</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08279835619785335</v>
+        <v>0.08281454284803222</v>
       </c>
       <c r="C20">
-        <v>65159.0213313517</v>
+        <v>64344.16525245869</v>
       </c>
       <c r="D20">
-        <v>76248.24326243903</v>
+        <v>76214.89951305087</v>
       </c>
       <c r="E20">
-        <v>-1360.311019397832</v>
+        <v>-578.7986898929794</v>
       </c>
       <c r="F20">
-        <v>14067.22193108733</v>
+        <v>14848.73426059218</v>
       </c>
       <c r="G20">
         <v>2978</v>
@@ -2933,28 +2933,28 @@
         <v>5054</v>
       </c>
       <c r="M20">
-        <v>836.1080774248302</v>
+        <v>882.5585261706542</v>
       </c>
       <c r="N20">
-        <v>4217.89192257517</v>
+        <v>4171.441473829345</v>
       </c>
       <c r="O20">
-        <v>527.2364903218962</v>
+        <v>521.4301842286682</v>
       </c>
       <c r="P20">
-        <v>3690.655432253273</v>
+        <v>3650.011289600677</v>
       </c>
       <c r="Q20">
-        <v>5424.655432253274</v>
+        <v>5384.011289600678</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08955742569939538</v>
+        <v>0.09004099423195792</v>
       </c>
       <c r="T20">
-        <v>0.8529136725348405</v>
+        <v>0.8623393233001208</v>
       </c>
       <c r="U20">
         <v>0.05943661666253409</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.044673094854028</v>
+        <v>5.726532405651183</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08281454284803222</v>
+        <v>0.08297072949821109</v>
       </c>
       <c r="C21">
-        <v>64344.16525245869</v>
+        <v>63242.40766521049</v>
       </c>
       <c r="D21">
-        <v>76214.89951305087</v>
+        <v>75894.65425530753</v>
       </c>
       <c r="E21">
-        <v>-578.7986898929794</v>
+        <v>202.7136396118731</v>
       </c>
       <c r="F21">
-        <v>14848.73426059218</v>
+        <v>15630.24659009703</v>
       </c>
       <c r="G21">
         <v>2978</v>
@@ -3015,45 +3015,45 @@
         <v>5054</v>
       </c>
       <c r="M21">
-        <v>882.5585261706542</v>
+        <v>941.5131721885558</v>
       </c>
       <c r="N21">
-        <v>4171.441473829345</v>
+        <v>4112.486827811445</v>
       </c>
       <c r="O21">
-        <v>521.4301842286682</v>
+        <v>514.0608534764306</v>
       </c>
       <c r="P21">
-        <v>3650.011289600677</v>
+        <v>3598.425974335014</v>
       </c>
       <c r="Q21">
-        <v>5384.011289600678</v>
+        <v>5332.425974335014</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09004099423195792</v>
+        <v>0.09053665197783453</v>
       </c>
       <c r="T21">
-        <v>0.8623393233001208</v>
+        <v>0.8720006153345332</v>
       </c>
       <c r="U21">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V21">
         <v>0.125</v>
       </c>
       <c r="W21">
-        <v>0.05200703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>5.726532405651183</v>
+        <v>5.367954638650389</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08297072949821109</v>
+        <v>0.08299391614838998</v>
       </c>
       <c r="C22">
-        <v>63242.40766521049</v>
+        <v>62413.58268404388</v>
       </c>
       <c r="D22">
-        <v>75894.65425530753</v>
+        <v>75847.34160364576</v>
       </c>
       <c r="E22">
-        <v>202.7136396118731</v>
+        <v>984.2259691167237</v>
       </c>
       <c r="F22">
-        <v>15630.24659009703</v>
+        <v>16411.75891960189</v>
       </c>
       <c r="G22">
         <v>2978</v>
@@ -3097,28 +3097,28 @@
         <v>5054</v>
       </c>
       <c r="M22">
-        <v>941.5131721885558</v>
+        <v>988.5888307979835</v>
       </c>
       <c r="N22">
-        <v>4112.486827811445</v>
+        <v>4065.411169202016</v>
       </c>
       <c r="O22">
-        <v>514.0608534764306</v>
+        <v>508.1763961502521</v>
       </c>
       <c r="P22">
-        <v>3598.425974335014</v>
+        <v>3557.234773051764</v>
       </c>
       <c r="Q22">
-        <v>5332.425974335014</v>
+        <v>5291.234773051765</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09053665197783453</v>
+        <v>0.09104485802107512</v>
       </c>
       <c r="T22">
-        <v>0.8720006153345332</v>
+        <v>0.881906497040703</v>
       </c>
       <c r="U22">
         <v>0.0602366166625341</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.367954638650389</v>
+        <v>5.112337751095608</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08299391614838998</v>
+        <v>0.08301710279856887</v>
       </c>
       <c r="C23">
-        <v>62413.58268404388</v>
+        <v>61584.81665544587</v>
       </c>
       <c r="D23">
-        <v>75847.34160364576</v>
+        <v>75800.08790455261</v>
       </c>
       <c r="E23">
-        <v>984.2259691167237</v>
+        <v>1765.738298621574</v>
       </c>
       <c r="F23">
-        <v>16411.75891960189</v>
+        <v>17193.27124910674</v>
       </c>
       <c r="G23">
         <v>2978</v>
@@ -3179,28 +3179,28 @@
         <v>5054</v>
       </c>
       <c r="M23">
-        <v>988.5888307979835</v>
+        <v>1035.664489407411</v>
       </c>
       <c r="N23">
-        <v>4065.411169202016</v>
+        <v>4018.335510592588</v>
       </c>
       <c r="O23">
-        <v>508.1763961502521</v>
+        <v>502.2919388240736</v>
       </c>
       <c r="P23">
-        <v>3557.234773051764</v>
+        <v>3516.043571768515</v>
       </c>
       <c r="Q23">
-        <v>5291.234773051765</v>
+        <v>5250.043571768515</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09104485802107512</v>
+        <v>0.09156609498850135</v>
       </c>
       <c r="T23">
-        <v>0.8819064970407028</v>
+        <v>0.8920663757136974</v>
       </c>
       <c r="U23">
         <v>0.0602366166625341</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.112337751095608</v>
+        <v>4.879958762409444</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08301710279856887</v>
+        <v>0.08304028944874775</v>
       </c>
       <c r="C24">
-        <v>61584.81665544587</v>
+        <v>60756.10946930086</v>
       </c>
       <c r="D24">
-        <v>75800.08790455261</v>
+        <v>75752.89304791245</v>
       </c>
       <c r="E24">
-        <v>1765.738298621574</v>
+        <v>2547.250628126429</v>
       </c>
       <c r="F24">
-        <v>17193.27124910674</v>
+        <v>17974.78357861159</v>
       </c>
       <c r="G24">
         <v>2978</v>
@@ -3261,28 +3261,28 @@
         <v>5054</v>
       </c>
       <c r="M24">
-        <v>1035.664489407411</v>
+        <v>1082.740148016839</v>
       </c>
       <c r="N24">
-        <v>4018.335510592588</v>
+        <v>3971.259851983161</v>
       </c>
       <c r="O24">
-        <v>502.2919388240736</v>
+        <v>496.4074814978951</v>
       </c>
       <c r="P24">
-        <v>3516.043571768515</v>
+        <v>3474.852370485266</v>
       </c>
       <c r="Q24">
-        <v>5250.043571768515</v>
+        <v>5208.852370485266</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09156609498850135</v>
+        <v>0.09210087057845812</v>
       </c>
       <c r="T24">
-        <v>0.8920663757136974</v>
+        <v>0.902490147339237</v>
       </c>
       <c r="U24">
         <v>0.0602366166625341</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.879958762409444</v>
+        <v>4.667786642304685</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08304028944874775</v>
+        <v>0.08306347609892663</v>
       </c>
       <c r="C25">
-        <v>60756.10946930086</v>
+        <v>59927.4610157673</v>
       </c>
       <c r="D25">
-        <v>75752.89304791245</v>
+        <v>75705.75692388375</v>
       </c>
       <c r="E25">
-        <v>2547.250628126429</v>
+        <v>3328.762957631279</v>
       </c>
       <c r="F25">
-        <v>17974.78357861159</v>
+        <v>18756.29590811644</v>
       </c>
       <c r="G25">
         <v>2978</v>
@@ -3343,28 +3343,28 @@
         <v>5054</v>
       </c>
       <c r="M25">
-        <v>1082.740148016839</v>
+        <v>1129.815806626267</v>
       </c>
       <c r="N25">
-        <v>3971.259851983161</v>
+        <v>3924.184193373733</v>
       </c>
       <c r="O25">
-        <v>496.4074814978951</v>
+        <v>490.5230241717167</v>
       </c>
       <c r="P25">
-        <v>3474.852370485266</v>
+        <v>3433.661169202016</v>
       </c>
       <c r="Q25">
-        <v>5208.852370485266</v>
+        <v>5167.661169202016</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09210087057845812</v>
+        <v>0.09264971921025589</v>
       </c>
       <c r="T25">
-        <v>0.902490147339237</v>
+        <v>0.9131882287443965</v>
       </c>
       <c r="U25">
         <v>0.0602366166625341</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.667786642304685</v>
+        <v>4.473295532208658</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08306347609892661</v>
+        <v>0.08308666274910551</v>
       </c>
       <c r="C26">
-        <v>59927.46101576735</v>
+        <v>59098.87118527684</v>
       </c>
       <c r="D26">
-        <v>75705.75692388379</v>
+        <v>75658.67942289813</v>
       </c>
       <c r="E26">
-        <v>3328.762957631279</v>
+        <v>4110.27528713613</v>
       </c>
       <c r="F26">
-        <v>18756.29590811644</v>
+        <v>19537.80823762129</v>
       </c>
       <c r="G26">
         <v>2978</v>
@@ -3425,28 +3425,28 @@
         <v>5054</v>
       </c>
       <c r="M26">
-        <v>1129.815806626267</v>
+        <v>1176.891465235695</v>
       </c>
       <c r="N26">
-        <v>3924.184193373733</v>
+        <v>3877.108534764306</v>
       </c>
       <c r="O26">
-        <v>490.5230241717167</v>
+        <v>484.6385668455382</v>
       </c>
       <c r="P26">
-        <v>3433.661169202016</v>
+        <v>3392.469967918767</v>
       </c>
       <c r="Q26">
-        <v>5167.661169202016</v>
+        <v>5126.469967918767</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09264971921025586</v>
+        <v>0.09321320380556823</v>
       </c>
       <c r="T26">
-        <v>0.9131882287443963</v>
+        <v>0.9241715923203599</v>
       </c>
       <c r="U26">
         <v>0.0602366166625341</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.473295532208658</v>
+        <v>4.294363710920312</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08308666274910551</v>
+        <v>0.08333734939928439</v>
       </c>
       <c r="C27">
-        <v>59098.87118527684</v>
+        <v>57812.08554252506</v>
       </c>
       <c r="D27">
-        <v>75658.67942289813</v>
+        <v>75153.4061096512</v>
       </c>
       <c r="E27">
-        <v>4110.27528713613</v>
+        <v>4891.787616640981</v>
       </c>
       <c r="F27">
-        <v>19537.80823762129</v>
+        <v>20319.32056712614</v>
       </c>
       <c r="G27">
         <v>2978</v>
@@ -3507,45 +3507,45 @@
         <v>5054</v>
       </c>
       <c r="M27">
-        <v>1176.891465235695</v>
+        <v>1244.286444412249</v>
       </c>
       <c r="N27">
-        <v>3877.108534764306</v>
+        <v>3809.713555587751</v>
       </c>
       <c r="O27">
-        <v>484.6385668455382</v>
+        <v>476.2141944484689</v>
       </c>
       <c r="P27">
-        <v>3392.469967918767</v>
+        <v>3333.499361139282</v>
       </c>
       <c r="Q27">
-        <v>5126.469967918767</v>
+        <v>5067.499361139282</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09321320380556823</v>
+        <v>0.09379191771426741</v>
       </c>
       <c r="T27">
-        <v>0.9241715923203599</v>
+        <v>0.9354518035605388</v>
       </c>
       <c r="U27">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.05270703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.294363710920312</v>
+        <v>4.061765699285833</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08333734939928439</v>
+        <v>0.08336928604946327</v>
       </c>
       <c r="C28">
-        <v>57812.08554252506</v>
+        <v>56966.68730266474</v>
       </c>
       <c r="D28">
-        <v>75153.4061096512</v>
+        <v>75089.52019929573</v>
       </c>
       <c r="E28">
-        <v>4891.787616640981</v>
+        <v>5673.299946145835</v>
       </c>
       <c r="F28">
-        <v>20319.32056712614</v>
+        <v>21100.832896631</v>
       </c>
       <c r="G28">
         <v>2978</v>
@@ -3589,28 +3589,28 @@
         <v>5054</v>
       </c>
       <c r="M28">
-        <v>1244.286444412249</v>
+        <v>1292.143615351181</v>
       </c>
       <c r="N28">
-        <v>3809.713555587751</v>
+        <v>3761.856384648819</v>
       </c>
       <c r="O28">
-        <v>476.2141944484689</v>
+        <v>470.2320480811023</v>
       </c>
       <c r="P28">
-        <v>3333.499361139282</v>
+        <v>3291.624336567716</v>
       </c>
       <c r="Q28">
-        <v>5067.499361139282</v>
+        <v>5025.624336567716</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09379191771426741</v>
+        <v>0.09438648679854739</v>
       </c>
       <c r="T28">
-        <v>0.9354518035605388</v>
+        <v>0.9470410616840101</v>
       </c>
       <c r="U28">
         <v>0.0612366166625341</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.061765699285833</v>
+        <v>3.911329932645617</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08336928604946327</v>
+        <v>0.08340122269964215</v>
       </c>
       <c r="C29">
-        <v>56966.68730266474</v>
+        <v>56121.39758597594</v>
       </c>
       <c r="D29">
-        <v>75089.52019929573</v>
+        <v>75025.74281211178</v>
       </c>
       <c r="E29">
-        <v>5673.299946145835</v>
+        <v>6454.812275650685</v>
       </c>
       <c r="F29">
-        <v>21100.832896631</v>
+        <v>21882.34522613585</v>
       </c>
       <c r="G29">
         <v>2978</v>
@@ -3671,28 +3671,28 @@
         <v>5054</v>
       </c>
       <c r="M29">
-        <v>1292.143615351181</v>
+        <v>1340.000786290114</v>
       </c>
       <c r="N29">
-        <v>3761.856384648819</v>
+        <v>3713.999213709886</v>
       </c>
       <c r="O29">
-        <v>470.2320480811023</v>
+        <v>464.2499017137358</v>
       </c>
       <c r="P29">
-        <v>3291.624336567716</v>
+        <v>3249.74931199615</v>
       </c>
       <c r="Q29">
-        <v>5025.624336567716</v>
+        <v>4983.749311996151</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09438648679854739</v>
+        <v>0.09499757169072404</v>
       </c>
       <c r="T29">
-        <v>0.9470410616840101</v>
+        <v>0.9589522436442446</v>
       </c>
       <c r="U29">
         <v>0.0612366166625341</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.911329932645617</v>
+        <v>3.771639577908274</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08340122269964215</v>
+        <v>0.08343315934982103</v>
       </c>
       <c r="C30">
-        <v>56121.39758597594</v>
+        <v>55276.21611617041</v>
       </c>
       <c r="D30">
-        <v>75025.74281211178</v>
+        <v>74962.07367181111</v>
       </c>
       <c r="E30">
-        <v>6454.812275650685</v>
+        <v>7236.32460515554</v>
       </c>
       <c r="F30">
-        <v>21882.34522613585</v>
+        <v>22663.8575556407</v>
       </c>
       <c r="G30">
         <v>2978</v>
@@ -3753,28 +3753,28 @@
         <v>5054</v>
       </c>
       <c r="M30">
-        <v>1340.000786290114</v>
+        <v>1387.857957229047</v>
       </c>
       <c r="N30">
-        <v>3713.999213709886</v>
+        <v>3666.142042770954</v>
       </c>
       <c r="O30">
-        <v>464.2499017137358</v>
+        <v>458.2677553463692</v>
       </c>
       <c r="P30">
-        <v>3249.74931199615</v>
+        <v>3207.874287424585</v>
       </c>
       <c r="Q30">
-        <v>4983.749311996151</v>
+        <v>4941.874287424585</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09499757169072404</v>
+        <v>0.09562587024183522</v>
       </c>
       <c r="T30">
-        <v>0.9589522436442446</v>
+        <v>0.97119895185688</v>
       </c>
       <c r="U30">
         <v>0.0612366166625341</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.771639577908274</v>
+        <v>3.641583040739023</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08343315934982103</v>
+        <v>0.08346509599999991</v>
       </c>
       <c r="C31">
-        <v>55276.21611617041</v>
+        <v>54431.14261789701</v>
       </c>
       <c r="D31">
-        <v>74962.07367181111</v>
+        <v>74898.51250304256</v>
       </c>
       <c r="E31">
-        <v>7236.324605155536</v>
+        <v>8017.836934660387</v>
       </c>
       <c r="F31">
-        <v>22663.8575556407</v>
+        <v>23445.36988514555</v>
       </c>
       <c r="G31">
         <v>2978</v>
@@ -3835,28 +3835,28 @@
         <v>5054</v>
       </c>
       <c r="M31">
-        <v>1387.857957229046</v>
+        <v>1435.715128167979</v>
       </c>
       <c r="N31">
-        <v>3666.142042770954</v>
+        <v>3618.284871832021</v>
       </c>
       <c r="O31">
-        <v>458.2677553463692</v>
+        <v>452.2856089790026</v>
       </c>
       <c r="P31">
-        <v>3207.874287424585</v>
+        <v>3165.999262853019</v>
       </c>
       <c r="Q31">
-        <v>4941.874287424585</v>
+        <v>4899.999262853018</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09562587024183522</v>
+        <v>0.09627212018012102</v>
       </c>
       <c r="T31">
-        <v>0.9711989518568799</v>
+        <v>0.9837955660184478</v>
       </c>
       <c r="U31">
         <v>0.0612366166625341</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.641583040739023</v>
+        <v>3.520196939381056</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08346509599999991</v>
+        <v>0.0834970326501788</v>
       </c>
       <c r="C32">
-        <v>54431.14261789701</v>
+        <v>53586.17681673759</v>
       </c>
       <c r="D32">
-        <v>74898.51250304256</v>
+        <v>74835.05903138799</v>
       </c>
       <c r="E32">
-        <v>8017.836934660387</v>
+        <v>8799.349264165241</v>
       </c>
       <c r="F32">
-        <v>23445.36988514555</v>
+        <v>24226.8822146504</v>
       </c>
       <c r="G32">
         <v>2978</v>
@@ -3917,28 +3917,28 @@
         <v>5054</v>
       </c>
       <c r="M32">
-        <v>1435.715128167979</v>
+        <v>1483.572299106912</v>
       </c>
       <c r="N32">
-        <v>3618.284871832021</v>
+        <v>3570.427700893089</v>
       </c>
       <c r="O32">
-        <v>452.2856089790026</v>
+        <v>446.3034626116361</v>
       </c>
       <c r="P32">
-        <v>3165.999262853019</v>
+        <v>3124.124238281453</v>
       </c>
       <c r="Q32">
-        <v>4899.999262853018</v>
+        <v>4858.124238281453</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09627212018012102</v>
+        <v>0.09693710200067598</v>
       </c>
       <c r="T32">
-        <v>0.9837955660184478</v>
+        <v>0.9967572994310756</v>
       </c>
       <c r="U32">
         <v>0.0612366166625341</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.520196939381056</v>
+        <v>3.406642199401022</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0834970326501788</v>
+        <v>0.08352896930035769</v>
       </c>
       <c r="C33">
-        <v>53586.17681673759</v>
+        <v>52741.3184392033</v>
       </c>
       <c r="D33">
-        <v>74835.05903138799</v>
+        <v>74771.71298335855</v>
       </c>
       <c r="E33">
-        <v>8799.349264165241</v>
+        <v>9580.861593670092</v>
       </c>
       <c r="F33">
-        <v>24226.8822146504</v>
+        <v>25008.39454415525</v>
       </c>
       <c r="G33">
         <v>2978</v>
@@ -3999,28 +3999,28 @@
         <v>5054</v>
       </c>
       <c r="M33">
-        <v>1483.572299106912</v>
+        <v>1531.429470045844</v>
       </c>
       <c r="N33">
-        <v>3570.427700893089</v>
+        <v>3522.570529954156</v>
       </c>
       <c r="O33">
-        <v>446.3034626116361</v>
+        <v>440.3213162442694</v>
       </c>
       <c r="P33">
-        <v>3124.124238281453</v>
+        <v>3082.249213709886</v>
       </c>
       <c r="Q33">
-        <v>4858.124238281453</v>
+        <v>4816.249213709886</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09693710200067598</v>
+        <v>0.09762164211007079</v>
       </c>
       <c r="T33">
-        <v>0.9967572994310756</v>
+        <v>1.010100260297016</v>
       </c>
       <c r="U33">
         <v>0.0612366166625341</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.406642199401022</v>
+        <v>3.300184630669739</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08352896930035769</v>
+        <v>0.08356090595053654</v>
       </c>
       <c r="C34">
-        <v>52741.3184392033</v>
+        <v>51896.56721273047</v>
       </c>
       <c r="D34">
-        <v>74771.71298335855</v>
+        <v>74708.47408639058</v>
       </c>
       <c r="E34">
-        <v>9580.861593670092</v>
+        <v>10362.37392317495</v>
       </c>
       <c r="F34">
-        <v>25008.39454415525</v>
+        <v>25789.90687366011</v>
       </c>
       <c r="G34">
         <v>2978</v>
@@ -4081,28 +4081,28 @@
         <v>5054</v>
       </c>
       <c r="M34">
-        <v>1531.429470045844</v>
+        <v>1579.286640984777</v>
       </c>
       <c r="N34">
-        <v>3522.570529954156</v>
+        <v>3474.713359015223</v>
       </c>
       <c r="O34">
-        <v>440.3213162442694</v>
+        <v>434.3391698769028</v>
       </c>
       <c r="P34">
-        <v>3082.249213709886</v>
+        <v>3040.37418913832</v>
       </c>
       <c r="Q34">
-        <v>4816.249213709886</v>
+        <v>4774.37418913832</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09762164211007079</v>
+        <v>0.09832661625258185</v>
       </c>
       <c r="T34">
-        <v>1.010100260297016</v>
+        <v>1.023841518502238</v>
       </c>
       <c r="U34">
         <v>0.0612366166625341</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.300184630669739</v>
+        <v>3.200179035800959</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08356090595053654</v>
+        <v>0.08359284260071544</v>
       </c>
       <c r="C35">
-        <v>51896.56721273047</v>
+        <v>51051.92286567659</v>
       </c>
       <c r="D35">
-        <v>74708.47408639058</v>
+        <v>74645.34206884155</v>
       </c>
       <c r="E35">
-        <v>10362.37392317495</v>
+        <v>11143.8862526798</v>
       </c>
       <c r="F35">
-        <v>25789.90687366011</v>
+        <v>26571.41920316496</v>
       </c>
       <c r="G35">
         <v>2978</v>
@@ -4163,28 +4163,28 @@
         <v>5054</v>
       </c>
       <c r="M35">
-        <v>1579.286640984777</v>
+        <v>1627.14381192371</v>
       </c>
       <c r="N35">
-        <v>3474.713359015223</v>
+        <v>3426.85618807629</v>
       </c>
       <c r="O35">
-        <v>434.3391698769028</v>
+        <v>428.3570235095362</v>
       </c>
       <c r="P35">
-        <v>3040.37418913832</v>
+        <v>2998.499164566754</v>
       </c>
       <c r="Q35">
-        <v>4774.37418913832</v>
+        <v>4732.499164566754</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09832661625258185</v>
+        <v>0.09905295324789629</v>
       </c>
       <c r="T35">
-        <v>1.023841518502238</v>
+        <v>1.037999178471255</v>
       </c>
       <c r="U35">
         <v>0.0612366166625341</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.200179035800959</v>
+        <v>3.106056122983284</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08359284260071544</v>
+        <v>0.08362477925089432</v>
       </c>
       <c r="C36">
-        <v>51051.92286567659</v>
+        <v>50207.38512731681</v>
       </c>
       <c r="D36">
-        <v>74645.34206884155</v>
+        <v>74582.31665998662</v>
       </c>
       <c r="E36">
-        <v>11143.8862526798</v>
+        <v>11925.39858218465</v>
       </c>
       <c r="F36">
-        <v>26571.41920316496</v>
+        <v>27352.93153266981</v>
       </c>
       <c r="G36">
         <v>2978</v>
@@ -4245,28 +4245,28 @@
         <v>5054</v>
       </c>
       <c r="M36">
-        <v>1627.14381192371</v>
+        <v>1675.000982862643</v>
       </c>
       <c r="N36">
-        <v>3426.85618807629</v>
+        <v>3378.999017137357</v>
       </c>
       <c r="O36">
-        <v>428.3570235095362</v>
+        <v>422.3748771421697</v>
       </c>
       <c r="P36">
-        <v>2998.499164566754</v>
+        <v>2956.624139995188</v>
       </c>
       <c r="Q36">
-        <v>4732.499164566754</v>
+        <v>4690.624139995188</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09905295324789629</v>
+        <v>0.09980163907383578</v>
       </c>
       <c r="T36">
-        <v>1.037999178471255</v>
+        <v>1.052592458747011</v>
       </c>
       <c r="U36">
         <v>0.0612366166625341</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.106056122983284</v>
+        <v>3.017311662326619</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08362477925089432</v>
+        <v>0.08444421590107319</v>
       </c>
       <c r="C37">
-        <v>50207.38512731681</v>
+        <v>47844.38169231529</v>
       </c>
       <c r="D37">
-        <v>74582.31665998662</v>
+        <v>73000.82555448996</v>
       </c>
       <c r="E37">
-        <v>11925.39858218465</v>
+        <v>12706.9109116895</v>
       </c>
       <c r="F37">
-        <v>27352.93153266981</v>
+        <v>28134.44386217466</v>
       </c>
       <c r="G37">
         <v>2978</v>
@@ -4327,45 +4327,45 @@
         <v>5054</v>
       </c>
       <c r="M37">
-        <v>1675.000982862643</v>
+        <v>1793.194263457012</v>
       </c>
       <c r="N37">
-        <v>3378.999017137357</v>
+        <v>3260.805736542989</v>
       </c>
       <c r="O37">
-        <v>422.3748771421697</v>
+        <v>407.6007170678736</v>
       </c>
       <c r="P37">
-        <v>2956.624139995188</v>
+        <v>2853.205019475115</v>
       </c>
       <c r="Q37">
-        <v>4690.624139995188</v>
+        <v>4587.205019475115</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09980163907383578</v>
+        <v>0.1005737213318359</v>
       </c>
       <c r="T37">
-        <v>1.052592458747011</v>
+        <v>1.067641779031384</v>
       </c>
       <c r="U37">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.05358203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.017311662326619</v>
+        <v>2.818434178044179</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08444421590107321</v>
+        <v>0.08449802755125208</v>
       </c>
       <c r="C38">
-        <v>47844.38169231527</v>
+        <v>46961.35786116337</v>
       </c>
       <c r="D38">
-        <v>73000.82555448993</v>
+        <v>72899.31405284288</v>
       </c>
       <c r="E38">
-        <v>12706.9109116895</v>
+        <v>13488.42324119435</v>
       </c>
       <c r="F38">
-        <v>28134.44386217466</v>
+        <v>28915.95619167951</v>
       </c>
       <c r="G38">
         <v>2978</v>
@@ -4409,28 +4409,28 @@
         <v>5054</v>
       </c>
       <c r="M38">
-        <v>1793.194263457011</v>
+        <v>1843.005215219706</v>
       </c>
       <c r="N38">
-        <v>3260.805736542989</v>
+        <v>3210.994784780294</v>
       </c>
       <c r="O38">
-        <v>407.6007170678736</v>
+        <v>401.3743480975368</v>
       </c>
       <c r="P38">
-        <v>2853.205019475115</v>
+        <v>2809.620436682757</v>
       </c>
       <c r="Q38">
-        <v>4587.205019475115</v>
+        <v>4543.620436682757</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1005737213318359</v>
+        <v>0.101370314137709</v>
       </c>
       <c r="T38">
-        <v>1.067641779031384</v>
+        <v>1.083168855515261</v>
       </c>
       <c r="U38">
         <v>0.06373661666253409</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.818434178044179</v>
+        <v>2.742260281340283</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08449802755125208</v>
+        <v>0.08455183920143096</v>
       </c>
       <c r="C39">
-        <v>46961.35786116337</v>
+        <v>46078.61595218742</v>
       </c>
       <c r="D39">
-        <v>72899.31405284288</v>
+        <v>72798.08447337178</v>
       </c>
       <c r="E39">
-        <v>13488.42324119435</v>
+        <v>14269.9355706992</v>
       </c>
       <c r="F39">
-        <v>28915.95619167951</v>
+        <v>29697.46852118436</v>
       </c>
       <c r="G39">
         <v>2978</v>
@@ -4491,28 +4491,28 @@
         <v>5054</v>
       </c>
       <c r="M39">
-        <v>1843.005215219706</v>
+        <v>1892.816166982401</v>
       </c>
       <c r="N39">
-        <v>3210.994784780294</v>
+        <v>3161.183833017599</v>
       </c>
       <c r="O39">
-        <v>401.3743480975368</v>
+        <v>395.1479791271998</v>
       </c>
       <c r="P39">
-        <v>2809.620436682757</v>
+        <v>2766.035853890399</v>
       </c>
       <c r="Q39">
-        <v>4543.620436682757</v>
+        <v>4500.035853890398</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.101370314137709</v>
+        <v>0.1021926034857071</v>
       </c>
       <c r="T39">
-        <v>1.083168855515261</v>
+        <v>1.099196805434101</v>
       </c>
       <c r="U39">
         <v>0.06373661666253409</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.742260281340283</v>
+        <v>2.670095537094486</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08455183920143096</v>
+        <v>0.08460565085160984</v>
       </c>
       <c r="C40">
-        <v>46078.61595218742</v>
+        <v>45196.1547925662</v>
       </c>
       <c r="D40">
-        <v>72798.08447337178</v>
+        <v>72697.13564325542</v>
       </c>
       <c r="E40">
-        <v>14269.9355706992</v>
+        <v>15051.44790020405</v>
       </c>
       <c r="F40">
-        <v>29697.46852118436</v>
+        <v>30478.98085068922</v>
       </c>
       <c r="G40">
         <v>2978</v>
@@ -4573,28 +4573,28 @@
         <v>5054</v>
       </c>
       <c r="M40">
-        <v>1892.816166982401</v>
+        <v>1942.627118745096</v>
       </c>
       <c r="N40">
-        <v>3161.183833017599</v>
+        <v>3111.372881254904</v>
       </c>
       <c r="O40">
-        <v>395.1479791271998</v>
+        <v>388.921610156863</v>
       </c>
       <c r="P40">
-        <v>2766.035853890399</v>
+        <v>2722.451271098041</v>
       </c>
       <c r="Q40">
-        <v>4500.035853890398</v>
+        <v>4456.451271098042</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1021926034857071</v>
+        <v>0.1030418531401969</v>
       </c>
       <c r="T40">
-        <v>1.099196805434101</v>
+        <v>1.115750261907658</v>
       </c>
       <c r="U40">
         <v>0.06373661666253409</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.670095537094486</v>
+        <v>2.601631548963858</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08460565085160984</v>
+        <v>0.08465946250178873</v>
       </c>
       <c r="C41">
-        <v>45196.1547925662</v>
+        <v>44313.97321597484</v>
       </c>
       <c r="D41">
-        <v>72697.13564325542</v>
+        <v>72596.46639616891</v>
       </c>
       <c r="E41">
-        <v>15051.44790020405</v>
+        <v>15832.96022970891</v>
       </c>
       <c r="F41">
-        <v>30478.98085068922</v>
+        <v>31260.49318019407</v>
       </c>
       <c r="G41">
         <v>2978</v>
@@ -4655,28 +4655,28 @@
         <v>5054</v>
       </c>
       <c r="M41">
-        <v>1942.627118745096</v>
+        <v>1992.438070507791</v>
       </c>
       <c r="N41">
-        <v>3111.372881254904</v>
+        <v>3061.561929492209</v>
       </c>
       <c r="O41">
-        <v>388.921610156863</v>
+        <v>382.6952411865262</v>
       </c>
       <c r="P41">
-        <v>2722.451271098041</v>
+        <v>2678.866688305683</v>
       </c>
       <c r="Q41">
-        <v>4456.451271098042</v>
+        <v>4412.866688305683</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1030418531401969</v>
+        <v>0.103919411116503</v>
       </c>
       <c r="T41">
-        <v>1.115750261907658</v>
+        <v>1.132855500263667</v>
       </c>
       <c r="U41">
         <v>0.06373661666253409</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.601631548963858</v>
+        <v>2.536590760239761</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08465946250178873</v>
+        <v>0.08596889915196762</v>
       </c>
       <c r="C42">
-        <v>44313.97321597484</v>
+        <v>41165.94161958668</v>
       </c>
       <c r="D42">
-        <v>72596.46639616891</v>
+        <v>70229.9471292856</v>
       </c>
       <c r="E42">
-        <v>15832.96022970891</v>
+        <v>16614.47255921376</v>
       </c>
       <c r="F42">
-        <v>31260.49318019407</v>
+        <v>32042.00550969892</v>
       </c>
       <c r="G42">
         <v>2978</v>
@@ -4737,45 +4737,45 @@
         <v>5054</v>
       </c>
       <c r="M42">
-        <v>1992.438070507791</v>
+        <v>2154.396041554432</v>
       </c>
       <c r="N42">
-        <v>3061.561929492209</v>
+        <v>2899.603958445568</v>
       </c>
       <c r="O42">
-        <v>382.6952411865262</v>
+        <v>362.4504948056961</v>
       </c>
       <c r="P42">
-        <v>2678.866688305683</v>
+        <v>2537.153463639872</v>
       </c>
       <c r="Q42">
-        <v>4412.866688305683</v>
+        <v>4271.153463639872</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.103919411116503</v>
+        <v>0.1048267168208195</v>
       </c>
       <c r="T42">
-        <v>1.132855500263667</v>
+        <v>1.150540577208015</v>
       </c>
       <c r="U42">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V42">
         <v>0.125</v>
       </c>
       <c r="W42">
-        <v>0.05576953957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.536590760239761</v>
+        <v>2.345901079707451</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08596889915196762</v>
+        <v>0.08605333580214648</v>
       </c>
       <c r="C43">
-        <v>41165.94161958668</v>
+        <v>40237.11276687534</v>
       </c>
       <c r="D43">
-        <v>70229.9471292856</v>
+        <v>70082.63060607911</v>
       </c>
       <c r="E43">
-        <v>16614.47255921376</v>
+        <v>17395.98488871861</v>
       </c>
       <c r="F43">
-        <v>32042.00550969892</v>
+        <v>32823.51783920377</v>
       </c>
       <c r="G43">
         <v>2978</v>
@@ -4819,28 +4819,28 @@
         <v>5054</v>
       </c>
       <c r="M43">
-        <v>2154.396041554432</v>
+        <v>2206.942286470393</v>
       </c>
       <c r="N43">
-        <v>2899.603958445568</v>
+        <v>2847.057713529607</v>
       </c>
       <c r="O43">
-        <v>362.4504948056961</v>
+        <v>355.8822141912008</v>
       </c>
       <c r="P43">
-        <v>2537.153463639872</v>
+        <v>2491.175499338406</v>
       </c>
       <c r="Q43">
-        <v>4271.153463639872</v>
+        <v>4225.175499338406</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1048267168208195</v>
+        <v>0.1057653089287331</v>
       </c>
       <c r="T43">
-        <v>1.150540577208015</v>
+        <v>1.168835484391824</v>
       </c>
       <c r="U43">
         <v>0.0672366166625341</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.345901079707451</v>
+        <v>2.290046292095369</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0860533358021465</v>
+        <v>0.08719127245232539</v>
       </c>
       <c r="C44">
-        <v>40237.11276687531</v>
+        <v>37528.87557044443</v>
       </c>
       <c r="D44">
-        <v>70082.63060607908</v>
+        <v>68155.90573915305</v>
       </c>
       <c r="E44">
-        <v>17395.98488871861</v>
+        <v>18177.49721822346</v>
       </c>
       <c r="F44">
-        <v>32823.51783920377</v>
+        <v>33605.03016870862</v>
       </c>
       <c r="G44">
         <v>2978</v>
@@ -4901,45 +4901,45 @@
         <v>5054</v>
       </c>
       <c r="M44">
-        <v>2206.942286470393</v>
+        <v>2353.582615858739</v>
       </c>
       <c r="N44">
-        <v>2847.057713529607</v>
+        <v>2700.417384141261</v>
       </c>
       <c r="O44">
-        <v>355.8822141912008</v>
+        <v>337.5521730176577</v>
       </c>
       <c r="P44">
-        <v>2491.175499338406</v>
+        <v>2362.865211123603</v>
       </c>
       <c r="Q44">
-        <v>4225.175499338406</v>
+        <v>4096.865211123603</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1057653089287331</v>
+        <v>0.1067368340930648</v>
       </c>
       <c r="T44">
-        <v>1.168835484391823</v>
+        <v>1.187772318143485</v>
       </c>
       <c r="U44">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V44">
         <v>0.125</v>
       </c>
       <c r="W44">
-        <v>0.05883203957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.290046292095369</v>
+        <v>2.147364603199185</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08719127245232539</v>
+        <v>0.08730020910250426</v>
       </c>
       <c r="C45">
-        <v>37528.87557044443</v>
+        <v>36568.45628548806</v>
       </c>
       <c r="D45">
-        <v>68155.90573915305</v>
+        <v>67976.99878370154</v>
       </c>
       <c r="E45">
-        <v>18177.49721822346</v>
+        <v>18959.00954772831</v>
       </c>
       <c r="F45">
-        <v>33605.03016870862</v>
+        <v>34386.54249821347</v>
       </c>
       <c r="G45">
         <v>2978</v>
@@ -4983,28 +4983,28 @@
         <v>5054</v>
       </c>
       <c r="M45">
-        <v>2353.582615858739</v>
+        <v>2408.317095297314</v>
       </c>
       <c r="N45">
-        <v>2700.417384141261</v>
+        <v>2645.682904702686</v>
       </c>
       <c r="O45">
-        <v>337.5521730176577</v>
+        <v>330.7103630878357</v>
       </c>
       <c r="P45">
-        <v>2362.865211123603</v>
+        <v>2314.97254161485</v>
       </c>
       <c r="Q45">
-        <v>4096.865211123603</v>
+        <v>4048.97254161485</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1067368340930648</v>
+        <v>0.107743056584694</v>
       </c>
       <c r="T45">
-        <v>1.187772318143485</v>
+        <v>1.207385467386277</v>
       </c>
       <c r="U45">
         <v>0.07003661666253409</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.147364603199185</v>
+        <v>2.098560862217385</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08730020910250426</v>
+        <v>0.08740914575268313</v>
       </c>
       <c r="C46">
-        <v>36568.45628548806</v>
+        <v>35608.97379094484</v>
       </c>
       <c r="D46">
-        <v>67976.99878370154</v>
+        <v>67799.02861866317</v>
       </c>
       <c r="E46">
-        <v>18959.00954772831</v>
+        <v>19740.52187723316</v>
       </c>
       <c r="F46">
-        <v>34386.54249821347</v>
+        <v>35168.05482771833</v>
       </c>
       <c r="G46">
         <v>2978</v>
@@ -5065,28 +5065,28 @@
         <v>5054</v>
       </c>
       <c r="M46">
-        <v>2408.317095297314</v>
+        <v>2463.05157473589</v>
       </c>
       <c r="N46">
-        <v>2645.682904702686</v>
+        <v>2590.94842526411</v>
       </c>
       <c r="O46">
-        <v>330.7103630878357</v>
+        <v>323.8685531580138</v>
       </c>
       <c r="P46">
-        <v>2314.97254161485</v>
+        <v>2267.079872106096</v>
       </c>
       <c r="Q46">
-        <v>4048.97254161485</v>
+        <v>4001.079872106096</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.107743056584694</v>
+        <v>0.1087858689851097</v>
       </c>
       <c r="T46">
-        <v>1.207385467386277</v>
+        <v>1.227711822056079</v>
       </c>
       <c r="U46">
         <v>0.07003661666253409</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.098560862217385</v>
+        <v>2.051926176390332</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08740914575268313</v>
+        <v>0.08751808240286202</v>
       </c>
       <c r="C47">
-        <v>35608.97379094484</v>
+        <v>34650.42074821219</v>
       </c>
       <c r="D47">
-        <v>67799.02861866317</v>
+        <v>67621.98790543537</v>
       </c>
       <c r="E47">
-        <v>19740.52187723316</v>
+        <v>20522.03420673802</v>
       </c>
       <c r="F47">
-        <v>35168.05482771833</v>
+        <v>35949.56715722318</v>
       </c>
       <c r="G47">
         <v>2978</v>
@@ -5147,28 +5147,28 @@
         <v>5054</v>
       </c>
       <c r="M47">
-        <v>2463.05157473589</v>
+        <v>2517.786054174465</v>
       </c>
       <c r="N47">
-        <v>2590.94842526411</v>
+        <v>2536.213945825535</v>
       </c>
       <c r="O47">
-        <v>323.8685531580138</v>
+        <v>317.0267432281918</v>
       </c>
       <c r="P47">
-        <v>2267.079872106096</v>
+        <v>2219.187202597343</v>
       </c>
       <c r="Q47">
-        <v>4001.079872106096</v>
+        <v>3953.187202597343</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1087858689851097</v>
+        <v>0.1098673040670223</v>
       </c>
       <c r="T47">
-        <v>1.227711822056079</v>
+        <v>1.248791004676615</v>
       </c>
       <c r="U47">
         <v>0.07003661666253409</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.051926176390332</v>
+        <v>2.007319085599238</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08751808240286202</v>
+        <v>0.09083476905304091</v>
       </c>
       <c r="C48">
-        <v>34650.42074821219</v>
+        <v>28888.73533776264</v>
       </c>
       <c r="D48">
-        <v>67621.98790543537</v>
+        <v>62641.81482449066</v>
       </c>
       <c r="E48">
-        <v>20522.03420673802</v>
+        <v>21303.54653624287</v>
       </c>
       <c r="F48">
-        <v>35949.56715722318</v>
+        <v>36731.07948672803</v>
       </c>
       <c r="G48">
         <v>2978</v>
@@ -5229,45 +5229,45 @@
         <v>5054</v>
       </c>
       <c r="M48">
-        <v>2517.786054174465</v>
+        <v>2859.022953609519</v>
       </c>
       <c r="N48">
-        <v>2536.213945825535</v>
+        <v>2194.977046390481</v>
       </c>
       <c r="O48">
-        <v>317.0267432281918</v>
+        <v>274.3721307988101</v>
       </c>
       <c r="P48">
-        <v>2219.187202597343</v>
+        <v>1920.604915591671</v>
       </c>
       <c r="Q48">
-        <v>3953.187202597343</v>
+        <v>3654.604915591671</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1098673040670223</v>
+        <v>0.1109895480199505</v>
       </c>
       <c r="T48">
-        <v>1.248791004676615</v>
+        <v>1.270665628150757</v>
       </c>
       <c r="U48">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V48">
         <v>0.125</v>
       </c>
       <c r="W48">
-        <v>0.06128203957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.007319085599238</v>
+        <v>1.767736769520972</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09083476905304091</v>
+        <v>0.09264995570321978</v>
       </c>
       <c r="C49">
-        <v>28888.73533776264</v>
+        <v>25680.18579326682</v>
       </c>
       <c r="D49">
-        <v>62641.81482449066</v>
+        <v>60214.7776094997</v>
       </c>
       <c r="E49">
-        <v>21303.54653624287</v>
+        <v>22085.05886574772</v>
       </c>
       <c r="F49">
-        <v>36731.07948672803</v>
+        <v>37512.59181623288</v>
       </c>
       <c r="G49">
         <v>2978</v>
@@ -5311,45 +5311,45 @@
         <v>5054</v>
       </c>
       <c r="M49">
-        <v>2859.022953609519</v>
+        <v>3066.152337301541</v>
       </c>
       <c r="N49">
-        <v>2194.977046390481</v>
+        <v>1987.847662698459</v>
       </c>
       <c r="O49">
-        <v>274.3721307988101</v>
+        <v>248.4809578373074</v>
       </c>
       <c r="P49">
-        <v>1920.604915591671</v>
+        <v>1739.366704861152</v>
       </c>
       <c r="Q49">
-        <v>3654.604915591671</v>
+        <v>3473.366704861152</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1109895480199505</v>
+        <v>0.1121549552018374</v>
       </c>
       <c r="T49">
-        <v>1.270665628150757</v>
+        <v>1.29338158329698</v>
       </c>
       <c r="U49">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V49">
         <v>0.125</v>
       </c>
       <c r="W49">
-        <v>0.06810703957971734</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.767736769520972</v>
+        <v>1.648319928046342</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09264995570321977</v>
+        <v>0.09286126735339867</v>
       </c>
       <c r="C50">
-        <v>25680.18579326684</v>
+        <v>24628.30071909555</v>
       </c>
       <c r="D50">
-        <v>60214.77760949972</v>
+        <v>59944.40486483328</v>
       </c>
       <c r="E50">
-        <v>22085.05886574772</v>
+        <v>22866.57119525257</v>
       </c>
       <c r="F50">
-        <v>37512.59181623288</v>
+        <v>38294.10414573773</v>
       </c>
       <c r="G50">
         <v>2978</v>
@@ -5393,28 +5393,28 @@
         <v>5054</v>
       </c>
       <c r="M50">
-        <v>3066.152337301541</v>
+        <v>3130.030510995322</v>
       </c>
       <c r="N50">
-        <v>1987.847662698459</v>
+        <v>1923.969489004678</v>
       </c>
       <c r="O50">
-        <v>248.4809578373074</v>
+        <v>240.4961861255847</v>
       </c>
       <c r="P50">
-        <v>1739.366704861152</v>
+        <v>1683.473302879093</v>
       </c>
       <c r="Q50">
-        <v>3473.366704861152</v>
+        <v>3417.473302879093</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1121549552018374</v>
+        <v>0.1133660646261513</v>
       </c>
       <c r="T50">
-        <v>1.29338158329698</v>
+        <v>1.316988360213644</v>
       </c>
       <c r="U50">
         <v>0.0817366166625341</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.648319928046342</v>
+        <v>1.614680745841315</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09286126735339867</v>
+        <v>0.09307257900357754</v>
       </c>
       <c r="C51">
-        <v>24628.30071909555</v>
+        <v>23578.83281411809</v>
       </c>
       <c r="D51">
-        <v>59944.40486483328</v>
+        <v>59676.44928936067</v>
       </c>
       <c r="E51">
-        <v>22866.57119525257</v>
+        <v>23648.08352475742</v>
       </c>
       <c r="F51">
-        <v>38294.10414573773</v>
+        <v>39075.61647524258</v>
       </c>
       <c r="G51">
         <v>2978</v>
@@ -5475,28 +5475,28 @@
         <v>5054</v>
       </c>
       <c r="M51">
-        <v>3130.030510995322</v>
+        <v>3193.908684689105</v>
       </c>
       <c r="N51">
-        <v>1923.969489004678</v>
+        <v>1860.091315310895</v>
       </c>
       <c r="O51">
-        <v>240.4961861255847</v>
+        <v>232.5114144138619</v>
       </c>
       <c r="P51">
-        <v>1683.473302879093</v>
+        <v>1627.579900897033</v>
       </c>
       <c r="Q51">
-        <v>3417.473302879093</v>
+        <v>3361.579900897033</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1133660646261513</v>
+        <v>0.1146256184274378</v>
       </c>
       <c r="T51">
-        <v>1.316988360213644</v>
+        <v>1.341539408206974</v>
       </c>
       <c r="U51">
         <v>0.0817366166625341</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.614680745841315</v>
+        <v>1.582387130924489</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09307257900357754</v>
+        <v>0.09328389065375643</v>
       </c>
       <c r="C52">
-        <v>23578.83281411809</v>
+        <v>22531.74980785248</v>
       </c>
       <c r="D52">
-        <v>59676.44928936067</v>
+        <v>59410.87861259992</v>
       </c>
       <c r="E52">
-        <v>23648.08352475742</v>
+        <v>24429.59585426228</v>
       </c>
       <c r="F52">
-        <v>39075.61647524258</v>
+        <v>39857.12880474744</v>
       </c>
       <c r="G52">
         <v>2978</v>
@@ -5557,28 +5557,28 @@
         <v>5054</v>
       </c>
       <c r="M52">
-        <v>3193.908684689105</v>
+        <v>3257.786858382887</v>
       </c>
       <c r="N52">
-        <v>1860.091315310895</v>
+        <v>1796.213141617113</v>
       </c>
       <c r="O52">
-        <v>232.5114144138619</v>
+        <v>224.5266427021391</v>
       </c>
       <c r="P52">
-        <v>1627.579900897033</v>
+        <v>1571.686498914974</v>
       </c>
       <c r="Q52">
-        <v>3361.579900897033</v>
+        <v>3305.686498914974</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1146256184274378</v>
+        <v>0.1159365825879604</v>
       </c>
       <c r="T52">
-        <v>1.341539408206974</v>
+        <v>1.367092539791869</v>
       </c>
       <c r="U52">
         <v>0.0817366166625341</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.582387130924489</v>
+        <v>1.55135993227891</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09328389065375643</v>
+        <v>0.09349520230393532</v>
       </c>
       <c r="C53">
-        <v>22531.74980785248</v>
+        <v>21487.0200017091</v>
       </c>
       <c r="D53">
-        <v>59410.87861259992</v>
+        <v>59147.66113596139</v>
       </c>
       <c r="E53">
-        <v>24429.59585426228</v>
+        <v>25211.10818376712</v>
       </c>
       <c r="F53">
-        <v>39857.12880474744</v>
+        <v>40638.64113425228</v>
       </c>
       <c r="G53">
         <v>2978</v>
@@ -5639,28 +5639,28 @@
         <v>5054</v>
       </c>
       <c r="M53">
-        <v>3257.786858382887</v>
+        <v>3321.665032076669</v>
       </c>
       <c r="N53">
-        <v>1796.213141617113</v>
+        <v>1732.334967923331</v>
       </c>
       <c r="O53">
-        <v>224.5266427021391</v>
+        <v>216.5418709904164</v>
       </c>
       <c r="P53">
-        <v>1571.686498914974</v>
+        <v>1515.793096932915</v>
       </c>
       <c r="Q53">
-        <v>3305.686498914974</v>
+        <v>3249.793096932915</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1159365825879604</v>
+        <v>0.1173021702551715</v>
       </c>
       <c r="T53">
-        <v>1.367092539791869</v>
+        <v>1.393710385192801</v>
       </c>
       <c r="U53">
         <v>0.0817366166625341</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.55135993227891</v>
+        <v>1.521526087427393</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09349520230393532</v>
+        <v>0.1002917639541142</v>
       </c>
       <c r="C54">
-        <v>21487.0200017091</v>
+        <v>13328.23271900282</v>
       </c>
       <c r="D54">
-        <v>59147.66113596139</v>
+        <v>51770.38618275996</v>
       </c>
       <c r="E54">
-        <v>25211.10818376712</v>
+        <v>25992.62051327198</v>
       </c>
       <c r="F54">
-        <v>40638.64113425228</v>
+        <v>41420.15346375714</v>
       </c>
       <c r="G54">
         <v>2978</v>
@@ -5721,45 +5721,45 @@
         <v>5054</v>
       </c>
       <c r="M54">
-        <v>3321.665032076669</v>
+        <v>3973.709384955803</v>
       </c>
       <c r="N54">
-        <v>1732.334967923331</v>
+        <v>1080.290615044197</v>
       </c>
       <c r="O54">
-        <v>216.5418709904164</v>
+        <v>135.0363268805247</v>
       </c>
       <c r="P54">
-        <v>1515.793096932915</v>
+        <v>945.2542881636725</v>
       </c>
       <c r="Q54">
-        <v>3249.793096932915</v>
+        <v>2679.254288163673</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1173021702551715</v>
+        <v>0.1187258680358809</v>
       </c>
       <c r="T54">
-        <v>1.393710385192801</v>
+        <v>1.421460904866113</v>
       </c>
       <c r="U54">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V54">
         <v>0.125</v>
       </c>
       <c r="W54">
-        <v>0.07151953957971734</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.521526087427393</v>
+        <v>1.271859492074107</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1002917639541142</v>
+        <v>0.114558428619496</v>
       </c>
       <c r="C55">
-        <v>13328.23271900282</v>
+        <v>1804.899290675923</v>
       </c>
       <c r="D55">
-        <v>51770.38618275996</v>
+        <v>41028.56508393792</v>
       </c>
       <c r="E55">
-        <v>25992.62051327198</v>
+        <v>26774.13284277683</v>
       </c>
       <c r="F55">
-        <v>41420.15346375714</v>
+        <v>42201.66579326199</v>
       </c>
       <c r="G55">
         <v>2978</v>
@@ -5803,45 +5803,45 @@
         <v>5054</v>
       </c>
       <c r="M55">
-        <v>3973.709384955803</v>
+        <v>5255.652675415847</v>
       </c>
       <c r="N55">
-        <v>1080.290615044197</v>
+        <v>-201.6526754158467</v>
       </c>
       <c r="O55">
-        <v>135.0363268805247</v>
+        <v>-25.20658442698084</v>
       </c>
       <c r="P55">
-        <v>945.2542881636725</v>
+        <v>-176.4460909888659</v>
       </c>
       <c r="Q55">
-        <v>2679.254288163673</v>
+        <v>1557.553909011134</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1187258680358809</v>
+        <v>0.1204181331901826</v>
       </c>
       <c r="T55">
-        <v>1.421460904866113</v>
+        <v>1.454446302534929</v>
       </c>
       <c r="U55">
-        <v>0.0959366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V55">
-        <v>0.125</v>
+        <v>0.1202039097741583</v>
       </c>
       <c r="W55">
-        <v>0.08394453957971734</v>
+        <v>0.1095668284296519</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.271859492074107</v>
+        <v>0.9616312781932662</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.114558428619496</v>
+        <v>0.1153457947861214</v>
       </c>
       <c r="C56">
-        <v>1804.899290675923</v>
+        <v>558.8800256816176</v>
       </c>
       <c r="D56">
-        <v>41028.56508393792</v>
+        <v>40564.05814844846</v>
       </c>
       <c r="E56">
-        <v>26774.13284277683</v>
+        <v>27555.64517228169</v>
       </c>
       <c r="F56">
-        <v>42201.66579326199</v>
+        <v>42983.17812276685</v>
       </c>
       <c r="G56">
         <v>2978</v>
@@ -5885,37 +5885,37 @@
         <v>5054</v>
       </c>
       <c r="M56">
-        <v>5255.652675415847</v>
+        <v>5352.979576812437</v>
       </c>
       <c r="N56">
-        <v>-201.6526754158467</v>
+        <v>-298.9795768124368</v>
       </c>
       <c r="O56">
-        <v>-25.20658442698084</v>
+        <v>-37.3724471015546</v>
       </c>
       <c r="P56">
-        <v>-176.4460909888659</v>
+        <v>-261.6071297108822</v>
       </c>
       <c r="Q56">
-        <v>1557.553909011134</v>
+        <v>1472.392870289118</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1204181331901826</v>
+        <v>0.1220763139277422</v>
       </c>
       <c r="T56">
-        <v>1.454446302534929</v>
+        <v>1.48676733148015</v>
       </c>
       <c r="U56">
         <v>0.1245366166625341</v>
       </c>
       <c r="V56">
-        <v>0.1202039097741583</v>
+        <v>0.1180183841419008</v>
       </c>
       <c r="W56">
-        <v>0.1095668284296519</v>
+        <v>0.1098390063975225</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9616312781932662</v>
+        <v>0.9441470731352067</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1153457947861214</v>
+        <v>0.1161331609527467</v>
       </c>
       <c r="C57">
-        <v>558.8800256816176</v>
+        <v>-676.7391082731192</v>
       </c>
       <c r="D57">
-        <v>40564.05814844846</v>
+        <v>40109.95134399857</v>
       </c>
       <c r="E57">
-        <v>27555.64517228169</v>
+        <v>28337.15750178653</v>
       </c>
       <c r="F57">
-        <v>42983.17812276685</v>
+        <v>43764.69045227169</v>
       </c>
       <c r="G57">
         <v>2978</v>
@@ -5967,37 +5967,37 @@
         <v>5054</v>
       </c>
       <c r="M57">
-        <v>5352.979576812437</v>
+        <v>5450.306478209026</v>
       </c>
       <c r="N57">
-        <v>-298.9795768124368</v>
+        <v>-396.306478209026</v>
       </c>
       <c r="O57">
-        <v>-37.3724471015546</v>
+        <v>-49.53830977612824</v>
       </c>
       <c r="P57">
-        <v>-261.6071297108822</v>
+        <v>-346.7681684328977</v>
       </c>
       <c r="Q57">
-        <v>1472.392870289118</v>
+        <v>1387.231831567102</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1220763139277422</v>
+        <v>0.1238098665170091</v>
       </c>
       <c r="T57">
-        <v>1.48676733148015</v>
+        <v>1.520557498104699</v>
       </c>
       <c r="U57">
         <v>0.1245366166625341</v>
       </c>
       <c r="V57">
-        <v>0.1180183841419008</v>
+        <v>0.1159109129965098</v>
       </c>
       <c r="W57">
-        <v>0.1098390063975225</v>
+        <v>0.1101014637236834</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9441470731352067</v>
+        <v>0.9272873039720781</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1161331609527467</v>
+        <v>0.116920527119372</v>
       </c>
       <c r="C58">
-        <v>-676.7391082731192</v>
+        <v>-1902.303526709278</v>
       </c>
       <c r="D58">
-        <v>40109.95134399857</v>
+        <v>39665.89925506727</v>
       </c>
       <c r="E58">
-        <v>28337.15750178653</v>
+        <v>29118.66983129139</v>
       </c>
       <c r="F58">
-        <v>43764.69045227169</v>
+        <v>44546.20278177655</v>
       </c>
       <c r="G58">
         <v>2978</v>
@@ -6049,37 +6049,37 @@
         <v>5054</v>
       </c>
       <c r="M58">
-        <v>5450.306478209026</v>
+        <v>5547.633379605616</v>
       </c>
       <c r="N58">
-        <v>-396.306478209026</v>
+        <v>-493.633379605616</v>
       </c>
       <c r="O58">
-        <v>-49.53830977612824</v>
+        <v>-61.704172450702</v>
       </c>
       <c r="P58">
-        <v>-346.7681684328977</v>
+        <v>-431.929207154914</v>
       </c>
       <c r="Q58">
-        <v>1387.231831567102</v>
+        <v>1302.070792845086</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1238098665170091</v>
+        <v>0.1256240494592651</v>
       </c>
       <c r="T58">
-        <v>1.520557498104699</v>
+        <v>1.555919300386203</v>
       </c>
       <c r="U58">
         <v>0.1245366166625341</v>
       </c>
       <c r="V58">
-        <v>0.1159109129965098</v>
+        <v>0.1138773882070973</v>
       </c>
       <c r="W58">
-        <v>0.1101014637236834</v>
+        <v>0.1103547120208562</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9272873039720781</v>
+        <v>0.9110191056567785</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.116920527119372</v>
+        <v>0.1177078932859974</v>
       </c>
       <c r="C59">
-        <v>-1902.303526709278</v>
+        <v>-3118.143516433483</v>
       </c>
       <c r="D59">
-        <v>39665.89925506727</v>
+        <v>39231.57159484792</v>
       </c>
       <c r="E59">
-        <v>29118.66983129139</v>
+        <v>29900.18216079624</v>
       </c>
       <c r="F59">
-        <v>44546.20278177655</v>
+        <v>45327.7151112814</v>
       </c>
       <c r="G59">
         <v>2978</v>
@@ -6131,37 +6131,37 @@
         <v>5054</v>
       </c>
       <c r="M59">
-        <v>5547.633379605616</v>
+        <v>5644.960281002206</v>
       </c>
       <c r="N59">
-        <v>-493.633379605616</v>
+        <v>-590.9602810022061</v>
       </c>
       <c r="O59">
-        <v>-61.704172450702</v>
+        <v>-73.87003512527576</v>
       </c>
       <c r="P59">
-        <v>-431.929207154914</v>
+        <v>-517.0902458769303</v>
       </c>
       <c r="Q59">
-        <v>1302.070792845086</v>
+        <v>1216.90975412307</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1256240494592651</v>
+        <v>0.1275246220654381</v>
       </c>
       <c r="T59">
-        <v>1.555919300386203</v>
+        <v>1.592964998014446</v>
       </c>
       <c r="U59">
         <v>0.1245366166625341</v>
       </c>
       <c r="V59">
-        <v>0.1138773882070973</v>
+        <v>0.1119139849621474</v>
       </c>
       <c r="W59">
-        <v>0.1103547120208562</v>
+        <v>0.1105992276181266</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9110191056567785</v>
+        <v>0.8953118796971788</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1177078932859974</v>
+        <v>0.1184952594526227</v>
       </c>
       <c r="C60">
-        <v>-3118.143516433462</v>
+        <v>-4324.575054837405</v>
       </c>
       <c r="D60">
-        <v>39231.57159484793</v>
+        <v>38806.65238594884</v>
       </c>
       <c r="E60">
-        <v>29900.18216079623</v>
+        <v>30681.69449030108</v>
       </c>
       <c r="F60">
-        <v>45327.7151112814</v>
+        <v>46109.22744078624</v>
       </c>
       <c r="G60">
         <v>2978</v>
@@ -6213,37 +6213,37 @@
         <v>5054</v>
       </c>
       <c r="M60">
-        <v>5644.960281002205</v>
+        <v>5742.287182398794</v>
       </c>
       <c r="N60">
-        <v>-590.9602810022052</v>
+        <v>-688.2871823987944</v>
       </c>
       <c r="O60">
-        <v>-73.87003512527565</v>
+        <v>-86.03589779984929</v>
       </c>
       <c r="P60">
-        <v>-517.0902458769295</v>
+        <v>-602.2512845989451</v>
       </c>
       <c r="Q60">
-        <v>1216.90975412307</v>
+        <v>1131.748715401055</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.127524622065438</v>
+        <v>0.1295179055304487</v>
       </c>
       <c r="T60">
-        <v>1.592964998014446</v>
+        <v>1.631817802844066</v>
       </c>
       <c r="U60">
         <v>0.1245366166625341</v>
       </c>
       <c r="V60">
-        <v>0.1119139849621474</v>
+        <v>0.1100171377593991</v>
       </c>
       <c r="W60">
-        <v>0.1105992276181266</v>
+        <v>0.1108354545510826</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.895311879697179</v>
+        <v>0.880137102075193</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1184952594526227</v>
+        <v>0.119282625619248</v>
       </c>
       <c r="C61">
-        <v>-4324.575054837405</v>
+        <v>-5521.900576524698</v>
       </c>
       <c r="D61">
-        <v>38806.65238594884</v>
+        <v>38390.8391937664</v>
       </c>
       <c r="E61">
-        <v>30681.69449030108</v>
+        <v>31463.20681980594</v>
       </c>
       <c r="F61">
-        <v>46109.22744078624</v>
+        <v>46890.7397702911</v>
       </c>
       <c r="G61">
         <v>2978</v>
@@ -6295,37 +6295,37 @@
         <v>5054</v>
       </c>
       <c r="M61">
-        <v>5742.287182398794</v>
+        <v>5839.614083795384</v>
       </c>
       <c r="N61">
-        <v>-688.2871823987944</v>
+        <v>-785.6140837953844</v>
       </c>
       <c r="O61">
-        <v>-86.03589779984929</v>
+        <v>-98.20176047442305</v>
       </c>
       <c r="P61">
-        <v>-602.2512845989451</v>
+        <v>-687.4123233209614</v>
       </c>
       <c r="Q61">
-        <v>1131.748715401055</v>
+        <v>1046.587676679039</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1295179055304487</v>
+        <v>0.1316108531687099</v>
       </c>
       <c r="T61">
-        <v>1.631817802844066</v>
+        <v>1.672613247915168</v>
       </c>
       <c r="U61">
         <v>0.1245366166625341</v>
       </c>
       <c r="V61">
-        <v>0.1100171377593991</v>
+        <v>0.1081835187967425</v>
       </c>
       <c r="W61">
-        <v>0.1108354545510826</v>
+        <v>0.1110638072529401</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.880137102075193</v>
+        <v>0.8654681503739398</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.119282625619248</v>
+        <v>0.1200699917858734</v>
       </c>
       <c r="C62">
-        <v>-5521.900576524698</v>
+        <v>-6710.409691173612</v>
       </c>
       <c r="D62">
-        <v>38390.8391937664</v>
+        <v>37983.84240862234</v>
       </c>
       <c r="E62">
-        <v>31463.20681980594</v>
+        <v>32244.71914931079</v>
       </c>
       <c r="F62">
-        <v>46890.7397702911</v>
+        <v>47672.25209979595</v>
       </c>
       <c r="G62">
         <v>2978</v>
@@ -6377,37 +6377,37 @@
         <v>5054</v>
       </c>
       <c r="M62">
-        <v>5839.614083795384</v>
+        <v>5936.940985191975</v>
       </c>
       <c r="N62">
-        <v>-785.6140837953844</v>
+        <v>-882.9409851919745</v>
       </c>
       <c r="O62">
-        <v>-98.20176047442305</v>
+        <v>-110.3676231489968</v>
       </c>
       <c r="P62">
-        <v>-687.4123233209614</v>
+        <v>-772.5733620429777</v>
       </c>
       <c r="Q62">
-        <v>1046.587676679039</v>
+        <v>961.4266379570223</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1316108531687099</v>
+        <v>0.1338111314550871</v>
       </c>
       <c r="T62">
-        <v>1.672613247915168</v>
+        <v>1.71550076709248</v>
       </c>
       <c r="U62">
         <v>0.1245366166625341</v>
       </c>
       <c r="V62">
-        <v>0.1081835187967425</v>
+        <v>0.1064100184885991</v>
       </c>
       <c r="W62">
-        <v>0.1110638072529401</v>
+        <v>0.1112846729809663</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8654681503739398</v>
+        <v>0.8512801479087931</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1200699917858734</v>
+        <v>0.1208573579524987</v>
       </c>
       <c r="C63">
-        <v>-6710.409691173612</v>
+        <v>-7890.379856216794</v>
       </c>
       <c r="D63">
-        <v>37983.84240862234</v>
+        <v>37585.38457308401</v>
       </c>
       <c r="E63">
-        <v>32244.71914931079</v>
+        <v>33026.23147881564</v>
       </c>
       <c r="F63">
-        <v>47672.25209979595</v>
+        <v>48453.76442930081</v>
       </c>
       <c r="G63">
         <v>2978</v>
@@ -6459,37 +6459,37 @@
         <v>5054</v>
       </c>
       <c r="M63">
-        <v>5936.940985191975</v>
+        <v>6034.267886588565</v>
       </c>
       <c r="N63">
-        <v>-882.9409851919745</v>
+        <v>-980.2678865885646</v>
       </c>
       <c r="O63">
-        <v>-110.3676231489968</v>
+        <v>-122.5334858235706</v>
       </c>
       <c r="P63">
-        <v>-772.5733620429777</v>
+        <v>-857.734400764994</v>
       </c>
       <c r="Q63">
-        <v>961.4266379570223</v>
+        <v>876.265599235006</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1338111314550871</v>
+        <v>0.1361272138618</v>
       </c>
       <c r="T63">
-        <v>1.71550076709248</v>
+        <v>1.76064552412123</v>
       </c>
       <c r="U63">
         <v>0.1245366166625341</v>
       </c>
       <c r="V63">
-        <v>0.1064100184885991</v>
+        <v>0.1046937278678153</v>
       </c>
       <c r="W63">
-        <v>0.1112846729809663</v>
+        <v>0.1114984140080883</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8512801479087931</v>
+        <v>0.8375498229425222</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1208573579524987</v>
+        <v>0.1216447241191241</v>
       </c>
       <c r="C64">
-        <v>-7890.379856216794</v>
+        <v>-9062.077007621287</v>
       </c>
       <c r="D64">
-        <v>37585.38457308401</v>
+        <v>37195.19975118437</v>
       </c>
       <c r="E64">
-        <v>33026.23147881564</v>
+        <v>33807.74380832049</v>
       </c>
       <c r="F64">
-        <v>48453.76442930081</v>
+        <v>49235.27675880565</v>
       </c>
       <c r="G64">
         <v>2978</v>
@@ -6541,37 +6541,37 @@
         <v>5054</v>
       </c>
       <c r="M64">
-        <v>6034.267886588565</v>
+        <v>6131.594787985154</v>
       </c>
       <c r="N64">
-        <v>-980.2678865885646</v>
+        <v>-1077.594787985154</v>
       </c>
       <c r="O64">
-        <v>-122.5334858235706</v>
+        <v>-134.6993484981442</v>
       </c>
       <c r="P64">
-        <v>-857.734400764994</v>
+        <v>-942.8954394870095</v>
       </c>
       <c r="Q64">
-        <v>876.265599235006</v>
+        <v>791.1045605129905</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1361272138618</v>
+        <v>0.1385684899121189</v>
       </c>
       <c r="T64">
-        <v>1.76064552412123</v>
+        <v>1.808230538286668</v>
       </c>
       <c r="U64">
         <v>0.1245366166625341</v>
       </c>
       <c r="V64">
-        <v>0.1046937278678153</v>
+        <v>0.1030319226635643</v>
       </c>
       <c r="W64">
-        <v>0.1114984140080883</v>
+        <v>0.1117053696057779</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8375498229425222</v>
+        <v>0.8242553813085141</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1216447241191241</v>
+        <v>0.1224320902857494</v>
       </c>
       <c r="C65">
-        <v>-9062.077007621287</v>
+        <v>-10225.75615178237</v>
       </c>
       <c r="D65">
-        <v>37195.19975118437</v>
+        <v>36813.03293652814</v>
       </c>
       <c r="E65">
-        <v>33807.74380832049</v>
+        <v>34589.25613782534</v>
       </c>
       <c r="F65">
-        <v>49235.27675880565</v>
+        <v>50016.78908831051</v>
       </c>
       <c r="G65">
         <v>2978</v>
@@ -6623,37 +6623,37 @@
         <v>5054</v>
       </c>
       <c r="M65">
-        <v>6131.594787985154</v>
+        <v>6228.921689381744</v>
       </c>
       <c r="N65">
-        <v>-1077.594787985154</v>
+        <v>-1174.921689381744</v>
       </c>
       <c r="O65">
-        <v>-134.6993484981442</v>
+        <v>-146.865211172718</v>
       </c>
       <c r="P65">
-        <v>-942.8954394870095</v>
+        <v>-1028.056478209026</v>
       </c>
       <c r="Q65">
-        <v>791.1045605129905</v>
+        <v>705.943521790974</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1385684899121189</v>
+        <v>0.1411453924096777</v>
       </c>
       <c r="T65">
-        <v>1.808230538286668</v>
+        <v>1.858459164350187</v>
       </c>
       <c r="U65">
         <v>0.1245366166625341</v>
       </c>
       <c r="V65">
-        <v>0.1030319226635643</v>
+        <v>0.1014220488719461</v>
       </c>
       <c r="W65">
-        <v>0.1117053696057779</v>
+        <v>0.1119058578410397</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8242553813085141</v>
+        <v>0.8113763909755685</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1224320902857494</v>
+        <v>0.1419893698069705</v>
       </c>
       <c r="C66">
-        <v>-10225.75615178237</v>
+        <v>-18492.11609603295</v>
       </c>
       <c r="D66">
-        <v>36813.03293652814</v>
+        <v>29328.18532178241</v>
       </c>
       <c r="E66">
-        <v>34589.25613782534</v>
+        <v>35370.7684673302</v>
       </c>
       <c r="F66">
-        <v>50016.78908831051</v>
+        <v>50798.30141781536</v>
       </c>
       <c r="G66">
         <v>2978</v>
@@ -6705,45 +6705,45 @@
         <v>5054</v>
       </c>
       <c r="M66">
-        <v>6228.921689381744</v>
+        <v>7758.760690760728</v>
       </c>
       <c r="N66">
-        <v>-1174.921689381744</v>
+        <v>-2704.760690760728</v>
       </c>
       <c r="O66">
-        <v>-146.865211172718</v>
+        <v>-338.095086345091</v>
       </c>
       <c r="P66">
-        <v>-1028.056478209026</v>
+        <v>-2366.665604415637</v>
       </c>
       <c r="Q66">
-        <v>705.943521790974</v>
+        <v>-632.6656044156371</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1411453924096777</v>
+        <v>0.1451264417773706</v>
       </c>
       <c r="T66">
-        <v>1.858459164350187</v>
+        <v>1.936057226449812</v>
       </c>
       <c r="U66">
-        <v>0.1245366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V66">
-        <v>0.1014220488719461</v>
+        <v>0.0814240862915516</v>
       </c>
       <c r="W66">
-        <v>0.1119058578410397</v>
+        <v>0.1403001772075243</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8113763909755685</v>
+        <v>0.6513926903324128</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1419893698069705</v>
+        <v>0.179206183869433</v>
       </c>
       <c r="C67">
-        <v>-18492.11609603295</v>
+        <v>-27455.42021547831</v>
       </c>
       <c r="D67">
-        <v>29328.18532178241</v>
+        <v>21146.39353184191</v>
       </c>
       <c r="E67">
-        <v>35370.7684673302</v>
+        <v>36152.28079683505</v>
       </c>
       <c r="F67">
-        <v>50798.30141781536</v>
+        <v>51579.81374732022</v>
       </c>
       <c r="G67">
         <v>2978</v>
@@ -6787,45 +6787,45 @@
         <v>5054</v>
       </c>
       <c r="M67">
-        <v>7758.760690760728</v>
+        <v>10663.43618220464</v>
       </c>
       <c r="N67">
-        <v>-2704.760690760728</v>
+        <v>-5609.436182204645</v>
       </c>
       <c r="O67">
-        <v>-338.095086345091</v>
+        <v>-701.1795227755806</v>
       </c>
       <c r="P67">
-        <v>-2366.665604415637</v>
+        <v>-4908.256659429064</v>
       </c>
       <c r="Q67">
-        <v>-632.6656044156371</v>
+        <v>-3174.256659429064</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1451264417773706</v>
+        <v>0.149540301523285</v>
       </c>
       <c r="T67">
-        <v>1.936057226449812</v>
+        <v>2.022091568410509</v>
       </c>
       <c r="U67">
-        <v>0.1527366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.0814240862915516</v>
+        <v>0.05924450516750661</v>
       </c>
       <c r="W67">
-        <v>0.1403001772075243</v>
+        <v>0.1944886081083578</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.6513926903324128</v>
+        <v>0.4739560413400529</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.179206183869433</v>
+        <v>0.1808155500360584</v>
       </c>
       <c r="C68">
-        <v>-27455.42021547831</v>
+        <v>-28488.99455033885</v>
       </c>
       <c r="D68">
-        <v>21146.39353184191</v>
+        <v>20894.33152648621</v>
       </c>
       <c r="E68">
-        <v>36152.28079683505</v>
+        <v>36933.7931263399</v>
       </c>
       <c r="F68">
-        <v>51579.81374732022</v>
+        <v>52361.32607682506</v>
       </c>
       <c r="G68">
         <v>2978</v>
@@ -6869,37 +6869,37 @@
         <v>5054</v>
       </c>
       <c r="M68">
-        <v>10663.43618220464</v>
+        <v>10825.00339708653</v>
       </c>
       <c r="N68">
-        <v>-5609.436182204645</v>
+        <v>-5771.003397086533</v>
       </c>
       <c r="O68">
-        <v>-701.1795227755806</v>
+        <v>-721.3754246358167</v>
       </c>
       <c r="P68">
-        <v>-4908.256659429064</v>
+        <v>-5049.627972450717</v>
       </c>
       <c r="Q68">
-        <v>-3174.256659429064</v>
+        <v>-3315.627972450717</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.149540301523285</v>
+        <v>0.1526839470239906</v>
       </c>
       <c r="T68">
-        <v>2.022091568410509</v>
+        <v>2.083367070483555</v>
       </c>
       <c r="U68">
         <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.05924450516750661</v>
+        <v>0.05836025882172292</v>
       </c>
       <c r="W68">
-        <v>0.1944886081083578</v>
+        <v>0.1946714142061813</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4739560413400529</v>
+        <v>0.4668820705737834</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1808155500360584</v>
+        <v>0.1824249162026837</v>
       </c>
       <c r="C69">
-        <v>-28488.99455033885</v>
+        <v>-29516.63058236876</v>
       </c>
       <c r="D69">
-        <v>20894.33152648621</v>
+        <v>20648.20782396115</v>
       </c>
       <c r="E69">
-        <v>36933.7931263399</v>
+        <v>37715.30545584475</v>
       </c>
       <c r="F69">
-        <v>52361.32607682506</v>
+        <v>53142.83840632992</v>
       </c>
       <c r="G69">
         <v>2978</v>
@@ -6951,37 +6951,37 @@
         <v>5054</v>
       </c>
       <c r="M69">
-        <v>10825.00339708653</v>
+        <v>10986.57061196842</v>
       </c>
       <c r="N69">
-        <v>-5771.003397086533</v>
+        <v>-5932.570611968422</v>
       </c>
       <c r="O69">
-        <v>-721.3754246358167</v>
+        <v>-741.5713264960527</v>
       </c>
       <c r="P69">
-        <v>-5049.627972450717</v>
+        <v>-5190.99928547237</v>
       </c>
       <c r="Q69">
-        <v>-3315.627972450717</v>
+        <v>-3456.99928547237</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1526839470239906</v>
+        <v>0.1560240703684903</v>
       </c>
       <c r="T69">
-        <v>2.083367070483555</v>
+        <v>2.148472291436166</v>
       </c>
       <c r="U69">
         <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.05836025882172292</v>
+        <v>0.05750201972140347</v>
       </c>
       <c r="W69">
-        <v>0.1946714142061813</v>
+        <v>0.1948488436540688</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4668820705737834</v>
+        <v>0.4600161577712277</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1824249162026837</v>
+        <v>0.1840342823693091</v>
       </c>
       <c r="C70">
-        <v>-29516.63058236876</v>
+        <v>-30538.53571822937</v>
       </c>
       <c r="D70">
-        <v>20648.20782396115</v>
+        <v>20407.8150176054</v>
       </c>
       <c r="E70">
-        <v>37715.30545584475</v>
+        <v>38496.81778534961</v>
       </c>
       <c r="F70">
-        <v>53142.83840632992</v>
+        <v>53924.35073583477</v>
       </c>
       <c r="G70">
         <v>2978</v>
@@ -7033,37 +7033,37 @@
         <v>5054</v>
       </c>
       <c r="M70">
-        <v>10986.57061196842</v>
+        <v>11148.13782685031</v>
       </c>
       <c r="N70">
-        <v>-5932.570611968422</v>
+        <v>-6094.137826850312</v>
       </c>
       <c r="O70">
-        <v>-741.5713264960527</v>
+        <v>-761.767228356289</v>
       </c>
       <c r="P70">
-        <v>-5190.99928547237</v>
+        <v>-5332.370598494023</v>
       </c>
       <c r="Q70">
-        <v>-3456.99928547237</v>
+        <v>-3598.370598494023</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1560240703684903</v>
+        <v>0.1595796855416674</v>
       </c>
       <c r="T70">
-        <v>2.148472291436166</v>
+        <v>2.217777849224429</v>
       </c>
       <c r="U70">
         <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.05750201972140347</v>
+        <v>0.05666865711674544</v>
       </c>
       <c r="W70">
-        <v>0.1948488436540688</v>
+        <v>0.1950211302194089</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4600161577712277</v>
+        <v>0.4533492569339636</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1840342823693091</v>
+        <v>0.1856436485359344</v>
       </c>
       <c r="C71">
-        <v>-30538.53571822937</v>
+        <v>-31554.90781696889</v>
       </c>
       <c r="D71">
-        <v>20407.8150176054</v>
+        <v>20172.95524837074</v>
       </c>
       <c r="E71">
-        <v>38496.81778534961</v>
+        <v>39278.33011485446</v>
       </c>
       <c r="F71">
-        <v>53924.35073583477</v>
+        <v>54705.86306533962</v>
       </c>
       <c r="G71">
         <v>2978</v>
@@ -7115,37 +7115,37 @@
         <v>5054</v>
       </c>
       <c r="M71">
-        <v>11148.13782685031</v>
+        <v>11309.7050417322</v>
       </c>
       <c r="N71">
-        <v>-6094.137826850312</v>
+        <v>-6255.705041732201</v>
       </c>
       <c r="O71">
-        <v>-761.767228356289</v>
+        <v>-781.9631302165251</v>
       </c>
       <c r="P71">
-        <v>-5332.370598494023</v>
+        <v>-5473.741911515675</v>
       </c>
       <c r="Q71">
-        <v>-3598.370598494023</v>
+        <v>-3739.741911515675</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1595796855416674</v>
+        <v>0.1633723417263897</v>
       </c>
       <c r="T71">
-        <v>2.217777849224429</v>
+        <v>2.29170377753191</v>
       </c>
       <c r="U71">
         <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.05666865711674544</v>
+        <v>0.0558591048722205</v>
       </c>
       <c r="W71">
-        <v>0.1950211302194089</v>
+        <v>0.1951884943114536</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4533492569339636</v>
+        <v>0.4468728389777641</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1856436485359344</v>
+        <v>0.1872530147025597</v>
       </c>
       <c r="C72">
-        <v>-31554.90781696889</v>
+        <v>-32565.935733157</v>
       </c>
       <c r="D72">
-        <v>20172.95524837074</v>
+        <v>19943.43966168747</v>
       </c>
       <c r="E72">
-        <v>39278.33011485446</v>
+        <v>40059.84244435931</v>
       </c>
       <c r="F72">
-        <v>54705.86306533962</v>
+        <v>55487.37539484447</v>
       </c>
       <c r="G72">
         <v>2978</v>
@@ -7197,37 +7197,37 @@
         <v>5054</v>
       </c>
       <c r="M72">
-        <v>11309.7050417322</v>
+        <v>11471.27225661409</v>
       </c>
       <c r="N72">
-        <v>-6255.705041732201</v>
+        <v>-6417.272256614087</v>
       </c>
       <c r="O72">
-        <v>-781.9631302165251</v>
+        <v>-802.1590320767609</v>
       </c>
       <c r="P72">
-        <v>-5473.741911515675</v>
+        <v>-5615.113224537326</v>
       </c>
       <c r="Q72">
-        <v>-3739.741911515675</v>
+        <v>-3881.113224537326</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1633723417263897</v>
+        <v>0.16742656040661</v>
       </c>
       <c r="T72">
-        <v>2.29170377753191</v>
+        <v>2.370728045722666</v>
       </c>
       <c r="U72">
         <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.0558591048722205</v>
+        <v>0.05507235691627375</v>
       </c>
       <c r="W72">
-        <v>0.1951884943114536</v>
+        <v>0.1953511439220321</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4468728389777641</v>
+        <v>0.44057885533019</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1872530147025597</v>
+        <v>0.1888623808691851</v>
       </c>
       <c r="C73">
-        <v>-32565.93573315699</v>
+        <v>-33571.79982335988</v>
       </c>
       <c r="D73">
-        <v>19943.43966168747</v>
+        <v>19719.08790098945</v>
       </c>
       <c r="E73">
-        <v>40059.8424443593</v>
+        <v>40841.35477386416</v>
       </c>
       <c r="F73">
-        <v>55487.37539484446</v>
+        <v>56268.88772434932</v>
       </c>
       <c r="G73">
         <v>2978</v>
@@ -7279,37 +7279,37 @@
         <v>5054</v>
       </c>
       <c r="M73">
-        <v>11471.27225661409</v>
+        <v>11632.83947149598</v>
       </c>
       <c r="N73">
-        <v>-6417.272256614087</v>
+        <v>-6578.839471495976</v>
       </c>
       <c r="O73">
-        <v>-802.1590320767609</v>
+        <v>-822.354933936997</v>
       </c>
       <c r="P73">
-        <v>-5615.113224537326</v>
+        <v>-5756.484537558979</v>
       </c>
       <c r="Q73">
-        <v>-3881.113224537326</v>
+        <v>-4022.484537558979</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.16742656040661</v>
+        <v>0.1717703661354175</v>
       </c>
       <c r="T73">
-        <v>2.370728045722665</v>
+        <v>2.455396904498475</v>
       </c>
       <c r="U73">
         <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.05507235691627375</v>
+        <v>0.05430746307021439</v>
       </c>
       <c r="W73">
-        <v>0.1953511439220321</v>
+        <v>0.1955092754878724</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.44057885533019</v>
+        <v>0.4344597045617151</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1888623808691851</v>
+        <v>0.1904717470358104</v>
       </c>
       <c r="C74">
-        <v>-33571.79982335988</v>
+        <v>-34572.67241881015</v>
       </c>
       <c r="D74">
-        <v>19719.08790098945</v>
+        <v>19499.72763504403</v>
       </c>
       <c r="E74">
-        <v>40841.35477386416</v>
+        <v>41622.86710336901</v>
       </c>
       <c r="F74">
-        <v>56268.88772434932</v>
+        <v>57050.40005385417</v>
       </c>
       <c r="G74">
         <v>2978</v>
@@ -7361,37 +7361,37 @@
         <v>5054</v>
       </c>
       <c r="M74">
-        <v>11632.83947149598</v>
+        <v>11794.40668637786</v>
       </c>
       <c r="N74">
-        <v>-6578.839471495976</v>
+        <v>-6740.406686377864</v>
       </c>
       <c r="O74">
-        <v>-822.354933936997</v>
+        <v>-842.550835797233</v>
       </c>
       <c r="P74">
-        <v>-5756.484537558979</v>
+        <v>-5897.855850580631</v>
       </c>
       <c r="Q74">
-        <v>-4022.484537558979</v>
+        <v>-4163.855850580631</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1717703661354175</v>
+        <v>0.1764359352515441</v>
       </c>
       <c r="T74">
-        <v>2.455396904498475</v>
+        <v>2.546337530591011</v>
       </c>
       <c r="U74">
         <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.05430746307021439</v>
+        <v>0.05356352521993748</v>
       </c>
       <c r="W74">
-        <v>0.1955092754878724</v>
+        <v>0.1956630746820459</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4344597045617151</v>
+        <v>0.4285082017594999</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1904717470358104</v>
+        <v>0.1920811132024357</v>
       </c>
       <c r="C75">
-        <v>-34572.67241881015</v>
+        <v>-35568.71826687538</v>
       </c>
       <c r="D75">
-        <v>19499.72763504403</v>
+        <v>19285.19411648364</v>
       </c>
       <c r="E75">
-        <v>41622.86710336901</v>
+        <v>42404.37943287386</v>
       </c>
       <c r="F75">
-        <v>57050.40005385417</v>
+        <v>57831.91238335902</v>
       </c>
       <c r="G75">
         <v>2978</v>
@@ -7443,37 +7443,37 @@
         <v>5054</v>
       </c>
       <c r="M75">
-        <v>11794.40668637786</v>
+        <v>11955.97390125975</v>
       </c>
       <c r="N75">
-        <v>-6740.406686377864</v>
+        <v>-6901.973901259753</v>
       </c>
       <c r="O75">
-        <v>-842.550835797233</v>
+        <v>-862.7467376574691</v>
       </c>
       <c r="P75">
-        <v>-5897.855850580631</v>
+        <v>-6039.227163602283</v>
       </c>
       <c r="Q75">
-        <v>-4163.855850580631</v>
+        <v>-4305.227163602283</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1764359352515441</v>
+        <v>0.1814603942996804</v>
       </c>
       <c r="T75">
-        <v>2.546337530591011</v>
+        <v>2.644273589459896</v>
       </c>
       <c r="U75">
         <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.05356352521993748</v>
+        <v>0.05283969379804643</v>
       </c>
       <c r="W75">
-        <v>0.1956630746820459</v>
+        <v>0.1958127171412417</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4285082017594999</v>
+        <v>0.4227175503843715</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1920811132024357</v>
+        <v>0.1936904793690611</v>
       </c>
       <c r="C76">
-        <v>-35568.71826687538</v>
+        <v>-36560.09494370187</v>
       </c>
       <c r="D76">
-        <v>19285.19411648364</v>
+        <v>19075.32976916201</v>
       </c>
       <c r="E76">
-        <v>42404.37943287386</v>
+        <v>43185.89176237871</v>
       </c>
       <c r="F76">
-        <v>57831.91238335902</v>
+        <v>58613.42471286387</v>
       </c>
       <c r="G76">
         <v>2978</v>
@@ -7525,37 +7525,37 @@
         <v>5054</v>
       </c>
       <c r="M76">
-        <v>11955.97390125975</v>
+        <v>12117.54111614164</v>
       </c>
       <c r="N76">
-        <v>-6901.973901259753</v>
+        <v>-7063.541116141641</v>
       </c>
       <c r="O76">
-        <v>-862.7467376574691</v>
+        <v>-882.9426395177052</v>
       </c>
       <c r="P76">
-        <v>-6039.227163602283</v>
+        <v>-6180.598476623936</v>
       </c>
       <c r="Q76">
-        <v>-4305.227163602283</v>
+        <v>-4446.598476623936</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1814603942996804</v>
+        <v>0.1868868100716676</v>
       </c>
       <c r="T76">
-        <v>2.644273589459896</v>
+        <v>2.750044533038291</v>
       </c>
       <c r="U76">
         <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.05283969379804643</v>
+        <v>0.05213516454740581</v>
       </c>
       <c r="W76">
-        <v>0.1958127171412417</v>
+        <v>0.1959583691348589</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4227175503843715</v>
+        <v>0.4170813163792465</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1936904793690611</v>
+        <v>0.1952998455356864</v>
       </c>
       <c r="C77">
-        <v>-36560.09494370187</v>
+        <v>-37546.95324020562</v>
       </c>
       <c r="D77">
-        <v>19075.32976916201</v>
+        <v>18869.98380216311</v>
       </c>
       <c r="E77">
-        <v>43185.89176237871</v>
+        <v>43967.40409188357</v>
       </c>
       <c r="F77">
-        <v>58613.42471286387</v>
+        <v>59394.93704236873</v>
       </c>
       <c r="G77">
         <v>2978</v>
@@ -7607,37 +7607,37 @@
         <v>5054</v>
       </c>
       <c r="M77">
-        <v>12117.54111614164</v>
+        <v>12279.10833102353</v>
       </c>
       <c r="N77">
-        <v>-7063.541116141641</v>
+        <v>-7225.10833102353</v>
       </c>
       <c r="O77">
-        <v>-882.9426395177052</v>
+        <v>-903.1385413779412</v>
       </c>
       <c r="P77">
-        <v>-6180.598476623936</v>
+        <v>-6321.969789645589</v>
       </c>
       <c r="Q77">
-        <v>-4446.598476623936</v>
+        <v>-4587.969789645589</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1868868100716676</v>
+        <v>0.1927654271579871</v>
       </c>
       <c r="T77">
-        <v>2.750044533038291</v>
+        <v>2.864629721914887</v>
       </c>
       <c r="U77">
         <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.05213516454740581</v>
+        <v>0.05144917554020311</v>
       </c>
       <c r="W77">
-        <v>0.1959583691348589</v>
+        <v>0.1961001881812757</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4170813163792465</v>
+        <v>0.4115934043216248</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1952998455356864</v>
+        <v>0.1969092117023118</v>
       </c>
       <c r="C78">
-        <v>-37546.95324020562</v>
+        <v>-38529.43752339782</v>
       </c>
       <c r="D78">
-        <v>18869.98380216311</v>
+        <v>18669.01184847576</v>
       </c>
       <c r="E78">
-        <v>43967.40409188357</v>
+        <v>44748.91642138841</v>
       </c>
       <c r="F78">
-        <v>59394.93704236873</v>
+        <v>60176.44937187358</v>
       </c>
       <c r="G78">
         <v>2978</v>
@@ -7689,37 +7689,37 @@
         <v>5054</v>
       </c>
       <c r="M78">
-        <v>12279.10833102353</v>
+        <v>12440.67554590542</v>
       </c>
       <c r="N78">
-        <v>-7225.10833102353</v>
+        <v>-7386.675545905418</v>
       </c>
       <c r="O78">
-        <v>-903.1385413779412</v>
+        <v>-923.3344432381773</v>
       </c>
       <c r="P78">
-        <v>-6321.969789645589</v>
+        <v>-6463.341102667241</v>
       </c>
       <c r="Q78">
-        <v>-4587.969789645589</v>
+        <v>-4729.341102667241</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1927654271579871</v>
+        <v>0.1991552283387691</v>
       </c>
       <c r="T78">
-        <v>2.864629721914887</v>
+        <v>2.989178840259013</v>
       </c>
       <c r="U78">
         <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.05144917554020311</v>
+        <v>0.05078100442929138</v>
       </c>
       <c r="W78">
-        <v>0.1961001881812757</v>
+        <v>0.1962383236160972</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4115934043216248</v>
+        <v>0.4062480354343311</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1969092117023118</v>
+        <v>0.1985185778689371</v>
       </c>
       <c r="C79">
-        <v>-38529.43752339782</v>
+        <v>-39507.68607486415</v>
       </c>
       <c r="D79">
-        <v>18669.01184847576</v>
+        <v>18472.27562651428</v>
       </c>
       <c r="E79">
-        <v>44748.91642138841</v>
+        <v>45530.42875089327</v>
       </c>
       <c r="F79">
-        <v>60176.44937187358</v>
+        <v>60957.96170137843</v>
       </c>
       <c r="G79">
         <v>2978</v>
@@ -7771,37 +7771,37 @@
         <v>5054</v>
       </c>
       <c r="M79">
-        <v>12440.67554590542</v>
+        <v>12602.24276078731</v>
       </c>
       <c r="N79">
-        <v>-7386.675545905418</v>
+        <v>-7548.242760787307</v>
       </c>
       <c r="O79">
-        <v>-923.3344432381773</v>
+        <v>-943.5303450984134</v>
       </c>
       <c r="P79">
-        <v>-6463.341102667241</v>
+        <v>-6604.712415688893</v>
       </c>
       <c r="Q79">
-        <v>-4729.341102667241</v>
+        <v>-4870.712415688893</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1991552283387691</v>
+        <v>0.2061259205359859</v>
       </c>
       <c r="T79">
-        <v>2.989178840259013</v>
+        <v>3.125050605725332</v>
       </c>
       <c r="U79">
         <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.05078100442929138</v>
+        <v>0.05012996591096713</v>
       </c>
       <c r="W79">
-        <v>0.1962383236160972</v>
+        <v>0.1963729171166926</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4062480354343311</v>
+        <v>0.4010397272877371</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1985185778689371</v>
+        <v>0.2001279440355625</v>
       </c>
       <c r="C80">
-        <v>-39507.68607486415</v>
+        <v>-40481.8314080656</v>
       </c>
       <c r="D80">
-        <v>18472.27562651428</v>
+        <v>18279.64262281769</v>
       </c>
       <c r="E80">
-        <v>45530.42875089327</v>
+        <v>46311.94108039812</v>
       </c>
       <c r="F80">
-        <v>60957.96170137843</v>
+        <v>61739.47403088328</v>
       </c>
       <c r="G80">
         <v>2978</v>
@@ -7853,37 +7853,37 @@
         <v>5054</v>
       </c>
       <c r="M80">
-        <v>12602.24276078731</v>
+        <v>12763.8099756692</v>
       </c>
       <c r="N80">
-        <v>-7548.242760787307</v>
+        <v>-7709.809975669195</v>
       </c>
       <c r="O80">
-        <v>-943.5303450984134</v>
+        <v>-963.7262469586494</v>
       </c>
       <c r="P80">
-        <v>-6604.712415688893</v>
+        <v>-6746.083728710546</v>
       </c>
       <c r="Q80">
-        <v>-4870.712415688893</v>
+        <v>-5012.083728710546</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2061259205359859</v>
+        <v>0.2137604881805567</v>
       </c>
       <c r="T80">
-        <v>3.125050605725332</v>
+        <v>3.2738625393313</v>
       </c>
       <c r="U80">
         <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.05012996591096713</v>
+        <v>0.04949540938044856</v>
       </c>
       <c r="W80">
-        <v>0.1963729171166926</v>
+        <v>0.1965041031868931</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4010397272877371</v>
+        <v>0.3959632750435885</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2001279440355625</v>
+        <v>0.2017373102021878</v>
       </c>
       <c r="C81">
-        <v>-40481.8314080656</v>
+        <v>-41452.00056599093</v>
       </c>
       <c r="D81">
-        <v>18279.64262281769</v>
+        <v>18090.98579439721</v>
       </c>
       <c r="E81">
-        <v>46311.94108039812</v>
+        <v>47093.45340990298</v>
       </c>
       <c r="F81">
-        <v>61739.47403088328</v>
+        <v>62520.98636038814</v>
       </c>
       <c r="G81">
         <v>2978</v>
@@ -7935,37 +7935,37 @@
         <v>5054</v>
       </c>
       <c r="M81">
-        <v>12763.8099756692</v>
+        <v>12925.37719055109</v>
       </c>
       <c r="N81">
-        <v>-7709.809975669195</v>
+        <v>-7871.377190551086</v>
       </c>
       <c r="O81">
-        <v>-963.7262469586494</v>
+        <v>-983.9221488188857</v>
       </c>
       <c r="P81">
-        <v>-6746.083728710546</v>
+        <v>-6887.4550417322</v>
       </c>
       <c r="Q81">
-        <v>-5012.083728710546</v>
+        <v>-5153.4550417322</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2137604881805567</v>
+        <v>0.2221585125895845</v>
       </c>
       <c r="T81">
-        <v>3.2738625393313</v>
+        <v>3.437555666297865</v>
       </c>
       <c r="U81">
         <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.04949540938044856</v>
+        <v>0.04887671676319295</v>
       </c>
       <c r="W81">
-        <v>0.1965041031868931</v>
+        <v>0.1966320096053386</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3959632750435885</v>
+        <v>0.3910137341055435</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2017373102021878</v>
+        <v>0.2033466763688132</v>
       </c>
       <c r="C82">
-        <v>-41452.00056599093</v>
+        <v>-42418.31540056573</v>
       </c>
       <c r="D82">
-        <v>18090.98579439721</v>
+        <v>17906.18328932725</v>
       </c>
       <c r="E82">
-        <v>47093.45340990298</v>
+        <v>47874.96573940782</v>
       </c>
       <c r="F82">
-        <v>62520.98636038814</v>
+        <v>63302.49868989299</v>
       </c>
       <c r="G82">
         <v>2978</v>
@@ -8017,37 +8017,37 @@
         <v>5054</v>
       </c>
       <c r="M82">
-        <v>12925.37719055109</v>
+        <v>13086.94440543297</v>
       </c>
       <c r="N82">
-        <v>-7871.377190551086</v>
+        <v>-8032.944405432972</v>
       </c>
       <c r="O82">
-        <v>-983.9221488188857</v>
+        <v>-1004.118050679122</v>
       </c>
       <c r="P82">
-        <v>-6887.4550417322</v>
+        <v>-7028.826354753851</v>
       </c>
       <c r="Q82">
-        <v>-5153.4550417322</v>
+        <v>-5294.826354753851</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2221585125895845</v>
+        <v>0.2314405395679837</v>
       </c>
       <c r="T82">
-        <v>3.437555666297865</v>
+        <v>3.618479648734595</v>
       </c>
       <c r="U82">
         <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.04887671676319295</v>
+        <v>0.04827330050685723</v>
       </c>
       <c r="W82">
-        <v>0.1966320096053386</v>
+        <v>0.1967567578406126</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3910137341055435</v>
+        <v>0.3861864040548579</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2033466763688132</v>
+        <v>0.2049560425354385</v>
       </c>
       <c r="C83">
-        <v>-42418.31540056573</v>
+        <v>-43380.89283510936</v>
       </c>
       <c r="D83">
-        <v>17906.18328932725</v>
+        <v>17725.11818428847</v>
       </c>
       <c r="E83">
-        <v>47874.96573940782</v>
+        <v>48656.47806891268</v>
       </c>
       <c r="F83">
-        <v>63302.49868989299</v>
+        <v>64084.01101939784</v>
       </c>
       <c r="G83">
         <v>2978</v>
@@ -8099,37 +8099,37 @@
         <v>5054</v>
       </c>
       <c r="M83">
-        <v>13086.94440543297</v>
+        <v>13248.51162031486</v>
       </c>
       <c r="N83">
-        <v>-8032.944405432972</v>
+        <v>-8194.511620314863</v>
       </c>
       <c r="O83">
-        <v>-1004.118050679122</v>
+        <v>-1024.313952539358</v>
       </c>
       <c r="P83">
-        <v>-7028.826354753851</v>
+        <v>-7170.197667775505</v>
       </c>
       <c r="Q83">
-        <v>-5294.826354753851</v>
+        <v>-5436.197667775505</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2314405395679837</v>
+        <v>0.2417539028773161</v>
       </c>
       <c r="T83">
-        <v>3.618479648734595</v>
+        <v>3.819506295886517</v>
       </c>
       <c r="U83">
         <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.04827330050685723</v>
+        <v>0.04768460172018824</v>
       </c>
       <c r="W83">
-        <v>0.1967567578406126</v>
+        <v>0.1968784634360019</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3861864040548579</v>
+        <v>0.3814768137615059</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2049560425354385</v>
+        <v>0.2065654087020638</v>
       </c>
       <c r="C84">
-        <v>-43380.89283510936</v>
+        <v>-44339.84511102767</v>
       </c>
       <c r="D84">
-        <v>17725.11818428847</v>
+        <v>17547.67823787503</v>
       </c>
       <c r="E84">
-        <v>48656.47806891268</v>
+        <v>49437.99039841753</v>
       </c>
       <c r="F84">
-        <v>64084.01101939784</v>
+        <v>64865.52334890269</v>
       </c>
       <c r="G84">
         <v>2978</v>
@@ -8181,37 +8181,37 @@
         <v>5054</v>
       </c>
       <c r="M84">
-        <v>13248.51162031486</v>
+        <v>13410.07883519675</v>
       </c>
       <c r="N84">
-        <v>-8194.511620314863</v>
+        <v>-8356.078835196751</v>
       </c>
       <c r="O84">
-        <v>-1024.313952539358</v>
+        <v>-1044.509854399594</v>
       </c>
       <c r="P84">
-        <v>-7170.197667775505</v>
+        <v>-7311.568980797158</v>
       </c>
       <c r="Q84">
-        <v>-5436.197667775505</v>
+        <v>-5577.568980797158</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2417539028773161</v>
+        <v>0.25328060304657</v>
       </c>
       <c r="T84">
-        <v>3.819506295886517</v>
+        <v>4.044183136821018</v>
       </c>
       <c r="U84">
         <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.04768460172018824</v>
+        <v>0.04711008844645103</v>
       </c>
       <c r="W84">
-        <v>0.1968784634360019</v>
+        <v>0.1969972363664421</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3814768137615059</v>
+        <v>0.3768807075716083</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2065654087020638</v>
+        <v>0.2081747748686892</v>
       </c>
       <c r="C85">
-        <v>-44339.84511102767</v>
+        <v>-45295.28001983525</v>
       </c>
       <c r="D85">
-        <v>17547.67823787503</v>
+        <v>17373.75565857229</v>
       </c>
       <c r="E85">
-        <v>49437.99039841753</v>
+        <v>50219.50272792238</v>
       </c>
       <c r="F85">
-        <v>64865.52334890269</v>
+        <v>65647.03567840754</v>
       </c>
       <c r="G85">
         <v>2978</v>
@@ -8263,37 +8263,37 @@
         <v>5054</v>
       </c>
       <c r="M85">
-        <v>13410.07883519675</v>
+        <v>13571.64605007864</v>
       </c>
       <c r="N85">
-        <v>-8356.078835196751</v>
+        <v>-8517.646050078638</v>
       </c>
       <c r="O85">
-        <v>-1044.509854399594</v>
+        <v>-1064.70575625983</v>
       </c>
       <c r="P85">
-        <v>-7311.568980797158</v>
+        <v>-7452.940293818809</v>
       </c>
       <c r="Q85">
-        <v>-5577.568980797158</v>
+        <v>-5718.940293818809</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.25328060304657</v>
+        <v>0.2662481407369807</v>
       </c>
       <c r="T85">
-        <v>4.044183136821018</v>
+        <v>4.296944582872333</v>
       </c>
       <c r="U85">
         <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.04711008844645103</v>
+        <v>0.04654925406018377</v>
       </c>
       <c r="W85">
-        <v>0.1969972363664421</v>
+        <v>0.197113181369967</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3768807075716083</v>
+        <v>0.3723940324814701</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2081747748686892</v>
+        <v>0.2097841410353145</v>
       </c>
       <c r="C86">
-        <v>-45295.28001983525</v>
+        <v>-46247.30112151521</v>
       </c>
       <c r="D86">
-        <v>17373.75565857229</v>
+        <v>17203.24688639718</v>
       </c>
       <c r="E86">
-        <v>50219.50272792238</v>
+        <v>51001.01505742723</v>
       </c>
       <c r="F86">
-        <v>65647.03567840754</v>
+        <v>66428.5480079124</v>
       </c>
       <c r="G86">
         <v>2978</v>
@@ -8345,37 +8345,37 @@
         <v>5054</v>
       </c>
       <c r="M86">
-        <v>13571.64605007864</v>
+        <v>13733.21326496053</v>
       </c>
       <c r="N86">
-        <v>-8517.646050078638</v>
+        <v>-8679.213264960528</v>
       </c>
       <c r="O86">
-        <v>-1064.70575625983</v>
+        <v>-1084.901658120066</v>
       </c>
       <c r="P86">
-        <v>-7452.940293818809</v>
+        <v>-7594.311606840462</v>
       </c>
       <c r="Q86">
-        <v>-5718.940293818809</v>
+        <v>-5860.311606840462</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2662481407369806</v>
+        <v>0.2809446834527792</v>
       </c>
       <c r="T86">
-        <v>4.29694458287233</v>
+        <v>4.583407555063818</v>
       </c>
       <c r="U86">
         <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.04654925406018377</v>
+        <v>0.04600161577712277</v>
       </c>
       <c r="W86">
-        <v>0.197113181369967</v>
+        <v>0.1972263982557619</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3723940324814701</v>
+        <v>0.3680129262169822</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2097841410353145</v>
+        <v>0.2113935072019398</v>
       </c>
       <c r="C87">
-        <v>-46247.30112151521</v>
+        <v>-47196.00795014559</v>
       </c>
       <c r="D87">
-        <v>17203.24688639718</v>
+        <v>17036.05238727164</v>
       </c>
       <c r="E87">
-        <v>51001.01505742723</v>
+        <v>51782.52738693207</v>
       </c>
       <c r="F87">
-        <v>66428.5480079124</v>
+        <v>67210.06033741724</v>
       </c>
       <c r="G87">
         <v>2978</v>
@@ -8427,37 +8427,37 @@
         <v>5054</v>
       </c>
       <c r="M87">
-        <v>13733.21326496053</v>
+        <v>13894.78047984241</v>
       </c>
       <c r="N87">
-        <v>-8679.213264960528</v>
+        <v>-8840.780479842413</v>
       </c>
       <c r="O87">
-        <v>-1084.901658120066</v>
+        <v>-1105.097559980302</v>
       </c>
       <c r="P87">
-        <v>-7594.311606840462</v>
+        <v>-7735.682919862112</v>
       </c>
       <c r="Q87">
-        <v>-5860.311606840462</v>
+        <v>-6001.682919862112</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2809446834527792</v>
+        <v>0.297740732270835</v>
       </c>
       <c r="T87">
-        <v>4.583407555063818</v>
+        <v>4.910793808996949</v>
       </c>
       <c r="U87">
         <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.04600161577712277</v>
+        <v>0.04546671326808648</v>
       </c>
       <c r="W87">
-        <v>0.1972263982557619</v>
+        <v>0.1973369821907243</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3680129262169822</v>
+        <v>0.3637337061446918</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2113935072019398</v>
+        <v>0.2130028733685652</v>
       </c>
       <c r="C88">
-        <v>-47196.00795014559</v>
+        <v>-48141.49620765078</v>
       </c>
       <c r="D88">
-        <v>17036.05238727164</v>
+        <v>16872.07645927131</v>
       </c>
       <c r="E88">
-        <v>51782.52738693207</v>
+        <v>52564.03971643693</v>
       </c>
       <c r="F88">
-        <v>67210.06033741724</v>
+        <v>67991.57266692209</v>
       </c>
       <c r="G88">
         <v>2978</v>
@@ -8509,37 +8509,37 @@
         <v>5054</v>
       </c>
       <c r="M88">
-        <v>13894.78047984241</v>
+        <v>14056.3476947243</v>
       </c>
       <c r="N88">
-        <v>-8840.780479842413</v>
+        <v>-9002.347694724303</v>
       </c>
       <c r="O88">
-        <v>-1105.097559980302</v>
+        <v>-1125.293461840538</v>
       </c>
       <c r="P88">
-        <v>-7735.682919862112</v>
+        <v>-7877.054232883766</v>
       </c>
       <c r="Q88">
-        <v>-6001.682919862112</v>
+        <v>-6143.054232883766</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.297740732270835</v>
+        <v>0.3171207885993607</v>
       </c>
       <c r="T88">
-        <v>4.910793808996949</v>
+        <v>5.288547178919791</v>
       </c>
       <c r="U88">
         <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.04546671326808648</v>
+        <v>0.04494410736845329</v>
       </c>
       <c r="W88">
-        <v>0.1973369821907243</v>
+        <v>0.1974450239662624</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3637337061446918</v>
+        <v>0.3595528589476263</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2130028733685652</v>
+        <v>0.2146122395351905</v>
       </c>
       <c r="C89">
-        <v>-48141.49620765078</v>
+        <v>-49083.85794646997</v>
       </c>
       <c r="D89">
-        <v>16872.07645927131</v>
+        <v>16711.22704995697</v>
       </c>
       <c r="E89">
-        <v>52564.03971643693</v>
+        <v>53345.55204594178</v>
       </c>
       <c r="F89">
-        <v>67991.57266692209</v>
+        <v>68773.08499642694</v>
       </c>
       <c r="G89">
         <v>2978</v>
@@ -8591,37 +8591,37 @@
         <v>5054</v>
       </c>
       <c r="M89">
-        <v>14056.3476947243</v>
+        <v>14217.91490960619</v>
       </c>
       <c r="N89">
-        <v>-9002.347694724303</v>
+        <v>-9163.914909606192</v>
       </c>
       <c r="O89">
-        <v>-1125.293461840538</v>
+        <v>-1145.489363700774</v>
       </c>
       <c r="P89">
-        <v>-7877.054232883766</v>
+        <v>-8018.425545905418</v>
       </c>
       <c r="Q89">
-        <v>-6143.054232883766</v>
+        <v>-6284.425545905418</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3171207885993607</v>
+        <v>0.3397308543159742</v>
       </c>
       <c r="T89">
-        <v>5.288547178919791</v>
+        <v>5.729259443829775</v>
       </c>
       <c r="U89">
         <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.04494410736845329</v>
+        <v>0.04443337887562996</v>
       </c>
       <c r="W89">
-        <v>0.1974450239662624</v>
+        <v>0.1975506102469018</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3595528589476263</v>
+        <v>0.3554670310050396</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2146122395351905</v>
+        <v>0.2162216057018159</v>
       </c>
       <c r="C90">
-        <v>-49083.85794646997</v>
+        <v>-50023.18174187577</v>
       </c>
       <c r="D90">
-        <v>16711.22704995697</v>
+        <v>16553.41558405603</v>
       </c>
       <c r="E90">
-        <v>53345.55204594178</v>
+        <v>54127.06437544664</v>
       </c>
       <c r="F90">
-        <v>68773.08499642694</v>
+        <v>69554.5973259318</v>
       </c>
       <c r="G90">
         <v>2978</v>
@@ -8673,37 +8673,37 @@
         <v>5054</v>
       </c>
       <c r="M90">
-        <v>14217.91490960619</v>
+        <v>14379.48212448808</v>
       </c>
       <c r="N90">
-        <v>-9163.914909606192</v>
+        <v>-9325.48212448808</v>
       </c>
       <c r="O90">
-        <v>-1145.489363700774</v>
+        <v>-1165.68526556101</v>
       </c>
       <c r="P90">
-        <v>-8018.425545905418</v>
+        <v>-8159.79685892707</v>
       </c>
       <c r="Q90">
-        <v>-6284.425545905418</v>
+        <v>-6425.79685892707</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3397308543159742</v>
+        <v>0.3664518410719718</v>
       </c>
       <c r="T90">
-        <v>5.729259443829775</v>
+        <v>6.250101211450663</v>
       </c>
       <c r="U90">
         <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.04443337887562996</v>
+        <v>0.04393412742758918</v>
       </c>
       <c r="W90">
-        <v>0.1975506102469018</v>
+        <v>0.1976538238021337</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3554670310050396</v>
+        <v>0.3514730194207134</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2162216057018159</v>
+        <v>0.2178309718684412</v>
       </c>
       <c r="C91">
-        <v>-50023.18174187577</v>
+        <v>-50959.5528546202</v>
       </c>
       <c r="D91">
-        <v>16553.41558405603</v>
+        <v>16398.55680081645</v>
       </c>
       <c r="E91">
-        <v>54127.06437544664</v>
+        <v>54908.57670495149</v>
       </c>
       <c r="F91">
-        <v>69554.5973259318</v>
+        <v>70336.10965543665</v>
       </c>
       <c r="G91">
         <v>2978</v>
@@ -8755,37 +8755,37 @@
         <v>5054</v>
       </c>
       <c r="M91">
-        <v>14379.48212448808</v>
+        <v>14541.04933936997</v>
       </c>
       <c r="N91">
-        <v>-9325.48212448808</v>
+        <v>-9487.049339369971</v>
       </c>
       <c r="O91">
-        <v>-1165.68526556101</v>
+        <v>-1185.881167421246</v>
       </c>
       <c r="P91">
-        <v>-8159.79685892707</v>
+        <v>-8301.168171948724</v>
       </c>
       <c r="Q91">
-        <v>-6425.79685892707</v>
+        <v>-6567.168171948724</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3664518410719718</v>
+        <v>0.398517025179169</v>
       </c>
       <c r="T91">
-        <v>6.250101211450663</v>
+        <v>6.87511133259573</v>
       </c>
       <c r="U91">
         <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.04393412742758918</v>
+        <v>0.04344597045617151</v>
       </c>
       <c r="W91">
-        <v>0.1976538238021337</v>
+        <v>0.1977547437228048</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3514730194207134</v>
+        <v>0.347567763649372</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2178309718684412</v>
+        <v>0.2194403380350665</v>
       </c>
       <c r="C92">
-        <v>-50959.5528546202</v>
+        <v>-51893.05338453611</v>
       </c>
       <c r="D92">
-        <v>16398.55680081645</v>
+        <v>16246.5686004054</v>
       </c>
       <c r="E92">
-        <v>54908.57670495149</v>
+        <v>55690.08903445634</v>
       </c>
       <c r="F92">
-        <v>70336.10965543665</v>
+        <v>71117.62198494151</v>
       </c>
       <c r="G92">
         <v>2978</v>
@@ -8837,37 +8837,37 @@
         <v>5054</v>
       </c>
       <c r="M92">
-        <v>14541.04933936997</v>
+        <v>14702.61655425186</v>
       </c>
       <c r="N92">
-        <v>-9487.049339369971</v>
+        <v>-9648.616554251859</v>
       </c>
       <c r="O92">
-        <v>-1185.881167421246</v>
+        <v>-1206.077069281482</v>
       </c>
       <c r="P92">
-        <v>-8301.168171948724</v>
+        <v>-8442.539484970377</v>
       </c>
       <c r="Q92">
-        <v>-6567.168171948724</v>
+        <v>-6708.539484970377</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.398517025179169</v>
+        <v>0.4377078057546323</v>
       </c>
       <c r="T92">
-        <v>6.87511133259573</v>
+        <v>7.639012591773033</v>
       </c>
       <c r="U92">
         <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.04344597045617151</v>
+        <v>0.04296854220940039</v>
       </c>
       <c r="W92">
-        <v>0.1977547437228048</v>
+        <v>0.1978534456232414</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.347567763649372</v>
+        <v>0.3437483376752032</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2194403380350665</v>
+        <v>0.2210497042016919</v>
       </c>
       <c r="C93">
-        <v>-51893.05338453611</v>
+        <v>-52823.7624156751</v>
       </c>
       <c r="D93">
-        <v>16246.5686004054</v>
+        <v>16097.37189877126</v>
       </c>
       <c r="E93">
-        <v>55690.08903445634</v>
+        <v>56471.6013639612</v>
       </c>
       <c r="F93">
-        <v>71117.62198494151</v>
+        <v>71899.13431444636</v>
       </c>
       <c r="G93">
         <v>2978</v>
@@ -8919,37 +8919,37 @@
         <v>5054</v>
       </c>
       <c r="M93">
-        <v>14702.61655425186</v>
+        <v>14864.18376913375</v>
       </c>
       <c r="N93">
-        <v>-9648.616554251859</v>
+        <v>-9810.183769133748</v>
       </c>
       <c r="O93">
-        <v>-1206.077069281482</v>
+        <v>-1226.272971141718</v>
       </c>
       <c r="P93">
-        <v>-8442.539484970377</v>
+        <v>-8583.91079799203</v>
       </c>
       <c r="Q93">
-        <v>-6708.539484970377</v>
+        <v>-6849.91079799203</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4377078057546323</v>
+        <v>0.4866962814739614</v>
       </c>
       <c r="T93">
-        <v>7.639012591773033</v>
+        <v>8.593889165744665</v>
       </c>
       <c r="U93">
         <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.04296854220940039</v>
+        <v>0.04250149283755909</v>
       </c>
       <c r="W93">
-        <v>0.1978534456232414</v>
+        <v>0.1979500018301902</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3437483376752032</v>
+        <v>0.3400119427004726</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2210497042016919</v>
+        <v>0.2226590703683172</v>
       </c>
       <c r="C94">
-        <v>-52823.7624156751</v>
+        <v>-53751.75615352116</v>
       </c>
       <c r="D94">
-        <v>16097.37189877126</v>
+        <v>15950.89049043005</v>
       </c>
       <c r="E94">
-        <v>56471.6013639612</v>
+        <v>57253.11369346605</v>
       </c>
       <c r="F94">
-        <v>71899.13431444636</v>
+        <v>72680.64664395122</v>
       </c>
       <c r="G94">
         <v>2978</v>
@@ -9001,37 +9001,37 @@
         <v>5054</v>
       </c>
       <c r="M94">
-        <v>14864.18376913375</v>
+        <v>15025.75098401564</v>
       </c>
       <c r="N94">
-        <v>-9810.183769133748</v>
+        <v>-9971.750984015638</v>
       </c>
       <c r="O94">
-        <v>-1226.272971141718</v>
+        <v>-1246.468873001955</v>
       </c>
       <c r="P94">
-        <v>-8583.91079799203</v>
+        <v>-8725.282111013683</v>
       </c>
       <c r="Q94">
-        <v>-6849.91079799203</v>
+        <v>-6991.282111013683</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4866962814739614</v>
+        <v>0.5496814645416702</v>
       </c>
       <c r="T94">
-        <v>8.593889165744665</v>
+        <v>9.821587617993904</v>
       </c>
       <c r="U94">
         <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.04250149283755909</v>
+        <v>0.04204448753823049</v>
       </c>
       <c r="W94">
-        <v>0.1979500018301902</v>
+        <v>0.1980444815595702</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3400119427004726</v>
+        <v>0.3363559003058439</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2226590703683172</v>
+        <v>0.2242684365349426</v>
       </c>
       <c r="C95">
-        <v>-53751.75615352116</v>
+        <v>-54677.10805478029</v>
       </c>
       <c r="D95">
-        <v>15950.89049043005</v>
+        <v>15807.05091867576</v>
       </c>
       <c r="E95">
-        <v>57253.11369346605</v>
+        <v>58034.62602297089</v>
       </c>
       <c r="F95">
-        <v>72680.64664395122</v>
+        <v>73462.15897345605</v>
       </c>
       <c r="G95">
         <v>2978</v>
@@ -9083,37 +9083,37 @@
         <v>5054</v>
       </c>
       <c r="M95">
-        <v>15025.75098401564</v>
+        <v>15187.31819889752</v>
       </c>
       <c r="N95">
-        <v>-9971.750984015638</v>
+        <v>-10133.31819889752</v>
       </c>
       <c r="O95">
-        <v>-1246.468873001955</v>
+        <v>-1266.66477486219</v>
       </c>
       <c r="P95">
-        <v>-8725.282111013683</v>
+        <v>-8866.653424035332</v>
       </c>
       <c r="Q95">
-        <v>-6991.282111013683</v>
+        <v>-7132.653424035332</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5496814645416702</v>
+        <v>0.6336617086319487</v>
       </c>
       <c r="T95">
-        <v>9.821587617993904</v>
+        <v>11.45851888765956</v>
       </c>
       <c r="U95">
         <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.04204448753823049</v>
+        <v>0.0415972057559089</v>
       </c>
       <c r="W95">
-        <v>0.1980444815595702</v>
+        <v>0.1981369510819422</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3363559003058439</v>
+        <v>0.3327776460472712</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2242684365349426</v>
+        <v>0.2258778027015679</v>
       </c>
       <c r="C96">
-        <v>-54677.10805478029</v>
+        <v>-55599.88895021052</v>
       </c>
       <c r="D96">
-        <v>15807.05091867576</v>
+        <v>15665.7823527504</v>
       </c>
       <c r="E96">
-        <v>58034.62602297089</v>
+        <v>58816.13835247575</v>
       </c>
       <c r="F96">
-        <v>73462.15897345605</v>
+        <v>74243.67130296091</v>
       </c>
       <c r="G96">
         <v>2978</v>
@@ -9165,37 +9165,37 @@
         <v>5054</v>
       </c>
       <c r="M96">
-        <v>15187.31819889752</v>
+        <v>15348.88541377941</v>
       </c>
       <c r="N96">
-        <v>-10133.31819889752</v>
+        <v>-10294.88541377941</v>
       </c>
       <c r="O96">
-        <v>-1266.66477486219</v>
+        <v>-1286.860676722427</v>
       </c>
       <c r="P96">
-        <v>-8866.653424035332</v>
+        <v>-9008.024737056987</v>
       </c>
       <c r="Q96">
-        <v>-7132.653424035332</v>
+        <v>-7274.024737056987</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6336617086319487</v>
+        <v>0.7512340503583388</v>
       </c>
       <c r="T96">
-        <v>11.45851888765956</v>
+        <v>13.75022266519148</v>
       </c>
       <c r="U96">
         <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.0415972057559089</v>
+        <v>0.04115934043216248</v>
       </c>
       <c r="W96">
-        <v>0.1981369510819422</v>
+        <v>0.1982274738775274</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3327776460472712</v>
+        <v>0.3292747234572999</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2258778027015679</v>
+        <v>0.2274871688681933</v>
       </c>
       <c r="C97">
-        <v>-55599.88895021052</v>
+        <v>-56520.16716092364</v>
       </c>
       <c r="D97">
-        <v>15665.7823527504</v>
+        <v>15527.01647154212</v>
       </c>
       <c r="E97">
-        <v>58816.13835247575</v>
+        <v>59597.6506819806</v>
       </c>
       <c r="F97">
-        <v>74243.67130296091</v>
+        <v>75025.18363246576</v>
       </c>
       <c r="G97">
         <v>2978</v>
@@ -9247,37 +9247,37 @@
         <v>5054</v>
       </c>
       <c r="M97">
-        <v>15348.88541377941</v>
+        <v>15510.4526286613</v>
       </c>
       <c r="N97">
-        <v>-10294.88541377941</v>
+        <v>-10456.4526286613</v>
       </c>
       <c r="O97">
-        <v>-1286.860676722427</v>
+        <v>-1307.056578582663</v>
       </c>
       <c r="P97">
-        <v>-9008.024737056987</v>
+        <v>-9149.39605007864</v>
       </c>
       <c r="Q97">
-        <v>-7274.024737056987</v>
+        <v>-7415.39605007864</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7512340503583388</v>
+        <v>0.927592562947924</v>
       </c>
       <c r="T97">
-        <v>13.75022266519148</v>
+        <v>17.18777833148935</v>
       </c>
       <c r="U97">
         <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.04115934043216248</v>
+        <v>0.04073059730266079</v>
       </c>
       <c r="W97">
-        <v>0.1982274738775274</v>
+        <v>0.1983161107815379</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3292747234572999</v>
+        <v>0.3258447784212863</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2274871688681932</v>
+        <v>0.2290965350348186</v>
       </c>
       <c r="C98">
-        <v>-56520.16716092364</v>
+        <v>-57438.00860856041</v>
       </c>
       <c r="D98">
-        <v>15527.01647154212</v>
+        <v>15390.68735341019</v>
       </c>
       <c r="E98">
-        <v>59597.6506819806</v>
+        <v>60379.16301148544</v>
       </c>
       <c r="F98">
-        <v>75025.18363246576</v>
+        <v>75806.6959619706</v>
       </c>
       <c r="G98">
         <v>2978</v>
@@ -9329,37 +9329,37 @@
         <v>5054</v>
       </c>
       <c r="M98">
-        <v>15510.4526286613</v>
+        <v>15672.01984354319</v>
       </c>
       <c r="N98">
-        <v>-10456.4526286613</v>
+        <v>-10618.01984354319</v>
       </c>
       <c r="O98">
-        <v>-1307.056578582663</v>
+        <v>-1327.252480442899</v>
       </c>
       <c r="P98">
-        <v>-9149.39605007864</v>
+        <v>-9290.767363100291</v>
       </c>
       <c r="Q98">
-        <v>-7415.39605007864</v>
+        <v>-7556.767363100291</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9275925629479217</v>
+        <v>1.221523417263896</v>
       </c>
       <c r="T98">
-        <v>17.18777833148931</v>
+        <v>22.91703777531908</v>
       </c>
       <c r="U98">
         <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.04073059730266079</v>
+        <v>0.04031069423768491</v>
       </c>
       <c r="W98">
-        <v>0.1983161107815379</v>
+        <v>0.1984029201205172</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3258447784212863</v>
+        <v>0.3224855539014793</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2290965350348186</v>
+        <v>0.230705901201444</v>
       </c>
       <c r="C99">
-        <v>-57438.00860856041</v>
+        <v>-58353.47691971186</v>
       </c>
       <c r="D99">
-        <v>15390.68735341019</v>
+        <v>15256.7313717636</v>
       </c>
       <c r="E99">
-        <v>60379.16301148544</v>
+        <v>61160.6753409903</v>
       </c>
       <c r="F99">
-        <v>75806.6959619706</v>
+        <v>76588.20829147546</v>
       </c>
       <c r="G99">
         <v>2978</v>
@@ -9411,37 +9411,37 @@
         <v>5054</v>
       </c>
       <c r="M99">
-        <v>15672.01984354319</v>
+        <v>15833.58705842508</v>
       </c>
       <c r="N99">
-        <v>-10618.01984354319</v>
+        <v>-10779.58705842508</v>
       </c>
       <c r="O99">
-        <v>-1327.252480442899</v>
+        <v>-1347.448382303135</v>
       </c>
       <c r="P99">
-        <v>-9290.767363100291</v>
+        <v>-9432.138676121942</v>
       </c>
       <c r="Q99">
-        <v>-7556.767363100291</v>
+        <v>-7698.138676121942</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.221523417263896</v>
+        <v>1.809385125895844</v>
       </c>
       <c r="T99">
-        <v>22.91703777531908</v>
+        <v>34.37555666297862</v>
       </c>
       <c r="U99">
         <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.04031069423768491</v>
+        <v>0.03989936062301466</v>
       </c>
       <c r="W99">
-        <v>0.1984029201205172</v>
+        <v>0.1984879578403337</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3224855539014793</v>
+        <v>0.3191948849841173</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.230705901201444</v>
+        <v>0.2323152673680693</v>
       </c>
       <c r="C100">
-        <v>-58353.47691971186</v>
+        <v>-59266.63352493465</v>
       </c>
       <c r="D100">
-        <v>15256.7313717636</v>
+        <v>15125.08709604566</v>
       </c>
       <c r="E100">
-        <v>61160.6753409903</v>
+        <v>61942.18767049515</v>
       </c>
       <c r="F100">
-        <v>76588.20829147546</v>
+        <v>77369.72062098031</v>
       </c>
       <c r="G100">
         <v>2978</v>
@@ -9493,37 +9493,37 @@
         <v>5054</v>
       </c>
       <c r="M100">
-        <v>15833.58705842508</v>
+        <v>15995.15427330697</v>
       </c>
       <c r="N100">
-        <v>-10779.58705842508</v>
+        <v>-10941.15427330697</v>
       </c>
       <c r="O100">
-        <v>-1347.448382303135</v>
+        <v>-1367.644284163371</v>
       </c>
       <c r="P100">
-        <v>-9432.138676121942</v>
+        <v>-9573.509989143595</v>
       </c>
       <c r="Q100">
-        <v>-7698.138676121942</v>
+        <v>-7839.509989143595</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.809385125895844</v>
+        <v>3.572970251791687</v>
       </c>
       <c r="T100">
-        <v>34.37555666297862</v>
+        <v>68.75111332595723</v>
       </c>
       <c r="U100">
         <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.03989936062301466</v>
+        <v>0.03949633677833774</v>
       </c>
       <c r="W100">
-        <v>0.1984879578403337</v>
+        <v>0.1985712776264165</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3191948849841173</v>
+        <v>0.315970694226702</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2323152673680693</v>
-      </c>
-      <c r="C101">
-        <v>-59266.63352493465</v>
-      </c>
-      <c r="D101">
-        <v>15125.08709604566</v>
-      </c>
-      <c r="E101">
-        <v>61942.18767049515</v>
-      </c>
-      <c r="F101">
-        <v>77369.72062098031</v>
-      </c>
-      <c r="G101">
-        <v>2978</v>
-      </c>
-      <c r="H101">
-        <v>62723.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>6788</v>
-      </c>
-      <c r="K101">
-        <v>1734</v>
-      </c>
-      <c r="L101">
-        <v>5054</v>
-      </c>
-      <c r="M101">
-        <v>15995.15427330697</v>
-      </c>
-      <c r="N101">
-        <v>-10941.15427330697</v>
-      </c>
-      <c r="O101">
-        <v>-1367.644284163371</v>
-      </c>
-      <c r="P101">
-        <v>-9573.509989143595</v>
-      </c>
-      <c r="Q101">
-        <v>-7839.509989143595</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.572970251791687</v>
-      </c>
-      <c r="T101">
-        <v>68.75111332595723</v>
-      </c>
-      <c r="U101">
-        <v>0.2067366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.03949633677833774</v>
-      </c>
-      <c r="W101">
-        <v>0.1985712776264165</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.315970694226702</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
